--- a/excel/1. Bi-monthly d-set calculations.xlsx
+++ b/excel/1. Bi-monthly d-set calculations.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP 35\Desktop\PhD\2. Fuzzy (1-IJMEMS)\2. Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP 35\Desktop\PhD\2. Fuzzy (1-IJMEMS)\git\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F3E063-DD0A-4C4A-AEF4-6BC9230BCE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52DB7DE-44AC-4708-95CB-F0DD21BD428E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{88C08D68-2E9A-4EC7-8AF8-2F1D08621B1E}"/>
   </bookViews>
@@ -1095,7 +1095,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1230,7 +1230,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1244,18 +1243,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1348,6 +1341,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1396,6 +1392,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1656,55 +1653,55 @@
             <c:numRef>
               <c:f>calculations!$CR$4:$CR$19</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.10233756076828503</c:v>
+                  <c:v>9.5692001688647416E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2728543129923055</c:v>
+                  <c:v>0.24785972406491297</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.1337851418104504E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.12314796911451484</c:v>
+                  <c:v>9.7125272970140286E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.20201607217139095</c:v>
+                  <c:v>0.18562173836122856</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.10213391263037562</c:v>
+                  <c:v>7.6348326566344313E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.3198652511055866E-2</c:v>
+                  <c:v>1.9329888954713031E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.7772273707873647E-2</c:v>
+                  <c:v>9.4487681982756856E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.16318820243494039</c:v>
+                  <c:v>0.13184769092129592</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.27066242449556105</c:v>
+                  <c:v>0.24360795985716413</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>6.1014576639333287E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.15288167564300262</c:v>
+                  <c:v>0.12533895113769858</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.7106406507775055E-2</c:v>
+                  <c:v>6.6169443219217416E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.12808124957554093</c:v>
+                  <c:v>9.6364700817106227E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.4231878896574176E-2</c:v>
+                  <c:v>2.5717500435727056E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>7.6760590746343546E-2</c:v>
+                  <c:v>4.6400004831139305E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1762,7 +1759,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0B3BB4EE-1F47-4F2A-B659-5C27A376C875}" type="CELLRANGE">
+                    <a:fld id="{DE20CCA9-4970-4D2E-AFB5-AA2E9EC05C8A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1794,7 +1791,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3BFA1169-05AA-442B-B6C8-99572EF703B0}" type="CELLRANGE">
+                    <a:fld id="{D2328611-87D3-4C7A-960F-400537B299ED}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1827,7 +1824,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{92F00774-1A72-4525-9E04-930DEB49B951}" type="CELLRANGE">
+                    <a:fld id="{4F1D549F-2603-4C70-9554-3DF90B81ABFB}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1860,7 +1857,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{20A06371-DAD3-42A3-94E4-76A905182815}" type="CELLRANGE">
+                    <a:fld id="{754BFBBD-7CBC-4104-AA47-7D5FB1B09211}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1893,7 +1890,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BA702A70-3882-4638-878D-927819D6E562}" type="CELLRANGE">
+                    <a:fld id="{D3A06479-113A-4181-BE3A-C5A208821710}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1926,7 +1923,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C326D379-6A92-43BC-9A1A-D1BCCCD2FDFD}" type="CELLRANGE">
+                    <a:fld id="{2536BC30-8912-481F-A724-2D1DCE2EC61C}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1959,7 +1956,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{62527363-95C4-438C-BC5E-0DD4D813F7E1}" type="CELLRANGE">
+                    <a:fld id="{F63CD86F-D204-40AB-945E-02B40EA59664}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1992,7 +1989,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2D6980E9-A5E1-4819-BC3D-309BA5C7CFC6}" type="CELLRANGE">
+                    <a:fld id="{A26521D3-2AD5-4FA8-9EC6-F59DE1A1F939}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2025,7 +2022,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F91AC951-F469-4DB4-B95F-F1175DF0B156}" type="CELLRANGE">
+                    <a:fld id="{E6B5689C-2FCB-4AFA-AE15-AB1427769880}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2058,7 +2055,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{916B810D-7B19-4DE8-82FB-14A2926DEED9}" type="CELLRANGE">
+                    <a:fld id="{BC55705B-9F9F-4D2D-87E7-A7B90B10EB87}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2091,7 +2088,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{325E2C07-E3A1-4BF9-9920-4BE5CDAB5566}" type="CELLRANGE">
+                    <a:fld id="{54ABD5E4-58C5-4D82-9CFA-A1AAAAF417B2}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2124,7 +2121,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{50CA3946-5658-44B0-8DFB-B9CB1F6ECF1F}" type="CELLRANGE">
+                    <a:fld id="{8C259200-A37E-45BC-B410-27B5F5E99CDF}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2157,7 +2154,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4AD8CEB4-5D12-45F3-A56E-8EA153DDF09A}" type="CELLRANGE">
+                    <a:fld id="{2C0775A8-C62A-4F8A-BCD1-6C53581D241B}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2190,7 +2187,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F8E7D30A-A60C-4E16-956C-91B3F538578C}" type="CELLRANGE">
+                    <a:fld id="{BBDF4F31-9FF4-4C95-B762-418CAE99157D}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2223,7 +2220,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FFF034B8-1934-4479-B96D-6C95857F91F2}" type="CELLRANGE">
+                    <a:fld id="{2C1E3668-6BE0-461B-8C91-FC2D778462A9}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2256,7 +2253,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8BF37A7C-CCDB-482A-A547-E222F757D8F9}" type="CELLRANGE">
+                    <a:fld id="{C5929DE8-353E-46C9-9C11-D867C0CEA4F8}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2402,52 +2399,52 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.70730470769234732</c:v>
+                  <c:v>0.69514697580722284</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.44779002457965195</c:v>
+                  <c:v>0.41837298407203521</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.60966029094774321</c:v>
+                  <c:v>0.58512891391484234</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.7028106260362752</c:v>
+                  <c:v>0.68655732289201454</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.5539329452730547</c:v>
+                  <c:v>0.52735653607068889</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.71845686025402644</c:v>
+                  <c:v>0.70573211816674031</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.61613018871295067</c:v>
+                  <c:v>0.60363880524245672</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.73809752718154686</c:v>
+                  <c:v>0.7201266203540666</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.64280642592999171</c:v>
+                  <c:v>0.61621603296852046</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.75230056304843929</c:v>
+                  <c:v>0.75067520916190289</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.68597567860655229</c:v>
+                  <c:v>0.6652961850344622</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.58116038464557684</c:v>
+                  <c:v>0.55798110091559416</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.6115802836702976</c:v>
+                  <c:v>0.58578531837909842</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.75260395519276724</c:v>
+                  <c:v>0.74860905335020655</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.51587021119041687</c:v>
+                  <c:v>0.4852862351914235</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2460,52 +2457,52 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="16"/>
                   <c:pt idx="0">
-                    <c:v>0.707</c:v>
+                    <c:v>0.695</c:v>
                   </c:pt>
                   <c:pt idx="1">
                     <c:v>1.000</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>0.448</c:v>
+                    <c:v>0.418</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>0.610</c:v>
+                    <c:v>0.585</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>0.703</c:v>
+                    <c:v>0.687</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>0.554</c:v>
+                    <c:v>0.527</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>0.718</c:v>
+                    <c:v>0.706</c:v>
                   </c:pt>
                   <c:pt idx="7">
+                    <c:v>0.604</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>0.720</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
                     <c:v>0.616</c:v>
                   </c:pt>
-                  <c:pt idx="8">
-                    <c:v>0.738</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>0.643</c:v>
-                  </c:pt>
                   <c:pt idx="10">
-                    <c:v>0.752</c:v>
+                    <c:v>0.751</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>0.686</c:v>
+                    <c:v>0.665</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>0.581</c:v>
+                    <c:v>0.558</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>0.612</c:v>
+                    <c:v>0.586</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>0.753</c:v>
+                    <c:v>0.749</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>0.516</c:v>
+                    <c:v>0.485</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -2646,7 +2643,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3676,26 +3673,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="80"/>
-      <c r="C1" s="80" t="s">
+      <c r="B1" s="73"/>
+      <c r="C1" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="23"/>
-      <c r="C3" s="76" t="s">
+      <c r="C3" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="D3" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="69" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3706,10 +3703,10 @@
       <c r="C4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="77">
+      <c r="D4" s="70">
         <v>45170</v>
       </c>
-      <c r="E4" s="77">
+      <c r="E4" s="70">
         <v>45199</v>
       </c>
       <c r="F4" s="8">
@@ -3723,10 +3720,10 @@
       <c r="C5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="77">
+      <c r="D5" s="70">
         <v>45200</v>
       </c>
-      <c r="E5" s="77">
+      <c r="E5" s="70">
         <v>45230</v>
       </c>
       <c r="F5" s="8">
@@ -3740,10 +3737,10 @@
       <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="77">
+      <c r="D6" s="70">
         <v>45231</v>
       </c>
-      <c r="E6" s="77">
+      <c r="E6" s="70">
         <v>45260</v>
       </c>
       <c r="F6" s="8">
@@ -3757,10 +3754,10 @@
       <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="77">
+      <c r="D7" s="70">
         <v>45261</v>
       </c>
-      <c r="E7" s="77">
+      <c r="E7" s="70">
         <v>45291</v>
       </c>
       <c r="F7" s="8">
@@ -3774,10 +3771,10 @@
       <c r="C8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="77">
+      <c r="D8" s="70">
         <v>45292</v>
       </c>
-      <c r="E8" s="77">
+      <c r="E8" s="70">
         <v>45322</v>
       </c>
       <c r="F8" s="8">
@@ -3791,10 +3788,10 @@
       <c r="C9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="77">
+      <c r="D9" s="70">
         <v>45323</v>
       </c>
-      <c r="E9" s="77">
+      <c r="E9" s="70">
         <v>45351</v>
       </c>
       <c r="F9" s="8">
@@ -3808,10 +3805,10 @@
       <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="77">
+      <c r="D10" s="70">
         <v>45352</v>
       </c>
-      <c r="E10" s="77">
+      <c r="E10" s="70">
         <v>45382</v>
       </c>
       <c r="F10" s="8">
@@ -3825,10 +3822,10 @@
       <c r="C11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="77">
+      <c r="D11" s="70">
         <v>45383</v>
       </c>
-      <c r="E11" s="77">
+      <c r="E11" s="70">
         <v>45412</v>
       </c>
       <c r="F11" s="8">
@@ -3842,10 +3839,10 @@
       <c r="C12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="77">
+      <c r="D12" s="70">
         <v>45413</v>
       </c>
-      <c r="E12" s="77">
+      <c r="E12" s="70">
         <v>45443</v>
       </c>
       <c r="F12" s="8">
@@ -3859,10 +3856,10 @@
       <c r="C13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="77">
+      <c r="D13" s="70">
         <v>45444</v>
       </c>
-      <c r="E13" s="77">
+      <c r="E13" s="70">
         <v>45473</v>
       </c>
       <c r="F13" s="8">
@@ -3876,10 +3873,10 @@
       <c r="C14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="77">
+      <c r="D14" s="70">
         <v>45474</v>
       </c>
-      <c r="E14" s="77">
+      <c r="E14" s="70">
         <v>45504</v>
       </c>
       <c r="F14" s="8">
@@ -3893,10 +3890,10 @@
       <c r="C15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="77">
+      <c r="D15" s="70">
         <v>45505</v>
       </c>
-      <c r="E15" s="77">
+      <c r="E15" s="70">
         <v>45535</v>
       </c>
       <c r="F15" s="8">
@@ -3907,10 +3904,10 @@
       <c r="B16" s="6"/>
     </row>
     <row r="17" spans="5:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="78" t="s">
+      <c r="E17" s="71" t="s">
         <v>125</v>
       </c>
-      <c r="F17" s="79">
+      <c r="F17" s="72">
         <f>SUM(F4:F15)</f>
         <v>8484</v>
       </c>
@@ -5575,11 +5572,11 @@
     <col min="28" max="28" width="20.140625" customWidth="1"/>
     <col min="29" max="29" width="21" customWidth="1"/>
     <col min="30" max="30" width="17.85546875" customWidth="1"/>
-    <col min="32" max="32" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.140625" customWidth="1"/>
+    <col min="33" max="33" width="5.7109375" customWidth="1"/>
+    <col min="34" max="35" width="5.85546875" customWidth="1"/>
+    <col min="36" max="36" width="5.7109375" customWidth="1"/>
+    <col min="37" max="37" width="8.140625" customWidth="1"/>
     <col min="38" max="38" width="19.140625" customWidth="1"/>
     <col min="39" max="42" width="6.7109375" style="9" customWidth="1"/>
     <col min="43" max="43" width="9.140625" customWidth="1"/>
@@ -5589,9 +5586,9 @@
     <col min="50" max="50" width="2.7109375" hidden="1" customWidth="1"/>
     <col min="51" max="54" width="5.7109375" hidden="1" customWidth="1"/>
     <col min="55" max="55" width="5.7109375" customWidth="1"/>
-    <col min="56" max="56" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.140625" customWidth="1"/>
     <col min="57" max="60" width="5.7109375" customWidth="1"/>
-    <col min="61" max="64" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="64" width="6.7109375" customWidth="1"/>
     <col min="65" max="66" width="5.7109375" customWidth="1"/>
     <col min="67" max="67" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="68" max="75" width="5.7109375" bestFit="1" customWidth="1"/>
@@ -5602,94 +5599,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="T1" s="117" t="s">
+      <c r="T1" s="113" t="s">
         <v>129</v>
       </c>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="117"/>
-      <c r="AA1" s="117"/>
-      <c r="AB1" s="117"/>
-      <c r="AC1" s="117"/>
-      <c r="AD1" s="117"/>
-      <c r="AF1" s="117" t="s">
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
+      <c r="AC1" s="113"/>
+      <c r="AD1" s="113"/>
+      <c r="AF1" s="113" t="s">
         <v>130</v>
       </c>
-      <c r="AG1" s="117"/>
-      <c r="AH1" s="117"/>
-      <c r="AI1" s="117"/>
-      <c r="AJ1" s="117"/>
-      <c r="AK1" s="117"/>
-      <c r="AL1" s="117"/>
-      <c r="AM1" s="117"/>
-      <c r="AN1" s="117"/>
-      <c r="AO1" s="117"/>
-      <c r="AP1" s="117"/>
-      <c r="AQ1" s="117"/>
-      <c r="AR1" s="117"/>
-      <c r="AS1" s="117"/>
-      <c r="AT1" s="117"/>
-      <c r="AU1" s="117"/>
-      <c r="AV1" s="117"/>
-      <c r="AW1" s="117"/>
-      <c r="AX1" s="117"/>
-      <c r="AY1" s="117"/>
-      <c r="AZ1" s="117"/>
-      <c r="BA1" s="117"/>
-      <c r="BB1" s="117"/>
-      <c r="BC1" s="117"/>
-      <c r="BD1" s="117"/>
-      <c r="BE1" s="117"/>
-      <c r="BF1" s="117"/>
-      <c r="BG1" s="117"/>
-      <c r="BH1" s="117"/>
-      <c r="BI1" s="117"/>
-      <c r="BJ1" s="117"/>
-      <c r="BK1" s="117"/>
-      <c r="BL1" s="117"/>
-      <c r="BM1" s="117"/>
-      <c r="BN1" s="117"/>
-      <c r="BO1" s="117"/>
-      <c r="BP1" s="117"/>
-      <c r="BQ1" s="117"/>
-      <c r="BR1" s="117"/>
-      <c r="BS1" s="117"/>
-      <c r="BT1" s="117"/>
-      <c r="BU1" s="117"/>
-      <c r="BV1" s="117"/>
-      <c r="BW1" s="117"/>
-      <c r="BX1" s="117"/>
-      <c r="BY1" s="117"/>
-      <c r="BZ1" s="117"/>
-      <c r="CA1" s="117"/>
-      <c r="CB1" s="117"/>
-      <c r="CC1" s="117"/>
-      <c r="CD1" s="117"/>
-      <c r="CE1" s="117"/>
-      <c r="CF1" s="117"/>
-      <c r="CG1" s="117"/>
-      <c r="CH1" s="117"/>
-      <c r="CI1" s="117"/>
-      <c r="CJ1" s="117"/>
-      <c r="CK1" s="117"/>
-      <c r="CL1" s="117"/>
-      <c r="CM1" s="117"/>
-      <c r="CO1" s="116" t="s">
+      <c r="AG1" s="113"/>
+      <c r="AH1" s="113"/>
+      <c r="AI1" s="113"/>
+      <c r="AJ1" s="113"/>
+      <c r="AK1" s="113"/>
+      <c r="AL1" s="113"/>
+      <c r="AM1" s="113"/>
+      <c r="AN1" s="113"/>
+      <c r="AO1" s="113"/>
+      <c r="AP1" s="113"/>
+      <c r="AQ1" s="113"/>
+      <c r="AR1" s="113"/>
+      <c r="AS1" s="113"/>
+      <c r="AT1" s="113"/>
+      <c r="AU1" s="113"/>
+      <c r="AV1" s="113"/>
+      <c r="AW1" s="113"/>
+      <c r="AX1" s="113"/>
+      <c r="AY1" s="113"/>
+      <c r="AZ1" s="113"/>
+      <c r="BA1" s="113"/>
+      <c r="BB1" s="113"/>
+      <c r="BC1" s="113"/>
+      <c r="BD1" s="113"/>
+      <c r="BE1" s="113"/>
+      <c r="BF1" s="113"/>
+      <c r="BG1" s="113"/>
+      <c r="BH1" s="113"/>
+      <c r="BI1" s="113"/>
+      <c r="BJ1" s="113"/>
+      <c r="BK1" s="113"/>
+      <c r="BL1" s="113"/>
+      <c r="BM1" s="113"/>
+      <c r="BN1" s="113"/>
+      <c r="BO1" s="113"/>
+      <c r="BP1" s="113"/>
+      <c r="BQ1" s="113"/>
+      <c r="BR1" s="113"/>
+      <c r="BS1" s="113"/>
+      <c r="BT1" s="113"/>
+      <c r="BU1" s="113"/>
+      <c r="BV1" s="113"/>
+      <c r="BW1" s="113"/>
+      <c r="BX1" s="113"/>
+      <c r="BY1" s="113"/>
+      <c r="BZ1" s="113"/>
+      <c r="CA1" s="113"/>
+      <c r="CB1" s="113"/>
+      <c r="CC1" s="113"/>
+      <c r="CD1" s="113"/>
+      <c r="CE1" s="113"/>
+      <c r="CF1" s="113"/>
+      <c r="CG1" s="113"/>
+      <c r="CH1" s="113"/>
+      <c r="CI1" s="113"/>
+      <c r="CJ1" s="113"/>
+      <c r="CK1" s="113"/>
+      <c r="CL1" s="113"/>
+      <c r="CM1" s="113"/>
+      <c r="CO1" s="112" t="s">
         <v>131</v>
       </c>
-      <c r="CP1" s="116"/>
-      <c r="CQ1" s="116"/>
-      <c r="CR1" s="116"/>
-      <c r="CS1" s="116"/>
-      <c r="CW1" s="63" t="s">
+      <c r="CP1" s="112"/>
+      <c r="CQ1" s="112"/>
+      <c r="CR1" s="112"/>
+      <c r="CS1" s="112"/>
+      <c r="CW1" s="61" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="73" t="s">
         <v>127</v>
       </c>
       <c r="H2" t="s">
@@ -5701,7 +5698,7 @@
       <c r="AF2" t="s">
         <v>54</v>
       </c>
-      <c r="AL2" s="80" t="s">
+      <c r="AL2" s="73" t="s">
         <v>128</v>
       </c>
       <c r="AR2" t="s">
@@ -5730,22 +5727,22 @@
       </c>
     </row>
     <row r="3" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="82" t="s">
+      <c r="D3" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="82" t="s">
+      <c r="E3" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="83" t="s">
+      <c r="F3" s="76" t="s">
         <v>51</v>
       </c>
       <c r="H3" s="29" t="s">
@@ -5816,7 +5813,7 @@
         <v>67</v>
       </c>
       <c r="AK3" s="33"/>
-      <c r="AL3" s="81" t="s">
+      <c r="AL3" s="74" t="s">
         <v>48</v>
       </c>
       <c r="AM3" s="34" t="s">
@@ -5866,36 +5863,36 @@
       </c>
       <c r="BC3" s="12"/>
       <c r="BD3" s="15"/>
-      <c r="BE3" s="118" t="s">
+      <c r="BE3" s="114" t="s">
         <v>69</v>
       </c>
-      <c r="BF3" s="118"/>
-      <c r="BG3" s="118"/>
-      <c r="BH3" s="118"/>
-      <c r="BI3" s="118" t="s">
+      <c r="BF3" s="114"/>
+      <c r="BG3" s="114"/>
+      <c r="BH3" s="114"/>
+      <c r="BI3" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="BJ3" s="118"/>
-      <c r="BK3" s="118"/>
-      <c r="BL3" s="119"/>
+      <c r="BJ3" s="114"/>
+      <c r="BK3" s="114"/>
+      <c r="BL3" s="115"/>
       <c r="BM3" s="12"/>
       <c r="BN3" s="12"/>
-      <c r="BP3" s="108" t="s">
+      <c r="BP3" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="BQ3" s="108"/>
-      <c r="BR3" s="108" t="s">
+      <c r="BQ3" s="104"/>
+      <c r="BR3" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="BS3" s="108"/>
-      <c r="BT3" s="108" t="s">
+      <c r="BS3" s="104"/>
+      <c r="BT3" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="BU3" s="108"/>
-      <c r="BV3" s="108" t="s">
+      <c r="BU3" s="104"/>
+      <c r="BV3" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="BW3" s="108"/>
+      <c r="BW3" s="104"/>
       <c r="BY3" s="40" t="s">
         <v>74</v>
       </c>
@@ -5918,10 +5915,10 @@
       <c r="CM3" t="s">
         <v>78</v>
       </c>
-      <c r="CP3" s="115" t="s">
+      <c r="CP3" s="111" t="s">
         <v>79</v>
       </c>
-      <c r="CQ3" s="115"/>
+      <c r="CQ3" s="111"/>
       <c r="CR3" t="s">
         <v>80</v>
       </c>
@@ -5936,19 +5933,19 @@
       <c r="A4" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="85">
+      <c r="B4" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="78">
         <v>6</v>
       </c>
-      <c r="D4" s="85">
+      <c r="D4" s="78">
         <v>32</v>
       </c>
-      <c r="E4" s="85">
+      <c r="E4" s="78">
         <v>2</v>
       </c>
-      <c r="F4" s="86">
+      <c r="F4" s="79">
         <v>0</v>
       </c>
       <c r="H4" s="42" t="s">
@@ -6033,19 +6030,19 @@
       <c r="AL4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AM4" s="91">
+      <c r="AM4" s="84">
         <f t="shared" ref="AM4:AM35" si="0">(AG$4-C4)/(AG$4-AG$5)</f>
         <v>0.98070739549839225</v>
       </c>
-      <c r="AN4" s="92">
+      <c r="AN4" s="85">
         <f t="shared" ref="AN4:AN35" si="1">(D4-AH$5)/(AH$4-AH$5)</f>
         <v>0.1807909604519774</v>
       </c>
-      <c r="AO4" s="92">
+      <c r="AO4" s="85">
         <f t="shared" ref="AO4:AO35" si="2">(E4-AI$5)/(AI$4-AI$5)</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP4" s="93">
+      <c r="AP4" s="86">
         <f t="shared" ref="AP4:AP35" si="3">(AJ$4-F4)/(AJ$4-AJ$5)</f>
         <v>1</v>
       </c>
@@ -6112,27 +6109,33 @@
       <c r="BN4" s="48"/>
       <c r="BO4" s="33"/>
       <c r="BP4" s="54">
-        <v>2.2727272727272728E-2</v>
+        <f>U35</f>
+        <v>1.4814814814814815E-2</v>
       </c>
       <c r="BQ4" s="54">
-        <v>0.10227272727272728</v>
+        <f>U36</f>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="BR4" s="54">
-        <v>0.11363636363636363</v>
+        <f>U37</f>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="BS4" s="54">
-        <v>0.31818181818181818</v>
-      </c>
-      <c r="BT4" s="55">
-        <v>0.39772727272727271</v>
-      </c>
-      <c r="BU4" s="55">
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="BV4" s="55">
+        <f>U38</f>
+        <v>0.2074074074074074</v>
+      </c>
+      <c r="BT4" s="54">
+        <f>V35</f>
+        <v>0.40229885057471265</v>
+      </c>
+      <c r="BU4" s="54">
+        <f>V36</f>
+        <v>0.55172413793103448</v>
+      </c>
+      <c r="BV4" s="54">
         <v>0.22727272727272727</v>
       </c>
-      <c r="BW4" s="55">
+      <c r="BW4" s="54">
         <v>0.375</v>
       </c>
       <c r="BY4" s="40" t="s">
@@ -6147,38 +6150,38 @@
       </c>
       <c r="CJ4" s="14">
         <f>(BZ6+CD6+BZ23+CD23)/$T$41</f>
-        <v>3.4888237372968742E-2</v>
+        <v>3.3429042896151825E-2</v>
       </c>
       <c r="CK4" s="14">
-        <f>(CA6+CE6+CA23+CE23)/$T$41</f>
-        <v>0.24405646101003106</v>
+        <f t="shared" ref="CJ4:CM11" si="4">(CA6+CE6+CA23+CE23)/$T$41</f>
+        <v>0.23212549967715335</v>
       </c>
       <c r="CL4" s="14">
-        <f>(CB6+CF6+CB23+CF23)/$T$41</f>
-        <v>6.6789062588146791E-2</v>
+        <f t="shared" si="4"/>
+        <v>6.6633535266871283E-2</v>
       </c>
       <c r="CM4" s="14">
-        <f>(CC6+CG6+CC23+CG23)/$T$41</f>
-        <v>0.29153875245514821</v>
+        <f t="shared" si="4"/>
+        <v>0.27296731419937559</v>
       </c>
       <c r="CO4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="CP4" s="14">
-        <f>CJ4-CM4</f>
-        <v>-0.25665051508217945</v>
+        <f t="shared" ref="CP4:CP19" si="5">CJ4-CM4</f>
+        <v>-0.23953827130322375</v>
       </c>
       <c r="CQ4" s="14">
-        <f>CK4-CL4</f>
-        <v>0.17726739842188427</v>
-      </c>
-      <c r="CR4" s="56">
-        <f>(CP4+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.10233756076828503</v>
-      </c>
-      <c r="CS4" s="56">
-        <f>(CQ4+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.70730470769234732</v>
+        <f t="shared" ref="CQ4:CQ19" si="6">CK4-CL4</f>
+        <v>0.16549196441028208</v>
+      </c>
+      <c r="CR4" s="116">
+        <f t="shared" ref="CR4:CR19" si="7">(CP4+$CP$21)/($CP$21+$CQ$21)</f>
+        <v>9.5692001688647416E-2</v>
+      </c>
+      <c r="CS4" s="55">
+        <f t="shared" ref="CS4:CS19" si="8">(CQ4+$CP$21)/($CP$21+$CQ$21)</f>
+        <v>0.69514697580722284</v>
       </c>
       <c r="CU4" s="14"/>
       <c r="CW4" s="44">
@@ -6239,7 +6242,7 @@
       <c r="R5" s="26">
         <v>0</v>
       </c>
-      <c r="T5" s="58" t="s">
+      <c r="T5" s="57" t="s">
         <v>92</v>
       </c>
       <c r="U5" s="52">
@@ -6260,7 +6263,7 @@
       <c r="AB5" t="s">
         <v>94</v>
       </c>
-      <c r="AC5" s="59" t="s">
+      <c r="AC5" s="58" t="s">
         <v>95</v>
       </c>
       <c r="AD5" s="19" t="s">
@@ -6300,7 +6303,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP5" s="94">
+      <c r="AP5" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6346,15 +6349,15 @@
         <v>0.53697749196141475</v>
       </c>
       <c r="BF5" s="13">
-        <f t="shared" ref="BF5:BH20" si="4">MIN(AN4,AN20,AN36,AN52,AN68,AN84)</f>
+        <f t="shared" ref="BF5:BH20" si="9">MIN(AN4,AN20,AN36,AN52,AN68,AN84)</f>
         <v>0.1807909604519774</v>
       </c>
       <c r="BG5" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH5" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="BI5" s="13">
@@ -6362,102 +6365,102 @@
         <v>0.98713826366559487</v>
       </c>
       <c r="BJ5" s="13">
-        <f t="shared" ref="BJ5:BL20" si="5">MAX(AN4,AN20,AN36,AN52,AN68,AN84)</f>
+        <f t="shared" ref="BJ5:BL20" si="10">MAX(AN4,AN20,AN36,AN52,AN68,AN84)</f>
         <v>0.60451977401129942</v>
       </c>
       <c r="BK5" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.23076923076923078</v>
       </c>
-      <c r="BL5" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL5" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM5" s="48"/>
       <c r="BN5" s="48"/>
       <c r="BO5" s="33"/>
-      <c r="BP5" s="109" t="s">
+      <c r="BP5" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="BQ5" s="110"/>
-      <c r="BR5" s="109" t="s">
+      <c r="BQ5" s="106"/>
+      <c r="BR5" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="BS5" s="110"/>
-      <c r="BT5" s="109" t="s">
+      <c r="BS5" s="106"/>
+      <c r="BT5" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="BU5" s="110"/>
-      <c r="BV5" s="109" t="s">
+      <c r="BU5" s="106"/>
+      <c r="BV5" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="BW5" s="110"/>
+      <c r="BW5" s="106"/>
       <c r="BY5" s="41"/>
-      <c r="BZ5" s="60" t="s">
+      <c r="BZ5" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="CA5" s="60" t="s">
+      <c r="CA5" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="CB5" s="60" t="s">
+      <c r="CB5" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="CC5" s="60" t="s">
+      <c r="CC5" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="CD5" s="60" t="s">
+      <c r="CD5" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="CE5" s="60" t="s">
+      <c r="CE5" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="CF5" s="60" t="s">
+      <c r="CF5" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="CG5" s="60" t="s">
+      <c r="CG5" s="59" t="s">
         <v>100</v>
       </c>
       <c r="CI5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="CJ5" s="14">
-        <f>(BZ7+CD7+BZ24+CD24)/$T$41</f>
-        <v>3.3073964906898713E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.9287051190545779E-2</v>
       </c>
       <c r="CK5" s="14">
-        <f>(CA7+CE7+CA24+CE24)/$T$41</f>
-        <v>0.39916867164180647</v>
+        <f t="shared" si="4"/>
+        <v>0.38324157246395452</v>
       </c>
       <c r="CL5" s="14">
-        <f>(CB7+CF7+CB24+CF24)/$T$41</f>
-        <v>1.1963045704005778E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.1771348504938285E-2</v>
       </c>
       <c r="CM5" s="14">
-        <f>(CC7+CG7+CC24+CG24)/$T$41</f>
-        <v>0.16741986606295381</v>
+        <f t="shared" si="4"/>
+        <v>0.16601104765574823</v>
       </c>
       <c r="CO5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="CP5" s="14">
-        <f>CJ5-CM5</f>
-        <v>-0.1343459011560551</v>
+        <f t="shared" si="5"/>
+        <v>-0.13672399646520245</v>
       </c>
       <c r="CQ5" s="14">
-        <f>CK5-CL5</f>
-        <v>0.38720562593780067</v>
-      </c>
-      <c r="CR5" s="56">
-        <f>(CP5+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.2728543129923055</v>
-      </c>
-      <c r="CS5" s="56">
-        <f>(CQ5+$CP$21)/($CP$21+$CQ$21)</f>
+        <f t="shared" si="6"/>
+        <v>0.37147022395901624</v>
+      </c>
+      <c r="CR5" s="97">
+        <f t="shared" si="7"/>
+        <v>0.24785972406491297</v>
+      </c>
+      <c r="CS5" s="55">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="CU5" s="14"/>
       <c r="CW5" s="44">
-        <f>RANK(CR5,$CR$4:$CR$19,0)</f>
+        <f t="shared" ref="CW5:CW19" si="11">RANK(CR5,$CR$4:$CR$19,0)</f>
         <v>1</v>
       </c>
       <c r="CY5" s="14"/>
@@ -6514,7 +6517,7 @@
       <c r="R6" s="26">
         <v>1</v>
       </c>
-      <c r="T6" s="61" t="s">
+      <c r="T6" s="60" t="s">
         <v>37</v>
       </c>
       <c r="U6" s="52">
@@ -6569,7 +6572,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP6" s="94">
+      <c r="AP6" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6611,62 +6614,62 @@
         <v>2</v>
       </c>
       <c r="BE6" s="13">
-        <f t="shared" ref="BE6:BE20" si="6">MIN(AM5,AM21,AM37,AM53,AM69,AM85)</f>
+        <f t="shared" ref="BE6:BE20" si="12">MIN(AM5,AM21,AM37,AM53,AM69,AM85)</f>
         <v>0.99356913183279738</v>
       </c>
       <c r="BF6" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.12429378531073447</v>
       </c>
       <c r="BG6" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="BH6" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="BI6" s="13">
-        <f t="shared" ref="BI6:BI20" si="7">MAX(AM5,AM21,AM37,AM53,AM69,AM85)</f>
+        <f t="shared" ref="BI6:BI20" si="13">MAX(AM5,AM21,AM37,AM53,AM69,AM85)</f>
         <v>1</v>
       </c>
       <c r="BJ6" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.81355932203389836</v>
       </c>
       <c r="BK6" s="13">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="BL6" s="57">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="BL6" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM6" s="48"/>
       <c r="BN6" s="48"/>
       <c r="BO6" s="41"/>
-      <c r="BP6" s="60" t="s">
+      <c r="BP6" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="BQ6" s="60" t="s">
+      <c r="BQ6" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="BR6" s="60" t="s">
+      <c r="BR6" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="BS6" s="60" t="s">
+      <c r="BS6" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="BT6" s="60" t="s">
+      <c r="BT6" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="BU6" s="60" t="s">
+      <c r="BU6" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="BV6" s="60" t="s">
+      <c r="BV6" s="59" t="s">
         <v>99</v>
       </c>
-      <c r="BW6" s="60" t="s">
+      <c r="BW6" s="59" t="s">
         <v>100</v>
       </c>
       <c r="BY6" s="4" t="s">
@@ -6674,78 +6677,78 @@
       </c>
       <c r="BZ6" s="13">
         <f>BP7*BP$4</f>
-        <v>8.4156420076597505E-3</v>
+        <v>5.4857518272152447E-3</v>
       </c>
       <c r="CA6" s="13">
-        <f t="shared" ref="CA6:CG21" si="8">BQ7*BQ$4</f>
-        <v>6.9618020560370891E-2</v>
+        <f t="shared" ref="CA6:CG21" si="14">BQ7*BQ$4</f>
+        <v>4.5380635624538063E-2</v>
       </c>
       <c r="CB6" s="13">
-        <f t="shared" si="8"/>
-        <v>1.0078613182826026E-3</v>
+        <f t="shared" si="14"/>
+        <v>6.5697626673236328E-4</v>
       </c>
       <c r="CC6" s="13">
-        <f t="shared" si="8"/>
-        <v>0.1015924208828865</v>
+        <f t="shared" si="14"/>
+        <v>6.6223207686622321E-2</v>
       </c>
       <c r="CD6" s="13">
-        <f t="shared" si="8"/>
-        <v>5.0505050505050511E-2</v>
+        <f t="shared" si="14"/>
+        <v>5.1085568326947647E-2</v>
       </c>
       <c r="CE6" s="13">
-        <f t="shared" si="8"/>
-        <v>0.23160173160173161</v>
+        <f t="shared" si="14"/>
+        <v>0.23426382047071703</v>
       </c>
       <c r="CF6" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>6.3131313131313149E-2</v>
       </c>
       <c r="CG6" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.21577380952380953</v>
       </c>
       <c r="CI6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="CJ6" s="14">
-        <f>(BZ8+CD8+BZ25+CD25)/$T$41</f>
-        <v>1.465640706096592E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.2197642007688398E-2</v>
       </c>
       <c r="CK6" s="14">
-        <f>(CA8+CE8+CA25+CE25)/$T$41</f>
-        <v>0.12833512227789742</v>
+        <f t="shared" si="4"/>
+        <v>0.11418335462563983</v>
       </c>
       <c r="CL6" s="14">
-        <f>(CB8+CF8+CB25+CF25)/$T$41</f>
-        <v>0.13720687272133833</v>
+        <f t="shared" si="4"/>
+        <v>0.13569765415820495</v>
       </c>
       <c r="CM6" s="14">
-        <f>(CC8+CG8+CC25+CG25)/$T$41</f>
-        <v>0.32940466357318993</v>
+        <f t="shared" si="4"/>
+        <v>0.31639156831959592</v>
       </c>
       <c r="CO6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="CP6" s="14">
-        <f>CJ6-CM6</f>
-        <v>-0.31474825651222399</v>
+        <f t="shared" si="5"/>
+        <v>-0.3041939263119075</v>
       </c>
       <c r="CQ6" s="14">
-        <f>CK6-CL6</f>
-        <v>-8.8717504434409067E-3</v>
-      </c>
-      <c r="CR6" s="56">
-        <f>(CP6+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>2.1337851418104504E-2</v>
-      </c>
-      <c r="CS6" s="56">
-        <f>(CQ6+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.44779002457965195</v>
+        <f t="shared" si="6"/>
+        <v>-2.1514299532565118E-2</v>
+      </c>
+      <c r="CR6" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="CS6" s="55">
+        <f t="shared" si="8"/>
+        <v>0.41837298407203521</v>
       </c>
       <c r="CU6" s="14"/>
       <c r="CW6" s="44">
-        <f>RANK(CR6,$CR$4:$CR$19,0)</f>
-        <v>14</v>
+        <f t="shared" si="11"/>
+        <v>16</v>
       </c>
       <c r="CY6" s="14"/>
     </row>
@@ -6832,7 +6835,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP7" s="94">
+      <c r="AP7" s="87">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -6874,35 +6877,35 @@
         <v>4</v>
       </c>
       <c r="BE7" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.74919614147909963</v>
       </c>
       <c r="BF7" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>4.519774011299435E-2</v>
       </c>
       <c r="BG7" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH7" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI7" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.95176848874598075</v>
       </c>
       <c r="BJ7" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.12994350282485875</v>
       </c>
       <c r="BK7" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="BL7" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL7" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM7" s="48"/>
@@ -6910,16 +6913,16 @@
       <c r="BO7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="BP7" s="62">
+      <c r="BP7" s="13">
         <v>0.370288248337029</v>
       </c>
-      <c r="BQ7" s="62">
+      <c r="BQ7" s="13">
         <v>0.68070953436807091</v>
       </c>
-      <c r="BR7" s="62">
+      <c r="BR7" s="13">
         <v>8.8691796008869041E-3</v>
       </c>
-      <c r="BS7" s="62">
+      <c r="BS7" s="13">
         <v>0.31929046563192903</v>
       </c>
       <c r="BT7" s="13">
@@ -6938,79 +6941,79 @@
         <v>2</v>
       </c>
       <c r="BZ7" s="13">
-        <f t="shared" ref="BZ7:BZ21" si="9">BP8*BP$4</f>
-        <v>2.2436828347371481E-2</v>
+        <f t="shared" ref="BZ7:BZ21" si="15">BP8*BP$4</f>
+        <v>1.4625488107916224E-2</v>
       </c>
       <c r="CA7" s="13">
-        <f t="shared" si="8"/>
-        <v>0.10161922741794947</v>
+        <f t="shared" si="14"/>
+        <v>6.6240681576144836E-2</v>
       </c>
       <c r="CB7" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="CC7" s="13">
-        <f t="shared" si="8"/>
-        <v>2.0331106593087572E-3</v>
+        <f t="shared" si="14"/>
+        <v>1.3252869482901527E-3</v>
       </c>
       <c r="CD7" s="13">
-        <f t="shared" si="8"/>
-        <v>2.9264214046822744E-2</v>
+        <f t="shared" si="14"/>
+        <v>2.9600584323223007E-2</v>
       </c>
       <c r="CE7" s="13">
-        <f t="shared" si="8"/>
-        <v>0.2626938279112192</v>
+        <f t="shared" si="14"/>
+        <v>0.2657132971975551</v>
       </c>
       <c r="CF7" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>2.5083612040133769E-2</v>
       </c>
       <c r="CG7" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.1943979933110368</v>
       </c>
       <c r="CI7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="CJ7" s="14">
-        <f>(BZ9+CD9+BZ26+CD26)/$T$41</f>
-        <v>2.7799473977843311E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.4543388681883698E-2</v>
       </c>
       <c r="CK7" s="14">
-        <f>(CA9+CE9+CA26+CE26)/$T$41</f>
-        <v>0.19676872103747056</v>
+        <f t="shared" si="4"/>
+        <v>0.18042056262992626</v>
       </c>
       <c r="CL7" s="14">
-        <f>(CB9+CF9+CB26+CF26)/$T$41</f>
-        <v>8.953762424711656E-2</v>
+        <f t="shared" si="4"/>
+        <v>8.926385852261326E-2</v>
       </c>
       <c r="CM7" s="14">
-        <f>(CC9+CG9+CC26+CG26)/$T$41</f>
-        <v>0.26952354385605359</v>
+        <f t="shared" si="4"/>
+        <v>0.26311324996258983</v>
       </c>
       <c r="CO7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="CP7" s="14">
-        <f>CJ7-CM7</f>
-        <v>-0.24172406987821027</v>
+        <f t="shared" si="5"/>
+        <v>-0.23856986128070615</v>
       </c>
       <c r="CQ7" s="14">
-        <f>CK7-CL7</f>
-        <v>0.107231096790354</v>
-      </c>
-      <c r="CR7" s="56">
-        <f>(CP7+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.12314796911451484</v>
-      </c>
-      <c r="CS7" s="56">
-        <f>(CQ7+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.60966029094774321</v>
+        <f t="shared" si="6"/>
+        <v>9.1156704107312997E-2</v>
+      </c>
+      <c r="CR7" s="97">
+        <f t="shared" si="7"/>
+        <v>9.7125272970140286E-2</v>
+      </c>
+      <c r="CS7" s="55">
+        <f t="shared" si="8"/>
+        <v>0.58512891391484234</v>
       </c>
       <c r="CU7" s="14"/>
       <c r="CW7" s="44">
-        <f>RANK(CR7,$CR$4:$CR$19,0)</f>
-        <v>7</v>
+        <f t="shared" si="11"/>
+        <v>6</v>
       </c>
       <c r="CY7" s="14"/>
     </row>
@@ -7095,7 +7098,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP8" s="94">
+      <c r="AP8" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -7137,35 +7140,35 @@
         <v>5</v>
       </c>
       <c r="BE8" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.89067524115755625</v>
       </c>
       <c r="BF8" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.13559322033898305</v>
       </c>
       <c r="BG8" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH8" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI8" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.98392282958199362</v>
       </c>
       <c r="BJ8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.49152542372881358</v>
       </c>
       <c r="BK8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="BL8" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL8" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM8" s="48"/>
@@ -7201,78 +7204,78 @@
         <v>4</v>
       </c>
       <c r="BZ8" s="13">
-        <f t="shared" si="9"/>
-        <v>1.4158969372873115E-2</v>
+        <f t="shared" si="15"/>
+        <v>9.2295504060209942E-3</v>
       </c>
       <c r="CA8" s="13">
-        <f t="shared" si="8"/>
-        <v>8.0943121050072939E-2</v>
+        <f t="shared" si="14"/>
+        <v>5.2762923351158647E-2</v>
       </c>
       <c r="CB8" s="13">
-        <f t="shared" si="8"/>
-        <v>4.5576081672338313E-3</v>
+        <f t="shared" si="14"/>
+        <v>2.9708853238264977E-3</v>
       </c>
       <c r="CC8" s="13">
-        <f t="shared" si="8"/>
-        <v>6.6358774914924659E-2</v>
+        <f t="shared" si="14"/>
+        <v>4.3256090314913856E-2</v>
       </c>
       <c r="CD8" s="13">
-        <f t="shared" si="8"/>
-        <v>1.6571969696969696E-2</v>
+        <f t="shared" si="14"/>
+        <v>1.6762452107279693E-2</v>
       </c>
       <c r="CE8" s="13">
-        <f t="shared" si="8"/>
-        <v>6.5340909090909075E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.6091954022988494E-2</v>
       </c>
       <c r="CF8" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.18229166666666666</v>
       </c>
       <c r="CG8" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.330078125</v>
       </c>
       <c r="CI8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="CJ8" s="14">
-        <f>(BZ10+CD10+BZ27+CD27)/$T$41</f>
-        <v>6.1642421132130962E-2</v>
+        <f t="shared" si="4"/>
+        <v>5.8552153162062227E-2</v>
       </c>
       <c r="CK8" s="14">
-        <f>(CA10+CE10+CA27+CE27)/$T$41</f>
-        <v>0.24724516946958733</v>
+        <f t="shared" si="4"/>
+        <v>0.23197632458266035</v>
       </c>
       <c r="CL8" s="14">
-        <f>(CB10+CF10+CB27+CF27)/$T$41</f>
-        <v>7.3201189947778481E-2</v>
+        <f t="shared" si="4"/>
+        <v>7.2288080710454589E-2</v>
       </c>
       <c r="CM8" s="14">
-        <f>(CC10+CG10+CC27+CG27)/$T$41</f>
-        <v>0.2467976626128566</v>
+        <f t="shared" si="4"/>
+        <v>0.23732812535231851</v>
       </c>
       <c r="CO8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="CP8" s="14">
-        <f>CJ8-CM8</f>
-        <v>-0.18515524148072565</v>
+        <f t="shared" si="5"/>
+        <v>-0.17877597219025629</v>
       </c>
       <c r="CQ8" s="14">
-        <f>CK8-CL8</f>
-        <v>0.17404397952180883</v>
-      </c>
-      <c r="CR8" s="56">
-        <f>(CP8+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.20201607217139095</v>
-      </c>
-      <c r="CS8" s="56">
-        <f>(CQ8+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.7028106260362752</v>
+        <f t="shared" si="6"/>
+        <v>0.15968824387220576</v>
+      </c>
+      <c r="CR8" s="97">
+        <f t="shared" si="7"/>
+        <v>0.18562173836122856</v>
+      </c>
+      <c r="CS8" s="55">
+        <f t="shared" si="8"/>
+        <v>0.68655732289201454</v>
       </c>
       <c r="CU8" s="14"/>
       <c r="CW8" s="44">
-        <f>RANK(CR8,$CR$4:$CR$19,0)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="CY8" s="14"/>
@@ -7358,7 +7361,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP9" s="94">
+      <c r="AP9" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -7400,35 +7403,35 @@
         <v>6</v>
       </c>
       <c r="BE9" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.81672025723472674</v>
       </c>
       <c r="BF9" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.3728813559322034</v>
       </c>
       <c r="BG9" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH9" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="BJ9" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.68926553672316382</v>
       </c>
       <c r="BK9" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="BL9" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL9" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM9" s="48"/>
@@ -7464,78 +7467,78 @@
         <v>5</v>
       </c>
       <c r="BZ9" s="13">
-        <f t="shared" si="9"/>
-        <v>1.8516042780748664E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.2069716775599129E-2</v>
       </c>
       <c r="CA9" s="13">
-        <f t="shared" si="8"/>
-        <v>9.2045454545454569E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.0000000000000005E-2</v>
       </c>
       <c r="CB9" s="13">
-        <f t="shared" si="8"/>
-        <v>1.6711229946524012E-3</v>
+        <f t="shared" si="14"/>
+        <v>1.0893246187363801E-3</v>
       </c>
       <c r="CC9" s="13">
-        <f t="shared" si="8"/>
-        <v>3.1818181818181822E-2</v>
+        <f t="shared" si="14"/>
+        <v>2.0740740740740744E-2</v>
       </c>
       <c r="CD9" s="13">
-        <f t="shared" si="8"/>
-        <v>3.9772727272727272E-2</v>
+        <f t="shared" si="14"/>
+        <v>4.0229885057471271E-2</v>
       </c>
       <c r="CE9" s="13">
-        <f t="shared" si="8"/>
-        <v>0.19772727272727272</v>
+        <f t="shared" si="14"/>
+        <v>0.2</v>
       </c>
       <c r="CF9" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>8.5227272727272721E-2</v>
       </c>
       <c r="CG9" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.23906250000000001</v>
       </c>
       <c r="CI9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="CJ9" s="14">
-        <f>(BZ11+CD11+BZ28+CD28)/$T$41</f>
-        <v>3.9115665881576105E-2</v>
+        <f t="shared" si="4"/>
+        <v>3.584227715230355E-2</v>
       </c>
       <c r="CK9" s="14">
-        <f>(CA11+CE11+CA28+CE28)/$T$41</f>
-        <v>0.17746268470426985</v>
+        <f t="shared" si="4"/>
+        <v>0.16144494577606605</v>
       </c>
       <c r="CL9" s="14">
-        <f>(CB11+CF11+CB28+CF28)/$T$41</f>
-        <v>0.11020250812541586</v>
+        <f t="shared" si="4"/>
+        <v>0.10932296625395384</v>
       </c>
       <c r="CM9" s="14">
-        <f>(CC11+CG11+CC28+CG28)/$T$41</f>
-        <v>0.29591224935034471</v>
+        <f t="shared" si="4"/>
+        <v>0.28845037627015502</v>
       </c>
       <c r="CO9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="CP9" s="14">
-        <f>CJ9-CM9</f>
-        <v>-0.2567965834687686</v>
+        <f t="shared" si="5"/>
+        <v>-0.25260809911785148</v>
       </c>
       <c r="CQ9" s="14">
-        <f>CK9-CL9</f>
-        <v>6.7260176578853983E-2</v>
-      </c>
-      <c r="CR9" s="56">
-        <f>(CP9+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.10213391263037562</v>
-      </c>
-      <c r="CS9" s="56">
-        <f>(CQ9+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.5539329452730547</v>
+        <f t="shared" si="6"/>
+        <v>5.2121979522112213E-2</v>
+      </c>
+      <c r="CR9" s="97">
+        <f t="shared" si="7"/>
+        <v>7.6348326566344313E-2</v>
+      </c>
+      <c r="CS9" s="55">
+        <f t="shared" si="8"/>
+        <v>0.52735653607068889</v>
       </c>
       <c r="CU9" s="14"/>
       <c r="CW9" s="44">
-        <f>RANK(CR9,$CR$4:$CR$19,0)</f>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="CY9" s="14"/>
@@ -7621,7 +7624,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP10" s="94">
+      <c r="AP10" s="87">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -7663,35 +7666,35 @@
         <v>8</v>
       </c>
       <c r="BE10" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="BF10" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.1864406779661017</v>
       </c>
       <c r="BG10" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH10" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="BI10" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.96784565916398713</v>
       </c>
       <c r="BJ10" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.35028248587570621</v>
       </c>
       <c r="BK10" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="BL10" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL10" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM10" s="48"/>
@@ -7727,78 +7730,78 @@
         <v>6</v>
       </c>
       <c r="BZ10" s="13">
-        <f t="shared" si="9"/>
-        <v>1.6588296760710556E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.0813111962537252E-2</v>
       </c>
       <c r="CA10" s="13">
-        <f t="shared" si="8"/>
-        <v>8.5521159874608163E-2</v>
+        <f t="shared" si="14"/>
+        <v>5.5747126436781612E-2</v>
       </c>
       <c r="CB10" s="13">
-        <f t="shared" si="8"/>
-        <v>6.5308254963427409E-3</v>
+        <f t="shared" si="14"/>
+        <v>4.2571306939123048E-3</v>
       </c>
       <c r="CC10" s="13">
-        <f t="shared" si="8"/>
-        <v>5.2115987460815034E-2</v>
+        <f t="shared" si="14"/>
+        <v>3.3971902937420168E-2</v>
       </c>
       <c r="CD10" s="13">
-        <f t="shared" si="8"/>
-        <v>0.11266094420600856</v>
+        <f t="shared" si="14"/>
+        <v>0.11395589758768683</v>
       </c>
       <c r="CE10" s="13">
-        <f t="shared" si="8"/>
-        <v>0.28560280920795938</v>
+        <f t="shared" si="14"/>
+        <v>0.2888856001183957</v>
       </c>
       <c r="CF10" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>5.3648068669527892E-2</v>
       </c>
       <c r="CG10" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.17864806866952787</v>
       </c>
       <c r="CI10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="CJ10" s="14">
-        <f>(BZ12+CD12+BZ29+CD29)/$T$41</f>
-        <v>1.9607138677731121E-2</v>
+        <f t="shared" si="4"/>
+        <v>1.7676925349317262E-2</v>
       </c>
       <c r="CK10" s="14">
-        <f>(CA12+CE12+CA29+CE29)/$T$41</f>
-        <v>0.23242984644180709</v>
+        <f t="shared" si="4"/>
+        <v>0.21946623505401305</v>
       </c>
       <c r="CL10" s="14">
-        <f>(CB12+CF12+CB29+CF29)/$T$41</f>
-        <v>4.7163470232042738E-2</v>
+        <f t="shared" si="4"/>
+        <v>4.6822269425890808E-2</v>
       </c>
       <c r="CM10" s="14">
-        <f>(CC12+CG12+CC29+CG29)/$T$41</f>
-        <v>0.32584813311976174</v>
+        <f t="shared" si="4"/>
+        <v>0.30881033866580726</v>
       </c>
       <c r="CO10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="CP10" s="14">
-        <f>CJ10-CM10</f>
-        <v>-0.30624099444203062</v>
+        <f t="shared" si="5"/>
+        <v>-0.29113341331649001</v>
       </c>
       <c r="CQ10" s="14">
-        <f>CK10-CL10</f>
-        <v>0.18526637620976436</v>
-      </c>
-      <c r="CR10" s="56">
-        <f>(CP10+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>3.3198652511055866E-2</v>
-      </c>
-      <c r="CS10" s="56">
-        <f>(CQ10+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.71845686025402644</v>
+        <f t="shared" si="6"/>
+        <v>0.17264396562812223</v>
+      </c>
+      <c r="CR10" s="97">
+        <f t="shared" si="7"/>
+        <v>1.9329888954713031E-2</v>
+      </c>
+      <c r="CS10" s="55">
+        <f t="shared" si="8"/>
+        <v>0.70573211816674031</v>
       </c>
       <c r="CU10" s="14"/>
       <c r="CW10" s="44">
-        <f>RANK(CR10,$CR$4:$CR$19,0)</f>
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="CY10" s="14"/>
@@ -7884,7 +7887,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP11" s="94">
+      <c r="AP11" s="87">
         <f t="shared" si="3"/>
         <v>0.66666666666666663</v>
       </c>
@@ -7926,35 +7929,35 @@
         <v>9</v>
       </c>
       <c r="BE11" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.62700964630225076</v>
       </c>
       <c r="BF11" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.14124293785310735</v>
       </c>
       <c r="BG11" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH11" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI11" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="BJ11" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BK11" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="BL11" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL11" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM11" s="48"/>
@@ -7990,79 +7993,79 @@
         <v>8</v>
       </c>
       <c r="BZ11" s="13">
-        <f t="shared" si="9"/>
-        <v>1.8302493966210781E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.1930514585381843E-2</v>
       </c>
       <c r="CA11" s="13">
-        <f t="shared" si="8"/>
-        <v>9.0808527755430413E-2</v>
+        <f t="shared" si="14"/>
+        <v>5.9193706981317595E-2</v>
       </c>
       <c r="CB11" s="13">
-        <f t="shared" si="8"/>
-        <v>3.3521051220166275E-3</v>
+        <f t="shared" si="14"/>
+        <v>2.1850759313886163E-3</v>
       </c>
       <c r="CC11" s="13">
-        <f t="shared" si="8"/>
-        <v>3.5666398498256903E-2</v>
+        <f t="shared" si="14"/>
+        <v>2.3249207909974871E-2</v>
       </c>
       <c r="CD11" s="13">
-        <f t="shared" si="8"/>
-        <v>6.3713592233009694E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.4445932373619008E-2</v>
       </c>
       <c r="CE11" s="13">
-        <f t="shared" si="8"/>
-        <v>0.16416593115622238</v>
+        <f t="shared" si="14"/>
+        <v>0.16605289588215599</v>
       </c>
       <c r="CF11" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.12687555163283318</v>
       </c>
       <c r="CG11" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.26213592233009708</v>
       </c>
       <c r="CI11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="CJ11" s="14">
-        <f>(BZ13+CD13+BZ30+CD30)/$T$41</f>
-        <v>3.8598411865596614E-2</v>
+        <f t="shared" si="4"/>
+        <v>3.6981922691563314E-2</v>
       </c>
       <c r="CK11" s="14">
-        <f>(CA13+CE13+CA30+CE30)/$T$41</f>
-        <v>0.22171401380914385</v>
+        <f t="shared" si="4"/>
+        <v>0.21088595966714566</v>
       </c>
       <c r="CL11" s="14">
-        <f>(CB13+CF13+CB30+CF30)/$T$41</f>
-        <v>0.10984232694189464</v>
+        <f t="shared" si="4"/>
+        <v>0.10722278556435305</v>
       </c>
       <c r="CM11" s="14">
-        <f>(CC13+CG13+CC30+CG30)/$T$41</f>
-        <v>0.35590410979976639</v>
+        <f t="shared" si="4"/>
+        <v>0.33479165506767594</v>
       </c>
       <c r="CO11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="CP11" s="14">
-        <f>CJ11-CM11</f>
-        <v>-0.31730569793416979</v>
+        <f t="shared" si="5"/>
+        <v>-0.29780973237611263</v>
       </c>
       <c r="CQ11" s="14">
-        <f>CK11-CL11</f>
-        <v>0.11187168686724921</v>
-      </c>
-      <c r="CR11" s="56">
-        <f>(CP11+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>1.7772273707873647E-2</v>
-      </c>
-      <c r="CS11" s="56">
-        <f>(CQ11+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.61613018871295067</v>
+        <f t="shared" si="6"/>
+        <v>0.1036631741027926</v>
+      </c>
+      <c r="CR11" s="97">
+        <f t="shared" si="7"/>
+        <v>9.4487681982756856E-3</v>
+      </c>
+      <c r="CS11" s="55">
+        <f t="shared" si="8"/>
+        <v>0.60363880524245672</v>
       </c>
       <c r="CU11" s="14"/>
       <c r="CW11" s="44">
-        <f>RANK(CR11,$CR$4:$CR$19,0)</f>
-        <v>15</v>
+        <f t="shared" si="11"/>
+        <v>14</v>
       </c>
       <c r="CY11" s="14"/>
     </row>
@@ -8147,7 +8150,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP12" s="94">
+      <c r="AP12" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -8189,35 +8192,35 @@
         <v>10</v>
       </c>
       <c r="BE12" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.54019292604501612</v>
       </c>
       <c r="BF12" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.16949152542372881</v>
       </c>
       <c r="BG12" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH12" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="BI12" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="BJ12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.31638418079096048</v>
       </c>
       <c r="BK12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="BL12" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL12" s="56">
+        <f t="shared" si="10"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BM12" s="48"/>
@@ -8253,35 +8256,35 @@
         <v>9</v>
       </c>
       <c r="BZ12" s="13">
-        <f t="shared" si="9"/>
-        <v>1.0888988161715433E-2</v>
+        <f t="shared" si="15"/>
+        <v>7.098007098007098E-3</v>
       </c>
       <c r="CA12" s="13">
-        <f t="shared" si="8"/>
-        <v>7.3123743578289033E-2</v>
+        <f t="shared" si="14"/>
+        <v>4.7665847665847666E-2</v>
       </c>
       <c r="CB12" s="13">
-        <f t="shared" si="8"/>
-        <v>5.5840964931874043E-3</v>
+        <f t="shared" si="14"/>
+        <v>3.640003640003641E-3</v>
       </c>
       <c r="CC12" s="13">
-        <f t="shared" si="8"/>
-        <v>9.0685727049363424E-2</v>
+        <f t="shared" si="14"/>
+        <v>5.9113659113659116E-2</v>
       </c>
       <c r="CD12" s="13">
-        <f t="shared" si="8"/>
-        <v>3.0222437137330752E-2</v>
+        <f t="shared" si="14"/>
+        <v>3.05698214722426E-2</v>
       </c>
       <c r="CE12" s="13">
-        <f t="shared" si="8"/>
-        <v>0.29345122962144232</v>
+        <f t="shared" si="14"/>
+        <v>0.29682423226076926</v>
       </c>
       <c r="CF12" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="CG12" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.17325227963525835</v>
       </c>
       <c r="CI12" s="4" t="s">
@@ -8289,42 +8292,42 @@
       </c>
       <c r="CJ12" s="14">
         <f>(BZ21+CD21+BZ38+CD38)/$T$41</f>
-        <v>1.0563962042403105E-2</v>
+        <v>6.7757939615993761E-3</v>
       </c>
       <c r="CK12" s="14">
-        <f t="shared" ref="CK12:CM12" si="10">(CA21+CE21+CA38+CE38)/$T$41</f>
-        <v>0.26121899048073105</v>
+        <f t="shared" ref="CK12:CM12" si="16">(CA21+CE21+CA38+CE38)/$T$41</f>
+        <v>0.24412937717868033</v>
       </c>
       <c r="CL12" s="14">
-        <f t="shared" si="10"/>
-        <v>6.18651762070156E-2</v>
+        <f t="shared" si="16"/>
+        <v>6.1759562461585316E-2</v>
       </c>
       <c r="CM12" s="14">
-        <f t="shared" si="10"/>
-        <v>0.22356882859369981</v>
+        <f t="shared" si="16"/>
+        <v>0.22188496222198609</v>
       </c>
       <c r="CO12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="CP12" s="14">
-        <f>CJ12-CM12</f>
-        <v>-0.21300486655129669</v>
+        <f t="shared" si="5"/>
+        <v>-0.2151091682603867</v>
       </c>
       <c r="CQ12" s="14">
-        <f>CK12-CL12</f>
-        <v>0.19935381427371546</v>
-      </c>
-      <c r="CR12" s="56">
-        <f>(CP12+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.16318820243494039</v>
-      </c>
-      <c r="CS12" s="56">
-        <f>(CQ12+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.73809752718154686</v>
+        <f t="shared" si="6"/>
+        <v>0.18236981471709501</v>
+      </c>
+      <c r="CR12" s="97">
+        <f t="shared" si="7"/>
+        <v>0.13184769092129592</v>
+      </c>
+      <c r="CS12" s="55">
+        <f t="shared" si="8"/>
+        <v>0.7201266203540666</v>
       </c>
       <c r="CU12" s="14"/>
       <c r="CW12" s="44">
-        <f>RANK(CR12,$CR$4:$CR$19,0)</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="CY12" s="14"/>
@@ -8410,7 +8413,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP13" s="94">
+      <c r="AP13" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -8452,35 +8455,35 @@
         <v>11</v>
       </c>
       <c r="BE13" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.99035369774919613</v>
       </c>
       <c r="BF13" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.3728813559322034</v>
       </c>
       <c r="BG13" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH13" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="BI13" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="BJ13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.63276836158192096</v>
       </c>
       <c r="BK13" s="13">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BL13" s="57">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BL13" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM13" s="48"/>
@@ -8516,35 +8519,35 @@
         <v>10</v>
       </c>
       <c r="BZ13" s="13">
-        <f t="shared" si="9"/>
-        <v>9.1783216783216798E-3</v>
+        <f t="shared" si="15"/>
+        <v>5.9829059829059842E-3</v>
       </c>
       <c r="CA13" s="13">
-        <f t="shared" si="8"/>
-        <v>6.7116477272727279E-2</v>
+        <f t="shared" si="14"/>
+        <v>4.3749999999999997E-2</v>
       </c>
       <c r="CB13" s="13">
-        <f t="shared" si="8"/>
-        <v>1.0380244755244756E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.7663817663817663E-3</v>
       </c>
       <c r="CC13" s="13">
-        <f t="shared" si="8"/>
-        <v>0.109375</v>
+        <f t="shared" si="14"/>
+        <v>7.1296296296296288E-2</v>
       </c>
       <c r="CD13" s="13">
-        <f t="shared" si="8"/>
-        <v>5.8777429467084634E-2</v>
+        <f t="shared" si="14"/>
+        <v>5.9453032104637329E-2</v>
       </c>
       <c r="CE13" s="13">
-        <f t="shared" si="8"/>
-        <v>0.15047021943573669</v>
+        <f t="shared" si="14"/>
+        <v>0.1521997621878716</v>
       </c>
       <c r="CF13" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.1354679802955665</v>
       </c>
       <c r="CG13" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.27155172413793105</v>
       </c>
       <c r="CI13" s="4" t="s">
@@ -8552,42 +8555,42 @@
       </c>
       <c r="CJ13" s="14">
         <f>(BZ14+CD14+BZ31+CD31)/$T$41</f>
-        <v>6.6772606417424954E-2</v>
+        <v>6.2695346712639155E-2</v>
       </c>
       <c r="CK13" s="14">
-        <f t="shared" ref="CK13:CM13" si="11">(CA14+CE14+CA31+CE31)/$T$41</f>
-        <v>0.21870868881477076</v>
+        <f t="shared" ref="CK13:CM13" si="17">(CA14+CE14+CA31+CE31)/$T$41</f>
+        <v>0.2001320578941608</v>
       </c>
       <c r="CL13" s="14">
-        <f t="shared" si="11"/>
-        <v>8.7703240300774019E-2</v>
+        <f t="shared" si="17"/>
+        <v>8.7970901907073393E-2</v>
       </c>
       <c r="CM13" s="14">
-        <f t="shared" si="11"/>
-        <v>0.20269065853734111</v>
+        <f t="shared" si="17"/>
+        <v>0.20229210782842255</v>
       </c>
       <c r="CO13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="CP13" s="14">
-        <f>CJ13-CM13</f>
-        <v>-0.13591805211991614</v>
+        <f t="shared" si="5"/>
+        <v>-0.1395967611157834</v>
       </c>
       <c r="CQ13" s="14">
-        <f>CK13-CL13</f>
-        <v>0.13100544851399676</v>
-      </c>
-      <c r="CR13" s="56">
-        <f>(CP13+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.27066242449556105</v>
-      </c>
-      <c r="CS13" s="56">
-        <f>(CQ13+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.64280642592999171</v>
+        <f t="shared" si="6"/>
+        <v>0.11216115598708741</v>
+      </c>
+      <c r="CR13" s="97">
+        <f t="shared" si="7"/>
+        <v>0.24360795985716413</v>
+      </c>
+      <c r="CS13" s="55">
+        <f t="shared" si="8"/>
+        <v>0.61621603296852046</v>
       </c>
       <c r="CU13" s="14"/>
       <c r="CW13" s="44">
-        <f>RANK(CR13,$CR$4:$CR$19,0)</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="CY13" s="14"/>
@@ -8673,7 +8676,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP14" s="94">
+      <c r="AP14" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -8715,35 +8718,35 @@
         <v>12</v>
       </c>
       <c r="BE14" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BF14" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.12429378531073447</v>
       </c>
       <c r="BG14" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH14" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="BI14" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.97106109324758838</v>
       </c>
       <c r="BJ14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.41807909604519772</v>
       </c>
       <c r="BK14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.61538461538461542</v>
       </c>
-      <c r="BL14" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL14" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM14" s="48"/>
@@ -8779,79 +8782,79 @@
         <v>11</v>
       </c>
       <c r="BZ14" s="13">
-        <f t="shared" si="9"/>
-        <v>2.2292993630573247E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.453172918141071E-2</v>
       </c>
       <c r="CA14" s="13">
-        <f t="shared" si="8"/>
-        <v>0.10129559930515344</v>
+        <f t="shared" si="14"/>
+        <v>6.6029723991507416E-2</v>
       </c>
       <c r="CB14" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="CC14" s="13">
-        <f t="shared" si="8"/>
-        <v>3.0399536768963564E-3</v>
+        <f t="shared" si="14"/>
+        <v>1.9815994338287361E-3</v>
       </c>
       <c r="CD14" s="13">
-        <f t="shared" si="8"/>
-        <v>0.11771300448430491</v>
+        <f t="shared" si="14"/>
+        <v>0.1190660275243544</v>
       </c>
       <c r="CE14" s="13">
-        <f t="shared" si="8"/>
-        <v>0.27395026498165509</v>
+        <f t="shared" si="14"/>
+        <v>0.27709911860213393</v>
       </c>
       <c r="CF14" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>6.6245413779046053E-2</v>
       </c>
       <c r="CG14" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.18665919282511212</v>
       </c>
       <c r="CI14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="CJ14" s="14">
-        <f t="shared" ref="CJ14:CJ19" si="12">(BZ15+CD15+BZ32+CD32)/$T$41</f>
-        <v>2.3355107365270262E-2</v>
+        <f t="shared" ref="CJ14:CJ19" si="18">(BZ15+CD15+BZ32+CD32)/$T$41</f>
+        <v>2.3339988800372562E-2</v>
       </c>
       <c r="CK14" s="14">
-        <f t="shared" ref="CK14:CK19" si="13">(CA15+CE15+CA32+CE32)/$T$41</f>
-        <v>0.2727748303646883</v>
+        <f t="shared" ref="CK14:CK19" si="19">(CA15+CE15+CA32+CE32)/$T$41</f>
+        <v>0.26536637403481772</v>
       </c>
       <c r="CL14" s="14">
-        <f t="shared" ref="CL14:CL19" si="14">(CB15+CF15+CB32+CF32)/$T$41</f>
-        <v>6.323376589049387E-2</v>
+        <f t="shared" ref="CL14:CL19" si="20">(CB15+CF15+CB32+CF32)/$T$41</f>
+        <v>6.2355973018900147E-2</v>
       </c>
       <c r="CM14" s="14">
-        <f t="shared" ref="CM14:CM19" si="15">(CC15+CG15+CC32+CG32)/$T$41</f>
-        <v>0.3534081221822718</v>
+        <f t="shared" ref="CM14:CM19" si="21">(CC15+CG15+CC32+CG32)/$T$41</f>
+        <v>0.32341137890436455</v>
       </c>
       <c r="CO14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="CP14" s="14">
-        <f>CJ14-CM14</f>
-        <v>-0.33005301481700156</v>
+        <f t="shared" si="5"/>
+        <v>-0.30007139010399198</v>
       </c>
       <c r="CQ14" s="14">
-        <f>CK14-CL14</f>
-        <v>0.20954106447419443</v>
-      </c>
-      <c r="CR14" s="56">
-        <f>(CP14+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0</v>
-      </c>
-      <c r="CS14" s="56">
-        <f>(CQ14+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.75230056304843929</v>
+        <f t="shared" si="6"/>
+        <v>0.20301040101591758</v>
+      </c>
+      <c r="CR14" s="97">
+        <f t="shared" si="7"/>
+        <v>6.1014576639333287E-3</v>
+      </c>
+      <c r="CS14" s="55">
+        <f t="shared" si="8"/>
+        <v>0.75067520916190289</v>
       </c>
       <c r="CU14" s="14"/>
       <c r="CW14" s="44">
-        <f>RANK(CR14,$CR$4:$CR$19,0)</f>
-        <v>16</v>
+        <f t="shared" si="11"/>
+        <v>15</v>
       </c>
       <c r="CY14" s="14"/>
     </row>
@@ -8936,7 +8939,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="94">
+      <c r="AP15" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -8978,35 +8981,35 @@
         <v>13</v>
       </c>
       <c r="BE15" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="BF15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.30508474576271188</v>
       </c>
       <c r="BG15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="BI15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.977491961414791</v>
       </c>
       <c r="BJ15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.65536723163841804</v>
       </c>
       <c r="BK15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="BL15" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL15" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM15" s="48"/>
@@ -9042,78 +9045,78 @@
         <v>12</v>
       </c>
       <c r="BZ15" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="CA15" s="13">
-        <f t="shared" si="8"/>
-        <v>5.0385585051164174E-2</v>
+        <f t="shared" si="14"/>
+        <v>3.2843936922240344E-2</v>
       </c>
       <c r="CB15" s="13">
-        <f t="shared" si="8"/>
-        <v>1.668396855998816E-3</v>
+        <f t="shared" si="14"/>
+        <v>1.0875475802066355E-3</v>
       </c>
       <c r="CC15" s="13">
-        <f t="shared" si="8"/>
-        <v>0.16142666468930744</v>
+        <f t="shared" si="14"/>
+        <v>0.10522627031599299</v>
       </c>
       <c r="CD15" s="13">
-        <f t="shared" si="8"/>
-        <v>3.8209606986899562E-2</v>
+        <f t="shared" si="14"/>
+        <v>3.8648797871806459E-2</v>
       </c>
       <c r="CE15" s="13">
-        <f t="shared" si="8"/>
-        <v>0.17626042080190549</v>
+        <f t="shared" si="14"/>
+        <v>0.17828640265020326</v>
       </c>
       <c r="CF15" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.10222310440651053</v>
       </c>
       <c r="CG15" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.25382096069868998</v>
       </c>
       <c r="CI15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="CJ15" s="14">
-        <f t="shared" si="12"/>
-        <v>5.2593347726325561E-2</v>
+        <f t="shared" si="18"/>
+        <v>4.8900316315706252E-2</v>
       </c>
       <c r="CK15" s="14">
-        <f t="shared" si="13"/>
-        <v>0.2353051564484388</v>
+        <f t="shared" si="19"/>
+        <v>0.21840966420158983</v>
       </c>
       <c r="CL15" s="14">
-        <f t="shared" si="14"/>
-        <v>7.3336188437251565E-2</v>
+        <f t="shared" si="20"/>
+        <v>7.3086808973700138E-2</v>
       </c>
       <c r="CM15" s="14">
-        <f t="shared" si="15"/>
-        <v>0.2729906596753105</v>
+        <f t="shared" si="21"/>
+        <v>0.2684072067113118</v>
       </c>
       <c r="CO15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="CP15" s="14">
-        <f>CJ15-CM15</f>
-        <v>-0.22039731194898493</v>
+        <f t="shared" si="5"/>
+        <v>-0.21950689039560556</v>
       </c>
       <c r="CQ15" s="14">
-        <f>CK15-CL15</f>
-        <v>0.16196896801118724</v>
-      </c>
-      <c r="CR15" s="56">
-        <f>(CP15+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.15288167564300262</v>
-      </c>
-      <c r="CS15" s="56">
-        <f>(CQ15+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.68597567860655229</v>
+        <f t="shared" si="6"/>
+        <v>0.14532285522788968</v>
+      </c>
+      <c r="CR15" s="97">
+        <f t="shared" si="7"/>
+        <v>0.12533895113769858</v>
+      </c>
+      <c r="CS15" s="55">
+        <f t="shared" si="8"/>
+        <v>0.6652961850344622</v>
       </c>
       <c r="CU15" s="14"/>
       <c r="CW15" s="44">
-        <f>RANK(CR15,$CR$4:$CR$19,0)</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="CY15" s="14"/>
@@ -9199,7 +9202,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP16" s="94">
+      <c r="AP16" s="87">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -9241,35 +9244,35 @@
         <v>14</v>
       </c>
       <c r="BE16" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.80064308681672025</v>
       </c>
       <c r="BF16" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.2824858757062147</v>
       </c>
       <c r="BG16" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH16" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="BI16" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.932475884244373</v>
       </c>
       <c r="BJ16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.50847457627118642</v>
       </c>
       <c r="BK16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="BL16" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL16" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM16" s="48"/>
@@ -9305,78 +9308,78 @@
         <v>13</v>
       </c>
       <c r="BZ16" s="13">
-        <f t="shared" si="9"/>
-        <v>2.0412457912457913E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.3305898491083677E-2</v>
       </c>
       <c r="CA16" s="13">
-        <f t="shared" si="8"/>
-        <v>9.5959595959595967E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.2551440329218097E-2</v>
       </c>
       <c r="CB16" s="13">
-        <f t="shared" si="8"/>
-        <v>2.4551066217732877E-3</v>
+        <f t="shared" si="14"/>
+        <v>1.6003657978966616E-3</v>
       </c>
       <c r="CC16" s="13">
-        <f t="shared" si="8"/>
-        <v>1.9640852974186315E-2</v>
+        <f t="shared" si="14"/>
+        <v>1.2802926383173301E-2</v>
       </c>
       <c r="CD16" s="13">
-        <f t="shared" si="8"/>
-        <v>8.9863065804488412E-2</v>
+        <f t="shared" si="14"/>
+        <v>9.0895974606838861E-2</v>
       </c>
       <c r="CE16" s="13">
-        <f t="shared" si="8"/>
-        <v>0.2647394446557626</v>
+        <f t="shared" si="14"/>
+        <v>0.26778242677824265</v>
       </c>
       <c r="CF16" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>5.8006846709775593E-2</v>
       </c>
       <c r="CG16" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.19299163179916318</v>
       </c>
       <c r="CI16" s="4" t="s">
         <v>14</v>
       </c>
       <c r="CJ16" s="14">
-        <f t="shared" si="12"/>
-        <v>5.1374164519705029E-2</v>
+        <f t="shared" si="18"/>
+        <v>4.8418601751123079E-2</v>
       </c>
       <c r="CK16" s="14">
-        <f t="shared" si="13"/>
-        <v>0.18543227431497858</v>
+        <f t="shared" si="19"/>
+        <v>0.17031768694321917</v>
       </c>
       <c r="CL16" s="14">
-        <f t="shared" si="14"/>
-        <v>9.8642981580555664E-2</v>
+        <f t="shared" si="20"/>
+        <v>9.7503786837757123E-2</v>
       </c>
       <c r="CM16" s="14">
-        <f t="shared" si="15"/>
-        <v>0.31894935660390461</v>
+        <f t="shared" si="21"/>
+        <v>0.30790420743641789</v>
       </c>
       <c r="CO16" s="4" t="s">
         <v>14</v>
       </c>
       <c r="CP16" s="14">
-        <f>CJ16-CM16</f>
-        <v>-0.26757519208419955</v>
+        <f t="shared" si="5"/>
+        <v>-0.25948560568529483</v>
       </c>
       <c r="CQ16" s="14">
-        <f>CK16-CL16</f>
-        <v>8.6789292734422915E-2</v>
-      </c>
-      <c r="CR16" s="56">
-        <f>(CP16+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>8.7106406507775055E-2</v>
-      </c>
-      <c r="CS16" s="56">
-        <f>(CQ16+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.58116038464557684</v>
+        <f t="shared" si="6"/>
+        <v>7.2813900105462043E-2</v>
+      </c>
+      <c r="CR16" s="97">
+        <f t="shared" si="7"/>
+        <v>6.6169443219217416E-2</v>
+      </c>
+      <c r="CS16" s="55">
+        <f t="shared" si="8"/>
+        <v>0.55798110091559416</v>
       </c>
       <c r="CU16" s="14"/>
       <c r="CW16" s="44">
-        <f>RANK(CR16,$CR$4:$CR$19,0)</f>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="CY16" s="14"/>
@@ -9462,7 +9465,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP17" s="94">
+      <c r="AP17" s="87">
         <f t="shared" si="3"/>
         <v>0.66666666666666663</v>
       </c>
@@ -9504,35 +9507,35 @@
         <v>15</v>
       </c>
       <c r="BE17" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.96784565916398713</v>
       </c>
       <c r="BF17" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.10169491525423729</v>
       </c>
       <c r="BG17" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH17" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI17" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.99035369774919613</v>
       </c>
       <c r="BJ17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.42372881355932202</v>
       </c>
       <c r="BK17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="BL17" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL17" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM17" s="48"/>
@@ -9568,79 +9571,79 @@
         <v>14</v>
       </c>
       <c r="BZ17" s="13">
-        <f t="shared" si="9"/>
-        <v>1.6076962809917356E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.047979797979798E-2</v>
       </c>
       <c r="CA17" s="13">
-        <f t="shared" si="8"/>
-        <v>8.4258780991735546E-2</v>
+        <f t="shared" si="14"/>
+        <v>5.4924242424242424E-2</v>
       </c>
       <c r="CB17" s="13">
-        <f t="shared" si="8"/>
-        <v>6.7794421487603288E-3</v>
+        <f t="shared" si="14"/>
+        <v>4.4191919191919182E-3</v>
       </c>
       <c r="CC17" s="13">
-        <f t="shared" si="8"/>
-        <v>5.6043388429752067E-2</v>
+        <f t="shared" si="14"/>
+        <v>3.6531986531986534E-2</v>
       </c>
       <c r="CD17" s="13">
-        <f t="shared" si="8"/>
-        <v>9.1642228739002934E-2</v>
+        <f t="shared" si="14"/>
+        <v>9.2695587690025963E-2</v>
       </c>
       <c r="CE17" s="13">
-        <f t="shared" si="8"/>
-        <v>0.22622538751571009</v>
+        <f t="shared" si="14"/>
+        <v>0.22882567932623551</v>
       </c>
       <c r="CF17" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>9.1118558860494345E-2</v>
       </c>
       <c r="CG17" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.21947004608294932</v>
       </c>
       <c r="CI17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="CJ17" s="14">
-        <f t="shared" si="12"/>
-        <v>2.4851078570602599E-2</v>
+        <f>(BZ18+CD18+BZ35+CD35)/$T$41</f>
+        <v>2.11032013224015E-2</v>
       </c>
       <c r="CK17" s="14">
-        <f t="shared" si="13"/>
-        <v>0.20086776707418552</v>
+        <f t="shared" si="19"/>
+        <v>0.18353310854229721</v>
       </c>
       <c r="CL17" s="14">
-        <f t="shared" si="14"/>
-        <v>9.225953891339303E-2</v>
+        <f t="shared" si="20"/>
+        <v>9.1932895470408699E-2</v>
       </c>
       <c r="CM17" s="14">
-        <f t="shared" si="15"/>
-        <v>0.26303671041087506</v>
+        <f t="shared" si="21"/>
+        <v>0.26018695394060715</v>
       </c>
       <c r="CO17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="CP17" s="14">
-        <f>CJ17-CM17</f>
-        <v>-0.23818563184027247</v>
+        <f t="shared" si="5"/>
+        <v>-0.23908375261820564</v>
       </c>
       <c r="CQ17" s="14">
-        <f>CK17-CL17</f>
-        <v>0.10860822816079249</v>
-      </c>
-      <c r="CR17" s="56">
-        <f>(CP17+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.12808124957554093</v>
-      </c>
-      <c r="CS17" s="56">
-        <f>(CQ17+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.6115802836702976</v>
+        <f t="shared" si="6"/>
+        <v>9.1600213071888509E-2</v>
+      </c>
+      <c r="CR17" s="116">
+        <f t="shared" si="7"/>
+        <v>9.6364700817106227E-2</v>
+      </c>
+      <c r="CS17" s="55">
+        <f t="shared" si="8"/>
+        <v>0.58578531837909842</v>
       </c>
       <c r="CU17" s="14"/>
       <c r="CW17" s="44">
-        <f>RANK(CR17,$CR$4:$CR$19,0)</f>
-        <v>6</v>
+        <f t="shared" si="11"/>
+        <v>7</v>
       </c>
       <c r="CY17" s="14"/>
     </row>
@@ -9725,7 +9728,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP18" s="94">
+      <c r="AP18" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -9767,35 +9770,35 @@
         <v>16</v>
       </c>
       <c r="BE18" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.57234726688102899</v>
       </c>
       <c r="BF18" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.19209039548022599</v>
       </c>
       <c r="BG18" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="BH18" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI18" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="BJ18" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.48022598870056499</v>
       </c>
       <c r="BK18" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.57692307692307687</v>
       </c>
-      <c r="BL18" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL18" s="56">
+        <f t="shared" si="10"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BM18" s="48"/>
@@ -9831,87 +9834,87 @@
         <v>15</v>
       </c>
       <c r="BZ18" s="13">
-        <f t="shared" si="9"/>
-        <v>2.1512292738707833E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.4022827859305847E-2</v>
       </c>
       <c r="CA18" s="13">
-        <f t="shared" si="8"/>
-        <v>9.9056603773584911E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.4570230607966461E-2</v>
       </c>
       <c r="CB18" s="13">
-        <f t="shared" si="8"/>
-        <v>1.0720411663807906E-3</v>
+        <f t="shared" si="14"/>
+        <v>6.9881201956673749E-4</v>
       </c>
       <c r="CC18" s="13">
-        <f t="shared" si="8"/>
-        <v>1.0005717552887369E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.5222455159562103E-3</v>
       </c>
       <c r="CD18" s="13">
-        <f t="shared" si="8"/>
-        <v>3.0594405594405596E-2</v>
+        <f t="shared" si="14"/>
+        <v>3.0946065428824051E-2</v>
       </c>
       <c r="CE18" s="13">
-        <f t="shared" si="8"/>
-        <v>0.17482517482517479</v>
+        <f t="shared" si="14"/>
+        <v>0.17683465959328026</v>
       </c>
       <c r="CF18" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>9.9067599067599071E-2</v>
       </c>
       <c r="CG18" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.25480769230769229</v>
       </c>
       <c r="CI18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="CJ18" s="14">
-        <f t="shared" si="12"/>
-        <v>3.8299027374296746E-2</v>
+        <f t="shared" si="18"/>
+        <v>3.6534137729157382E-2</v>
       </c>
       <c r="CK18" s="14">
-        <f t="shared" si="13"/>
-        <v>0.28393448739213639</v>
+        <f t="shared" si="19"/>
+        <v>0.27332396575408319</v>
       </c>
       <c r="CL18" s="14">
-        <f t="shared" si="14"/>
-        <v>7.417581228088567E-2</v>
+        <f t="shared" si="20"/>
+        <v>7.1709592149002715E-2</v>
       </c>
       <c r="CM18" s="14">
-        <f t="shared" si="15"/>
-        <v>0.34379893126345851</v>
+        <f t="shared" si="21"/>
+        <v>0.32335167096206724</v>
       </c>
       <c r="CO18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="CP18" s="14">
-        <f>CJ18-CM18</f>
-        <v>-0.30549990388916176</v>
+        <f t="shared" si="5"/>
+        <v>-0.28681753323290987</v>
       </c>
       <c r="CQ18" s="14">
-        <f>CK18-CL18</f>
-        <v>0.20975867511125074</v>
-      </c>
-      <c r="CR18" s="56">
-        <f>(CP18+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>3.4231878896574176E-2</v>
-      </c>
-      <c r="CS18" s="56">
-        <f>(CQ18+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.75260395519276724</v>
+        <f t="shared" si="6"/>
+        <v>0.20161437360508047</v>
+      </c>
+      <c r="CR18" s="97">
+        <f t="shared" si="7"/>
+        <v>2.5717500435727056E-2</v>
+      </c>
+      <c r="CS18" s="55">
+        <f t="shared" si="8"/>
+        <v>0.74860905335020655</v>
       </c>
       <c r="CU18" s="14"/>
       <c r="CW18" s="44">
-        <f>RANK(CR18,$CR$4:$CR$19,0)</f>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="CY18" s="14"/>
     </row>
     <row r="19" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="73" t="s">
+      <c r="B19" s="66" t="s">
         <v>21</v>
       </c>
       <c r="C19" s="27">
@@ -9973,22 +9976,22 @@
         <v>9</v>
       </c>
       <c r="AD19" s="19"/>
-      <c r="AL19" s="87" t="s">
+      <c r="AL19" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="AM19" s="98">
+      <c r="AM19" s="91">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AN19" s="99">
+      <c r="AN19" s="92">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO19" s="99">
+      <c r="AO19" s="92">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP19" s="100">
+      <c r="AP19" s="93">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10030,35 +10033,35 @@
         <v>17</v>
       </c>
       <c r="BE19" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>0.91639871382636651</v>
       </c>
       <c r="BF19" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5.0847457627118647E-2</v>
       </c>
       <c r="BG19" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH19" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="BI19" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.98713826366559487</v>
       </c>
       <c r="BJ19" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0.29943502824858759</v>
       </c>
       <c r="BK19" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="BL19" s="57">
-        <f t="shared" si="5"/>
+      <c r="BL19" s="56">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM19" s="48"/>
@@ -10094,78 +10097,78 @@
         <v>16</v>
       </c>
       <c r="BZ19" s="13">
-        <f t="shared" si="9"/>
-        <v>9.9641737572772077E-3</v>
+        <f t="shared" si="15"/>
+        <v>6.4951651158547726E-3</v>
       </c>
       <c r="CA19" s="13">
-        <f t="shared" si="8"/>
-        <v>6.8769592476489047E-2</v>
+        <f t="shared" si="14"/>
+        <v>4.4827586206896558E-2</v>
       </c>
       <c r="CB19" s="13">
-        <f t="shared" si="8"/>
-        <v>1.0635915808329602E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.9330414158000368E-3</v>
       </c>
       <c r="CC19" s="13">
-        <f t="shared" si="8"/>
-        <v>0.10423197492163008</v>
+        <f t="shared" si="14"/>
+        <v>6.7943805874840349E-2</v>
       </c>
       <c r="CD19" s="13">
-        <f t="shared" si="8"/>
-        <v>5.9310207336523132E-2</v>
+        <f t="shared" si="14"/>
+        <v>5.9991933857632594E-2</v>
       </c>
       <c r="CE19" s="13">
-        <f t="shared" si="8"/>
-        <v>0.20334928229665072</v>
+        <f t="shared" si="14"/>
+        <v>0.20568663036902604</v>
       </c>
       <c r="CF19" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>9.1706539074960139E-2</v>
       </c>
       <c r="CG19" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.23519736842105265</v>
       </c>
       <c r="CI19" s="4" t="s">
         <v>17</v>
       </c>
       <c r="CJ19" s="14">
-        <f t="shared" si="12"/>
-        <v>1.7001631730252115E-2</v>
+        <f t="shared" si="18"/>
+        <v>1.3638605468025816E-2</v>
       </c>
       <c r="CK19" s="14">
-        <f t="shared" si="13"/>
-        <v>0.15338064305945073</v>
+        <f t="shared" si="19"/>
+        <v>0.13662648683168521</v>
       </c>
       <c r="CL19" s="14">
-        <f t="shared" si="14"/>
-        <v>0.11342129139212108</v>
+        <f t="shared" si="20"/>
+        <v>0.11292990140480394</v>
       </c>
       <c r="CM19" s="14">
-        <f t="shared" si="15"/>
-        <v>0.29199744956499563</v>
+        <f t="shared" si="21"/>
+        <v>0.28648171194313482</v>
       </c>
       <c r="CO19" s="4" t="s">
         <v>17</v>
       </c>
       <c r="CP19" s="14">
-        <f>CJ19-CM19</f>
-        <v>-0.27499581783474353</v>
+        <f t="shared" si="5"/>
+        <v>-0.27284310647510901</v>
       </c>
       <c r="CQ19" s="14">
-        <f>CK19-CL19</f>
-        <v>3.9959351667329654E-2</v>
-      </c>
-      <c r="CR19" s="56">
-        <f>(CP19+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>7.6760590746343546E-2</v>
-      </c>
-      <c r="CS19" s="56">
-        <f>(CQ19+$CP$21)/($CP$21+$CQ$21)</f>
-        <v>0.51587021119041687</v>
+        <f t="shared" si="6"/>
+        <v>2.3696585426881273E-2</v>
+      </c>
+      <c r="CR19" s="97">
+        <f t="shared" si="7"/>
+        <v>4.6400004831139305E-2</v>
+      </c>
+      <c r="CS19" s="55">
+        <f t="shared" si="8"/>
+        <v>0.4852862351914235</v>
       </c>
       <c r="CU19" s="14"/>
       <c r="CW19" s="44">
-        <f>RANK(CR19,$CR$4:$CR$19,0)</f>
+        <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="CY19" s="14"/>
@@ -10227,19 +10230,19 @@
       <c r="AL20" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AM20" s="91">
+      <c r="AM20" s="84">
         <f t="shared" si="0"/>
         <v>0.98713826366559487</v>
       </c>
-      <c r="AN20" s="92">
+      <c r="AN20" s="85">
         <f t="shared" si="1"/>
         <v>0.24293785310734464</v>
       </c>
-      <c r="AO20" s="92">
+      <c r="AO20" s="85">
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP20" s="93">
+      <c r="AP20" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10277,39 +10280,39 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="BC20" s="48"/>
-      <c r="BD20" s="64" t="s">
+      <c r="BD20" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="BE20" s="65">
-        <f t="shared" si="6"/>
+      <c r="BE20" s="63">
+        <f t="shared" si="12"/>
         <v>0.98713826366559487</v>
       </c>
-      <c r="BF20" s="65">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BG20" s="65">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BH20" s="65">
-        <f t="shared" si="4"/>
+      <c r="BF20" s="63">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BG20" s="63">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BH20" s="63">
+        <f t="shared" si="9"/>
         <v>0.88888888888888884</v>
       </c>
-      <c r="BI20" s="65">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="BJ20" s="65">
-        <f t="shared" si="5"/>
+      <c r="BI20" s="63">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="BJ20" s="63">
+        <f t="shared" si="10"/>
         <v>0.5423728813559322</v>
       </c>
-      <c r="BK20" s="65">
-        <f t="shared" si="5"/>
+      <c r="BK20" s="63">
+        <f t="shared" si="10"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="BL20" s="66">
-        <f t="shared" si="5"/>
+      <c r="BL20" s="64">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="BM20" s="48"/>
@@ -10345,35 +10348,35 @@
         <v>17</v>
       </c>
       <c r="BZ20" s="13">
-        <f t="shared" si="9"/>
-        <v>1.9451269451269449E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.2679346012679343E-2</v>
       </c>
       <c r="CA20" s="13">
-        <f t="shared" si="8"/>
-        <v>9.4287469287469283E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.1461461461461454E-2</v>
       </c>
       <c r="CB20" s="13">
-        <f t="shared" si="8"/>
-        <v>1.3650013650013627E-3</v>
+        <f t="shared" si="14"/>
+        <v>8.8977866755644386E-4</v>
       </c>
       <c r="CC20" s="13">
-        <f t="shared" si="8"/>
-        <v>2.4843024843024853E-2</v>
+        <f t="shared" si="14"/>
+        <v>1.619397174952731E-2</v>
       </c>
       <c r="CD20" s="13">
-        <f t="shared" si="8"/>
-        <v>1.6197038255861787E-2</v>
+        <f t="shared" si="14"/>
+        <v>1.6383211109377443E-2</v>
       </c>
       <c r="CE20" s="13">
-        <f t="shared" si="8"/>
-        <v>0.13081036610448377</v>
+        <f t="shared" si="14"/>
+        <v>0.13231393353097209</v>
       </c>
       <c r="CF20" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.12751953928424517</v>
       </c>
       <c r="CG20" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.28506787330316746</v>
       </c>
       <c r="CR20" s="13"/>
@@ -10450,7 +10453,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP21" s="94">
+      <c r="AP21" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10488,21 +10491,21 @@
         <v>0</v>
       </c>
       <c r="BC21" s="48"/>
-      <c r="BD21" s="111" t="s">
+      <c r="BD21" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="BE21" s="113" t="s">
+      <c r="BE21" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="BF21" s="113"/>
-      <c r="BG21" s="113"/>
-      <c r="BH21" s="113"/>
-      <c r="BI21" s="113" t="s">
+      <c r="BF21" s="109"/>
+      <c r="BG21" s="109"/>
+      <c r="BH21" s="109"/>
+      <c r="BI21" s="109" t="s">
         <v>112</v>
       </c>
-      <c r="BJ21" s="113"/>
-      <c r="BK21" s="113"/>
-      <c r="BL21" s="114"/>
+      <c r="BJ21" s="109"/>
+      <c r="BK21" s="109"/>
+      <c r="BL21" s="110"/>
       <c r="BM21" s="48"/>
       <c r="BN21" s="48"/>
       <c r="BO21" s="4" t="s">
@@ -10536,44 +10539,44 @@
         <v>21</v>
       </c>
       <c r="BZ21" s="13">
-        <f t="shared" si="9"/>
-        <v>2.2150072150072152E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.4438565549676662E-2</v>
       </c>
       <c r="CA21" s="13">
-        <f t="shared" si="8"/>
-        <v>0.10097402597402599</v>
+        <f t="shared" si="14"/>
+        <v>6.5820105820105834E-2</v>
       </c>
       <c r="CB21" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="CC21" s="13">
-        <f t="shared" si="8"/>
-        <v>4.0404040404040352E-3</v>
+        <f t="shared" si="14"/>
+        <v>2.6337448559670749E-3</v>
       </c>
       <c r="CD21" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="CE21" s="13">
-        <f t="shared" si="8"/>
-        <v>0.19180819180819181</v>
+        <f t="shared" si="14"/>
+        <v>0.19401288366805611</v>
       </c>
       <c r="CF21" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>6.7432567432567425E-2</v>
       </c>
       <c r="CG21" s="13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>0.24313186813186816</v>
       </c>
       <c r="CP21" s="13">
         <f>ABS(MIN(CP4:CP19))</f>
-        <v>0.33005301481700156</v>
+        <v>0.3041939263119075</v>
       </c>
       <c r="CQ21" s="13">
         <f>MAX(CQ4:CQ19)</f>
-        <v>0.38720562593780067</v>
+        <v>0.37147022395901624</v>
       </c>
     </row>
     <row r="22" spans="1:103" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10663,7 +10666,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP22" s="94">
+      <c r="AP22" s="87">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -10701,7 +10704,7 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="BC22" s="48"/>
-      <c r="BD22" s="112"/>
+      <c r="BD22" s="108"/>
       <c r="BE22" s="50" t="s">
         <v>64</v>
       </c>
@@ -10756,28 +10759,28 @@
         <v>0.64835164835164838</v>
       </c>
       <c r="BY22" s="41"/>
-      <c r="BZ22" s="60" t="s">
+      <c r="BZ22" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="CA22" s="60" t="s">
+      <c r="CA22" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="CB22" s="60" t="s">
+      <c r="CB22" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="CC22" s="60" t="s">
+      <c r="CC22" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="CD22" s="60" t="s">
+      <c r="CD22" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="CE22" s="60" t="s">
+      <c r="CE22" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="CF22" s="60" t="s">
+      <c r="CF22" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="CG22" s="60" t="s">
+      <c r="CG22" s="59" t="s">
         <v>116</v>
       </c>
     </row>
@@ -10834,7 +10837,7 @@
         <v>1</v>
       </c>
       <c r="T23" s="18" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="U23">
         <f>MIN(U9:U14)</f>
@@ -10868,7 +10871,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP23" s="94">
+      <c r="AP23" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10910,89 +10913,89 @@
         <v>1</v>
       </c>
       <c r="BE23" s="13">
-        <f t="shared" ref="BE23:BH38" si="16">BE5/(BI5+1-BE5)</f>
+        <f t="shared" ref="BE23:BH38" si="22">BE5/(BI5+1-BE5)</f>
         <v>0.37028824833702878</v>
       </c>
       <c r="BF23" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.126984126984127</v>
       </c>
       <c r="BG23" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>3.2258064516129031E-2</v>
       </c>
       <c r="BH23" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.49999999999999989</v>
       </c>
       <c r="BI23" s="13">
-        <f t="shared" ref="BI23:BL38" si="17">BI5/(BI5+1-BE5)</f>
+        <f t="shared" ref="BI23:BL38" si="23">BI5/(BI5+1-BE5)</f>
         <v>0.68070953436807091</v>
       </c>
       <c r="BJ23" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.42460317460317465</v>
       </c>
       <c r="BK23" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.19354838709677422</v>
       </c>
-      <c r="BL23" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL23" s="56">
+        <f t="shared" si="23"/>
         <v>0.74999999999999989</v>
       </c>
       <c r="BM23" s="48"/>
       <c r="BN23" s="48"/>
       <c r="BO23" s="41"/>
-      <c r="BP23" s="108" t="s">
+      <c r="BP23" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="BQ23" s="108"/>
-      <c r="BR23" s="108" t="s">
+      <c r="BQ23" s="104"/>
+      <c r="BR23" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="BS23" s="108"/>
-      <c r="BT23" s="108" t="s">
+      <c r="BS23" s="104"/>
+      <c r="BT23" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="BU23" s="108"/>
-      <c r="BV23" s="108" t="s">
+      <c r="BU23" s="104"/>
+      <c r="BV23" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="BW23" s="108"/>
+      <c r="BW23" s="104"/>
       <c r="BY23" s="4" t="s">
         <v>1</v>
       </c>
       <c r="BZ23" s="13">
-        <f t="shared" ref="BZ23:CG38" si="18">BP27*BP$24</f>
-        <v>1.4231499051233387E-2</v>
+        <f t="shared" ref="BZ23:CG38" si="24">BP27*BP$24</f>
+        <v>1.4662756598240468E-2</v>
       </c>
       <c r="CA23" s="13">
-        <f t="shared" si="18"/>
-        <v>0.14800759013282733</v>
+        <f t="shared" si="24"/>
+        <v>0.15249266862170088</v>
       </c>
       <c r="CB23" s="13">
-        <f t="shared" si="18"/>
-        <v>7.5901328273244778E-2</v>
+        <f t="shared" si="24"/>
+        <v>7.8201368523949169E-2</v>
       </c>
       <c r="CC23" s="13">
-        <f t="shared" si="18"/>
-        <v>0.18975332068311196</v>
+        <f t="shared" si="24"/>
+        <v>0.19550342130987294</v>
       </c>
       <c r="CD23" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE23" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6.2499999999999986E-2</v>
       </c>
       <c r="CF23" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG23" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0.10416666666666667</v>
       </c>
     </row>
@@ -11049,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="T24" s="18" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="U24">
         <f>MIN(U15:U19)</f>
@@ -11083,7 +11086,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP24" s="94">
+      <c r="AP24" s="87">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11125,97 +11128,105 @@
         <v>2</v>
       </c>
       <c r="BE24" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.9872204472843451</v>
       </c>
       <c r="BF24" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>7.3578595317725759E-2</v>
       </c>
       <c r="BG24" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.04</v>
       </c>
       <c r="BH24" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.79999999999999993</v>
       </c>
       <c r="BI24" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.99361022364217255</v>
       </c>
       <c r="BJ24" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.48160535117056857</v>
       </c>
       <c r="BK24" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.52</v>
       </c>
-      <c r="BL24" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL24" s="56">
+        <f t="shared" si="23"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="BM24" s="48"/>
       <c r="BN24" s="48"/>
       <c r="BO24" s="33"/>
-      <c r="BP24" s="55">
-        <v>0.441176470588235</v>
-      </c>
-      <c r="BQ24" s="55">
-        <v>0.76470588235294112</v>
-      </c>
-      <c r="BR24" s="55">
-        <v>0.11764705882352941</v>
-      </c>
-      <c r="BS24" s="55">
-        <v>0.23529411764705882</v>
-      </c>
-      <c r="BT24" s="55">
-        <v>0</v>
-      </c>
-      <c r="BU24" s="55">
+      <c r="BP24" s="54">
+        <f>W35</f>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="BQ24" s="54">
+        <f>W36</f>
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="BR24" s="54">
+        <f>W37</f>
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="BS24" s="54">
+        <f>W38</f>
+        <v>0.24242424242424243</v>
+      </c>
+      <c r="BT24" s="54">
+        <f>X35</f>
+        <v>0</v>
+      </c>
+      <c r="BU24" s="54">
+        <f>X36</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="BV24" s="55">
+      <c r="BV24" s="54">
+        <f>X37</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="BW24" s="55">
+      <c r="BW24" s="54">
+        <f>X38</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="BY24" s="4" t="s">
         <v>2</v>
       </c>
       <c r="BZ24" s="13">
-        <f t="shared" si="18"/>
-        <v>1.7647058823529401E-2</v>
+        <f t="shared" si="24"/>
+        <v>1.8181818181818181E-2</v>
       </c>
       <c r="CA24" s="13">
-        <f t="shared" si="18"/>
-        <v>0.39764705882352941</v>
+        <f t="shared" si="24"/>
+        <v>0.40969696969696967</v>
       </c>
       <c r="CB24" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CC24" s="13">
-        <f t="shared" si="18"/>
-        <v>0.11294117647058824</v>
+        <f t="shared" si="24"/>
+        <v>0.11636363636363638</v>
       </c>
       <c r="CD24" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE24" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>7.4999999999999983E-2</v>
       </c>
       <c r="CF24" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG24" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>4.1666666666666685E-2</v>
       </c>
     </row>
@@ -11288,7 +11299,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP25" s="94">
+      <c r="AP25" s="87">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11330,89 +11341,89 @@
         <v>4</v>
       </c>
       <c r="BE25" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.62299465240641705</v>
       </c>
       <c r="BF25" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="BG25" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH25" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.63636363636363635</v>
       </c>
       <c r="BI25" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.79144385026737973</v>
       </c>
       <c r="BJ25" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.11979166666666666</v>
       </c>
       <c r="BK25" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>7.1428571428571438E-2</v>
       </c>
-      <c r="BL25" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL25" s="56">
+        <f t="shared" si="23"/>
         <v>0.81818181818181812</v>
       </c>
       <c r="BM25" s="48"/>
       <c r="BN25" s="48"/>
       <c r="BO25" s="33"/>
-      <c r="BP25" s="109" t="s">
+      <c r="BP25" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="BQ25" s="110"/>
-      <c r="BR25" s="109" t="s">
+      <c r="BQ25" s="106"/>
+      <c r="BR25" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="BS25" s="110"/>
-      <c r="BT25" s="109" t="s">
+      <c r="BS25" s="106"/>
+      <c r="BT25" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="BU25" s="110"/>
-      <c r="BV25" s="109" t="s">
+      <c r="BU25" s="106"/>
+      <c r="BV25" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="BW25" s="110"/>
+      <c r="BW25" s="106"/>
       <c r="BY25" s="4" t="s">
         <v>4</v>
       </c>
       <c r="BZ25" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA25" s="13">
-        <f t="shared" si="18"/>
-        <v>5.4621848739495805E-2</v>
+        <f t="shared" si="24"/>
+        <v>5.627705627705628E-2</v>
       </c>
       <c r="CB25" s="13">
-        <f t="shared" si="18"/>
-        <v>0.10084033613445378</v>
+        <f t="shared" si="24"/>
+        <v>0.1038961038961039</v>
       </c>
       <c r="CC25" s="13">
-        <f t="shared" si="18"/>
-        <v>0.21848739495798319</v>
+        <f t="shared" si="24"/>
+        <v>0.22510822510822512</v>
       </c>
       <c r="CD25" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE25" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6.8181818181818177E-2</v>
       </c>
       <c r="CF25" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG25" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>7.5757575757575746E-2</v>
       </c>
     </row>
@@ -11487,7 +11498,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP26" s="94">
+      <c r="AP26" s="87">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11529,97 +11540,97 @@
         <v>5</v>
       </c>
       <c r="BE26" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.81470588235294117</v>
       </c>
       <c r="BF26" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.1</v>
       </c>
       <c r="BG26" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH26" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.63636363636363635</v>
       </c>
       <c r="BI26" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.90000000000000013</v>
       </c>
       <c r="BJ26" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.36250000000000004</v>
       </c>
       <c r="BK26" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>7.1428571428571438E-2</v>
       </c>
-      <c r="BL26" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL26" s="56">
+        <f t="shared" si="23"/>
         <v>0.81818181818181812</v>
       </c>
       <c r="BM26" s="48"/>
       <c r="BN26" s="48"/>
       <c r="BO26" s="41"/>
-      <c r="BP26" s="60" t="s">
+      <c r="BP26" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="BQ26" s="60" t="s">
+      <c r="BQ26" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="BR26" s="60" t="s">
+      <c r="BR26" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="BS26" s="60" t="s">
+      <c r="BS26" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="BT26" s="60" t="s">
+      <c r="BT26" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="BU26" s="60" t="s">
+      <c r="BU26" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="BV26" s="60" t="s">
+      <c r="BV26" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="BW26" s="60" t="s">
+      <c r="BW26" s="59" t="s">
         <v>116</v>
       </c>
       <c r="BY26" s="4" t="s">
         <v>5</v>
       </c>
       <c r="BZ26" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA26" s="13">
-        <f t="shared" si="18"/>
-        <v>5.4621848739495805E-2</v>
+        <f t="shared" si="24"/>
+        <v>5.627705627705628E-2</v>
       </c>
       <c r="CB26" s="13">
-        <f t="shared" si="18"/>
-        <v>0.10084033613445378</v>
+        <f t="shared" si="24"/>
+        <v>0.1038961038961039</v>
       </c>
       <c r="CC26" s="13">
-        <f t="shared" si="18"/>
-        <v>0.21848739495798319</v>
+        <f t="shared" si="24"/>
+        <v>0.22510822510822512</v>
       </c>
       <c r="CD26" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE26" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6.8181818181818177E-2</v>
       </c>
       <c r="CF26" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG26" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>7.5757575757575746E-2</v>
       </c>
     </row>
@@ -11710,7 +11721,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP27" s="94">
+      <c r="AP27" s="87">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11752,35 +11763,35 @@
         <v>6</v>
       </c>
       <c r="BE27" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.72988505747126442</v>
       </c>
       <c r="BF27" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.28326180257510725</v>
       </c>
       <c r="BG27" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH27" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.63636363636363635</v>
       </c>
       <c r="BI27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.8362068965517242</v>
       </c>
       <c r="BJ27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.5236051502145922</v>
       </c>
       <c r="BK27" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.10344827586206896</v>
       </c>
-      <c r="BL27" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL27" s="56">
+        <f t="shared" si="23"/>
         <v>0.81818181818181812</v>
       </c>
       <c r="BM27" s="48"/>
@@ -11816,35 +11827,35 @@
         <v>6</v>
       </c>
       <c r="BZ27" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA27" s="13">
-        <f t="shared" si="18"/>
-        <v>7.9107505070993914E-2</v>
+        <f t="shared" si="24"/>
+        <v>8.1504702194357362E-2</v>
       </c>
       <c r="CB27" s="13">
-        <f t="shared" si="18"/>
-        <v>9.3306288032454346E-2</v>
+        <f t="shared" si="24"/>
+        <v>9.6133751306165097E-2</v>
       </c>
       <c r="CC27" s="13">
-        <f t="shared" si="18"/>
-        <v>0.21095334685598377</v>
+        <f t="shared" si="24"/>
+        <v>0.21734587251828633</v>
       </c>
       <c r="CD27" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE27" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6.8181818181818177E-2</v>
       </c>
       <c r="CF27" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG27" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>7.5757575757575746E-2</v>
       </c>
     </row>
@@ -11901,7 +11912,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="18" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="U28">
         <f>MAX(U9:U14)</f>
@@ -11935,7 +11946,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP28" s="94">
+      <c r="AP28" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -11977,35 +11988,35 @@
         <v>8</v>
       </c>
       <c r="BE28" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.80530973451327437</v>
       </c>
       <c r="BF28" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.16019417475728154</v>
       </c>
       <c r="BG28" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH28" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.49999999999999989</v>
       </c>
       <c r="BI28" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.88790560471976399</v>
       </c>
       <c r="BJ28" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.30097087378640774</v>
       </c>
       <c r="BK28" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>7.1428571428571438E-2</v>
       </c>
-      <c r="BL28" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL28" s="56">
+        <f t="shared" si="23"/>
         <v>0.74999999999999989</v>
       </c>
       <c r="BM28" s="48"/>
@@ -12041,35 +12052,35 @@
         <v>8</v>
       </c>
       <c r="BZ28" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA28" s="13">
-        <f t="shared" si="18"/>
-        <v>5.4621848739495805E-2</v>
+        <f t="shared" si="24"/>
+        <v>5.627705627705628E-2</v>
       </c>
       <c r="CB28" s="13">
-        <f t="shared" si="18"/>
-        <v>0.10084033613445378</v>
+        <f t="shared" si="24"/>
+        <v>0.1038961038961039</v>
       </c>
       <c r="CC28" s="13">
-        <f t="shared" si="18"/>
-        <v>0.21848739495798319</v>
+        <f t="shared" si="24"/>
+        <v>0.22510822510822512</v>
       </c>
       <c r="CD28" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE28" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6.2499999999999986E-2</v>
       </c>
       <c r="CF28" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG28" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0.10416666666666667</v>
       </c>
     </row>
@@ -12126,7 +12137,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="18" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="U29">
         <f>MAX(U15:U19)</f>
@@ -12160,7 +12171,7 @@
         <f t="shared" si="2"/>
         <v>0.61538461538461542</v>
       </c>
-      <c r="AP29" s="94">
+      <c r="AP29" s="87">
         <f t="shared" si="3"/>
         <v>0.22222222222222221</v>
       </c>
@@ -12202,35 +12213,35 @@
         <v>9</v>
       </c>
       <c r="BE29" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.47911547911547908</v>
       </c>
       <c r="BF29" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>7.598784194528875E-2</v>
       </c>
       <c r="BG29" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH29" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BI29" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.71498771498771496</v>
       </c>
       <c r="BJ29" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.53799392097264431</v>
       </c>
       <c r="BK29" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.10344827586206896</v>
       </c>
-      <c r="BL29" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL29" s="56">
+        <f t="shared" si="23"/>
         <v>0.5</v>
       </c>
       <c r="BM29" s="48"/>
@@ -12266,35 +12277,35 @@
         <v>9</v>
       </c>
       <c r="BZ29" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA29" s="13">
-        <f t="shared" si="18"/>
-        <v>7.9107505070993914E-2</v>
+        <f t="shared" si="24"/>
+        <v>8.1504702194357362E-2</v>
       </c>
       <c r="CB29" s="13">
-        <f t="shared" si="18"/>
-        <v>9.3306288032454346E-2</v>
+        <f t="shared" si="24"/>
+        <v>9.6133751306165097E-2</v>
       </c>
       <c r="CC29" s="13">
-        <f t="shared" si="18"/>
-        <v>0.21095334685598377</v>
+        <f t="shared" si="24"/>
+        <v>0.21734587251828633</v>
       </c>
       <c r="CD29" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE29" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="CF29" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG29" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0.20833333333333334</v>
       </c>
     </row>
@@ -12367,7 +12378,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP30" s="94">
+      <c r="AP30" s="87">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -12409,35 +12420,35 @@
         <v>10</v>
       </c>
       <c r="BE30" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.40384615384615391</v>
       </c>
       <c r="BF30" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.14778325123152708</v>
       </c>
       <c r="BG30" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>2.9411764705882353E-2</v>
       </c>
       <c r="BH30" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.23076923076923075</v>
       </c>
       <c r="BI30" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.65625</v>
       </c>
       <c r="BJ30" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.27586206896551729</v>
       </c>
       <c r="BK30" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.26470588235294118</v>
       </c>
-      <c r="BL30" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL30" s="56">
+        <f t="shared" si="23"/>
         <v>0.53846153846153844</v>
       </c>
       <c r="BM30" s="48"/>
@@ -12473,35 +12484,35 @@
         <v>10</v>
       </c>
       <c r="BZ30" s="13">
-        <f t="shared" si="18"/>
-        <v>1.2975778546712793E-2</v>
+        <f t="shared" si="24"/>
+        <v>1.3368983957219251E-2</v>
       </c>
       <c r="CA30" s="13">
-        <f t="shared" si="18"/>
-        <v>0.20242214532871972</v>
+        <f t="shared" si="24"/>
+        <v>0.20855614973262032</v>
       </c>
       <c r="CB30" s="13">
-        <f t="shared" si="18"/>
-        <v>5.8823529411764705E-2</v>
+        <f t="shared" si="24"/>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="CC30" s="13">
-        <f t="shared" si="18"/>
-        <v>0.17301038062283738</v>
+        <f t="shared" si="24"/>
+        <v>0.17825311942959005</v>
       </c>
       <c r="CD30" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE30" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>4.4871794871794865E-2</v>
       </c>
       <c r="CF30" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>2.5641025641025637E-2</v>
       </c>
       <c r="CG30" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0.19230769230769235</v>
       </c>
     </row>
@@ -12576,7 +12587,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP31" s="94">
+      <c r="AP31" s="87">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -12618,35 +12629,35 @@
         <v>11</v>
       </c>
       <c r="BE31" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.98089171974522282</v>
       </c>
       <c r="BF31" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.29596412556053808</v>
       </c>
       <c r="BG31" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH31" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="BI31" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.99044585987261136</v>
       </c>
       <c r="BJ31" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.50224215246636772</v>
       </c>
       <c r="BK31" s="13">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="BL31" s="57">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BL31" s="56">
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="BM31" s="48"/>
@@ -12682,35 +12693,35 @@
         <v>11</v>
       </c>
       <c r="BZ31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CB31" s="13">
-        <f t="shared" si="18"/>
-        <v>0.11764705882352941</v>
+        <f t="shared" si="24"/>
+        <v>0.12121212121212122</v>
       </c>
       <c r="CC31" s="13">
-        <f t="shared" si="18"/>
-        <v>0.23529411764705882</v>
+        <f t="shared" si="24"/>
+        <v>0.24242424242424243</v>
       </c>
       <c r="CD31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="CF31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG31" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
     </row>
@@ -12768,19 +12779,19 @@
       </c>
       <c r="T32" s="18"/>
       <c r="U32">
-        <f>(U27+U28+U24)</f>
-        <v>88</v>
+        <f>(U27+U29+U23)</f>
+        <v>135</v>
       </c>
       <c r="V32">
-        <f t="shared" ref="V32:X32" si="19">(V27+V28+V24)</f>
-        <v>176</v>
+        <f t="shared" ref="V32:X32" si="25">(V27+V29+V23)</f>
+        <v>174</v>
       </c>
       <c r="W32">
-        <f t="shared" si="19"/>
-        <v>34</v>
+        <f t="shared" si="25"/>
+        <v>33</v>
       </c>
       <c r="X32">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>12</v>
       </c>
       <c r="AD32" s="19"/>
@@ -12799,7 +12810,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP32" s="94">
+      <c r="AP32" s="87">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -12841,35 +12852,35 @@
         <v>12</v>
       </c>
       <c r="BE32" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BF32" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>9.606986899563319E-2</v>
       </c>
       <c r="BG32" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>2.4390243902439025E-2</v>
       </c>
       <c r="BH32" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.125</v>
       </c>
       <c r="BI32" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.4926590538336052</v>
       </c>
       <c r="BJ32" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.32314410480349343</v>
       </c>
       <c r="BK32" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.3902439024390244</v>
       </c>
-      <c r="BL32" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL32" s="56">
+        <f t="shared" si="23"/>
         <v>0.5625</v>
       </c>
       <c r="BM32" s="48"/>
@@ -12905,35 +12916,35 @@
         <v>12</v>
       </c>
       <c r="BZ32" s="13">
-        <f t="shared" si="18"/>
-        <v>1.0760401721664269E-2</v>
+        <f t="shared" si="24"/>
+        <v>1.1086474501108648E-2</v>
       </c>
       <c r="CA32" s="13">
-        <f t="shared" si="18"/>
-        <v>0.29842180774748922</v>
+        <f t="shared" si="24"/>
+        <v>0.30746489283074646</v>
       </c>
       <c r="CB32" s="13">
-        <f t="shared" si="18"/>
-        <v>2.8694404591104734E-2</v>
+        <f t="shared" si="24"/>
+        <v>2.9563932002956393E-2</v>
       </c>
       <c r="CC32" s="13">
-        <f t="shared" si="18"/>
-        <v>0.14347202295552366</v>
+        <f t="shared" si="24"/>
+        <v>0.14781966001478197</v>
       </c>
       <c r="CD32" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE32" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>4.6875E-2</v>
       </c>
       <c r="CF32" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG32" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0.18229166666666669</v>
       </c>
     </row>
@@ -13006,7 +13017,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP33" s="94">
+      <c r="AP33" s="87">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -13048,35 +13059,35 @@
         <v>13</v>
       </c>
       <c r="BE33" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.89814814814814814</v>
       </c>
       <c r="BF33" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.22594142259414229</v>
       </c>
       <c r="BG33" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH33" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="BI33" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.93827160493827155</v>
       </c>
       <c r="BJ33" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.48535564853556484</v>
       </c>
       <c r="BK33" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.10344827586206896</v>
       </c>
-      <c r="BL33" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL33" s="56">
+        <f t="shared" si="23"/>
         <v>0.64285714285714279</v>
       </c>
       <c r="BM33" s="48"/>
@@ -13112,35 +13123,35 @@
         <v>13</v>
       </c>
       <c r="BZ33" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA33" s="13">
-        <f t="shared" si="18"/>
-        <v>7.9107505070993914E-2</v>
+        <f t="shared" si="24"/>
+        <v>8.1504702194357362E-2</v>
       </c>
       <c r="CB33" s="13">
-        <f t="shared" si="18"/>
-        <v>9.3306288032454346E-2</v>
+        <f t="shared" si="24"/>
+        <v>9.6133751306165097E-2</v>
       </c>
       <c r="CC33" s="13">
-        <f t="shared" si="18"/>
-        <v>0.21095334685598377</v>
+        <f t="shared" si="24"/>
+        <v>0.21734587251828633</v>
       </c>
       <c r="CD33" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE33" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>5.3571428571428562E-2</v>
       </c>
       <c r="CF33" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG33" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0.14880952380952381</v>
       </c>
     </row>
@@ -13225,7 +13236,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP34" s="94">
+      <c r="AP34" s="87">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -13267,35 +13278,35 @@
         <v>14</v>
       </c>
       <c r="BE34" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.70738636363636365</v>
       </c>
       <c r="BF34" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.23041474654377883</v>
       </c>
       <c r="BG34" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH34" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.19999999999999998</v>
       </c>
       <c r="BI34" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.82386363636363635</v>
       </c>
       <c r="BJ34" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.41474654377880188</v>
       </c>
       <c r="BK34" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>3.7037037037037035E-2</v>
       </c>
-      <c r="BL34" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL34" s="56">
+        <f t="shared" si="23"/>
         <v>0.6</v>
       </c>
       <c r="BM34" s="48"/>
@@ -13331,55 +13342,55 @@
         <v>14</v>
       </c>
       <c r="BZ34" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA34" s="13">
-        <f t="shared" si="18"/>
-        <v>2.8322440087145965E-2</v>
+        <f t="shared" si="24"/>
+        <v>2.918069584736251E-2</v>
       </c>
       <c r="CB34" s="13">
-        <f t="shared" si="18"/>
-        <v>0.10893246187363834</v>
+        <f t="shared" si="24"/>
+        <v>0.11223344556677889</v>
       </c>
       <c r="CC34" s="13">
-        <f t="shared" si="18"/>
-        <v>0.22657952069716775</v>
+        <f t="shared" si="24"/>
+        <v>0.2334455667789001</v>
       </c>
       <c r="CD34" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE34" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>4.9999999999999996E-2</v>
       </c>
       <c r="CF34" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG34" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0.16666666666666669</v>
       </c>
     </row>
     <row r="35" spans="1:85" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="87" t="s">
+      <c r="A35" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="88" t="s">
+      <c r="B35" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="89">
-        <v>0</v>
-      </c>
-      <c r="D35" s="89">
-        <v>0</v>
-      </c>
-      <c r="E35" s="89">
-        <v>0</v>
-      </c>
-      <c r="F35" s="90">
+      <c r="C35" s="82">
+        <v>0</v>
+      </c>
+      <c r="D35" s="82">
+        <v>0</v>
+      </c>
+      <c r="E35" s="82">
+        <v>0</v>
+      </c>
+      <c r="F35" s="83">
         <v>0</v>
       </c>
       <c r="H35" s="42" t="s">
@@ -13418,39 +13429,39 @@
       <c r="T35" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="U35" s="67">
+      <c r="U35" s="98">
         <f>U22/U$32</f>
-        <v>2.2727272727272728E-2</v>
-      </c>
-      <c r="V35" s="67">
+        <v>1.4814814814814815E-2</v>
+      </c>
+      <c r="V35" s="98">
         <f>V22/V$32</f>
-        <v>0.39772727272727271</v>
-      </c>
-      <c r="W35" s="67">
+        <v>0.40229885057471265</v>
+      </c>
+      <c r="W35" s="98">
         <f>W22/W$32</f>
-        <v>0.44117647058823528</v>
-      </c>
-      <c r="X35" s="68">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="X35" s="99">
         <f>X22/X$32</f>
         <v>0</v>
       </c>
       <c r="AD35" s="19"/>
-      <c r="AL35" s="64" t="s">
+      <c r="AL35" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="AM35" s="95">
+      <c r="AM35" s="88">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AN35" s="96">
+      <c r="AN35" s="89">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO35" s="96">
+      <c r="AO35" s="89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP35" s="97">
+      <c r="AP35" s="90">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -13492,35 +13503,35 @@
         <v>15</v>
       </c>
       <c r="BE35" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.94654088050314467</v>
       </c>
       <c r="BF35" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="BG35" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH35" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.63636363636363635</v>
       </c>
       <c r="BI35" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.96855345911949686</v>
       </c>
       <c r="BJ35" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.32051282051282048</v>
       </c>
       <c r="BK35" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.10344827586206896</v>
       </c>
-      <c r="BL35" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL35" s="56">
+        <f t="shared" si="23"/>
         <v>0.81818181818181812</v>
       </c>
       <c r="BM35" s="48"/>
@@ -13556,35 +13567,35 @@
         <v>15</v>
       </c>
       <c r="BZ35" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA35" s="13">
-        <f t="shared" si="18"/>
-        <v>7.9107505070993914E-2</v>
+        <f t="shared" si="24"/>
+        <v>8.1504702194357362E-2</v>
       </c>
       <c r="CB35" s="13">
-        <f t="shared" si="18"/>
-        <v>9.3306288032454346E-2</v>
+        <f t="shared" si="24"/>
+        <v>9.6133751306165097E-2</v>
       </c>
       <c r="CC35" s="13">
-        <f t="shared" si="18"/>
-        <v>0.21095334685598377</v>
+        <f t="shared" si="24"/>
+        <v>0.21734587251828633</v>
       </c>
       <c r="CD35" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE35" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6.8181818181818177E-2</v>
       </c>
       <c r="CF35" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG35" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>7.5757575757575746E-2</v>
       </c>
     </row>
@@ -13592,19 +13603,19 @@
       <c r="A36" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="85">
+      <c r="B36" s="77" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="78">
         <v>144</v>
       </c>
-      <c r="D36" s="85">
+      <c r="D36" s="78">
         <v>51</v>
       </c>
-      <c r="E36" s="85">
+      <c r="E36" s="78">
         <v>6</v>
       </c>
-      <c r="F36" s="86">
+      <c r="F36" s="79">
         <v>2</v>
       </c>
       <c r="H36" s="42" t="s">
@@ -13641,19 +13652,19 @@
         <v>1</v>
       </c>
       <c r="T36" s="18"/>
-      <c r="U36" s="40">
+      <c r="U36" s="13">
         <f>U27/U$32</f>
-        <v>0.10227272727272728</v>
-      </c>
-      <c r="V36" s="40">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="V36" s="13">
         <f>V27/V$32</f>
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="W36" s="40">
+        <v>0.55172413793103448</v>
+      </c>
+      <c r="W36" s="13">
         <f>W27/W$32</f>
-        <v>0.76470588235294112</v>
-      </c>
-      <c r="X36" s="69">
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="X36" s="56">
         <f>X27/X$32</f>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -13661,20 +13672,20 @@
       <c r="AL36" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="AM36" s="101">
-        <f t="shared" ref="AM36:AM67" si="20">(AG$4-C36)/(AG$4-AG$5)</f>
+      <c r="AM36" s="94">
+        <f t="shared" ref="AM36:AM67" si="26">(AG$4-C36)/(AG$4-AG$5)</f>
         <v>0.53697749196141475</v>
       </c>
-      <c r="AN36" s="102">
-        <f t="shared" ref="AN36:AN67" si="21">(D36-AH$5)/(AH$4-AH$5)</f>
+      <c r="AN36" s="95">
+        <f t="shared" ref="AN36:AN67" si="27">(D36-AH$5)/(AH$4-AH$5)</f>
         <v>0.28813559322033899</v>
       </c>
-      <c r="AO36" s="102">
-        <f t="shared" ref="AO36:AO67" si="22">(E36-AI$5)/(AI$4-AI$5)</f>
+      <c r="AO36" s="95">
+        <f t="shared" ref="AO36:AO67" si="28">(E36-AI$5)/(AI$4-AI$5)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="AP36" s="103">
-        <f t="shared" ref="AP36:AP67" si="23">(AJ$4-F36)/(AJ$4-AJ$5)</f>
+      <c r="AP36" s="96">
+        <f t="shared" ref="AP36:AP67" si="29">(AJ$4-F36)/(AJ$4-AJ$5)</f>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR36" s="42" t="s">
@@ -13715,35 +13726,35 @@
         <v>16</v>
       </c>
       <c r="BE36" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.43842364532019712</v>
       </c>
       <c r="BF36" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.14912280701754388</v>
       </c>
       <c r="BG36" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>2.5000000000000005E-2</v>
       </c>
       <c r="BH36" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BI36" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.6724137931034484</v>
       </c>
       <c r="BJ36" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.3728070175438597</v>
       </c>
       <c r="BK36" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.375</v>
       </c>
-      <c r="BL36" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL36" s="56">
+        <f t="shared" si="23"/>
         <v>0.43750000000000006</v>
       </c>
       <c r="BM36" s="48"/>
@@ -13779,35 +13790,35 @@
         <v>16</v>
       </c>
       <c r="BZ36" s="13">
-        <f t="shared" si="18"/>
-        <v>1.1029411764705878E-2</v>
+        <f t="shared" si="24"/>
+        <v>1.1363636363636366E-2</v>
       </c>
       <c r="CA36" s="13">
-        <f t="shared" si="18"/>
-        <v>0.28676470588235292</v>
+        <f t="shared" si="24"/>
+        <v>0.29545454545454541</v>
       </c>
       <c r="CB36" s="13">
-        <f t="shared" si="18"/>
-        <v>3.2352941176470598E-2</v>
+        <f t="shared" si="24"/>
+        <v>3.3333333333333347E-2</v>
       </c>
       <c r="CC36" s="13">
-        <f t="shared" si="18"/>
-        <v>0.1470588235294118</v>
+        <f t="shared" si="24"/>
+        <v>0.15151515151515155</v>
       </c>
       <c r="CD36" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE36" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>3.6458333333333336E-2</v>
       </c>
       <c r="CF36" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="CG36" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0.234375</v>
       </c>
     </row>
@@ -13866,19 +13877,19 @@
       <c r="T37" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="U37" s="40">
+      <c r="U37" s="13">
         <f>U23/U$32</f>
-        <v>0.11363636363636363</v>
-      </c>
-      <c r="V37" s="40">
+        <v>7.407407407407407E-2</v>
+      </c>
+      <c r="V37" s="13">
         <f>V23/V$32</f>
-        <v>0.22727272727272727</v>
-      </c>
-      <c r="W37" s="40">
+        <v>0.22988505747126436</v>
+      </c>
+      <c r="W37" s="13">
         <f>W23/W$32</f>
-        <v>0.11764705882352941</v>
-      </c>
-      <c r="X37" s="69">
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="X37" s="56">
         <f>X23/X$32</f>
         <v>0.16666666666666666</v>
       </c>
@@ -13887,19 +13898,19 @@
         <v>2</v>
       </c>
       <c r="AM37" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.99678456591639875</v>
       </c>
       <c r="AN37" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.15254237288135594</v>
       </c>
       <c r="AO37" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP37" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP37" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR37" s="42" t="s">
@@ -13940,35 +13951,35 @@
         <v>17</v>
       </c>
       <c r="BE37" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.85585585585585566</v>
       </c>
       <c r="BF37" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>4.0723981900452497E-2</v>
       </c>
       <c r="BG37" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH37" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.63636363636363635</v>
       </c>
       <c r="BI37" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.92192192192192179</v>
       </c>
       <c r="BJ37" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.23981900452488691</v>
       </c>
       <c r="BK37" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>3.7037037037037035E-2</v>
       </c>
-      <c r="BL37" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL37" s="56">
+        <f t="shared" si="23"/>
         <v>0.81818181818181812</v>
       </c>
       <c r="BM37" s="48"/>
@@ -14004,35 +14015,35 @@
         <v>17</v>
       </c>
       <c r="BZ37" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA37" s="13">
-        <f t="shared" si="18"/>
-        <v>2.8322440087145965E-2</v>
+        <f t="shared" si="24"/>
+        <v>2.918069584736251E-2</v>
       </c>
       <c r="CB37" s="13">
-        <f t="shared" si="18"/>
-        <v>0.10893246187363834</v>
+        <f t="shared" si="24"/>
+        <v>0.11223344556677889</v>
       </c>
       <c r="CC37" s="13">
-        <f t="shared" si="18"/>
-        <v>0.22657952069716775</v>
+        <f t="shared" si="24"/>
+        <v>0.2334455667789001</v>
       </c>
       <c r="CD37" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE37" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>6.8181818181818177E-2</v>
       </c>
       <c r="CF37" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG37" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>7.5757575757575746E-2</v>
       </c>
     </row>
@@ -14089,19 +14100,19 @@
         <v>2</v>
       </c>
       <c r="T38" s="20"/>
-      <c r="U38" s="70">
+      <c r="U38" s="63">
         <f>U28/U$32</f>
-        <v>0.31818181818181818</v>
-      </c>
-      <c r="V38" s="70">
+        <v>0.2074074074074074</v>
+      </c>
+      <c r="V38" s="63">
         <f>V28/V$32</f>
-        <v>0.375</v>
-      </c>
-      <c r="W38" s="70">
+        <v>0.37931034482758619</v>
+      </c>
+      <c r="W38" s="63">
         <f>W28/W$32</f>
-        <v>0.23529411764705882</v>
-      </c>
-      <c r="X38" s="71">
+        <v>0.24242424242424243</v>
+      </c>
+      <c r="X38" s="64">
         <f>X28/X$32</f>
         <v>0.41666666666666669</v>
       </c>
@@ -14110,19 +14121,19 @@
         <v>4</v>
       </c>
       <c r="AM38" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.89067524115755625</v>
       </c>
       <c r="AN38" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>4.519774011299435E-2</v>
       </c>
       <c r="AO38" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP38" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP38" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR38" s="42" t="s">
@@ -14163,35 +14174,35 @@
         <v>21</v>
       </c>
       <c r="BE38" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.97460317460317469</v>
       </c>
       <c r="BF38" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BG38" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="BH38" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>0.79999999999999993</v>
       </c>
       <c r="BI38" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.98730158730158746</v>
       </c>
       <c r="BJ38" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.35164835164835168</v>
       </c>
       <c r="BK38" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>0.23529411764705882</v>
       </c>
-      <c r="BL38" s="57">
-        <f t="shared" si="17"/>
+      <c r="BL38" s="56">
+        <f t="shared" si="23"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="BM38" s="48"/>
@@ -14227,35 +14238,35 @@
         <v>21</v>
       </c>
       <c r="BZ38" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CA38" s="13">
-        <f t="shared" si="18"/>
-        <v>0.17993079584775085</v>
+        <f t="shared" si="24"/>
+        <v>0.1853832442067736</v>
       </c>
       <c r="CB38" s="13">
-        <f t="shared" si="18"/>
-        <v>6.228373702422145E-2</v>
+        <f t="shared" si="24"/>
+        <v>6.4171122994652413E-2</v>
       </c>
       <c r="CC38" s="13">
-        <f t="shared" si="18"/>
-        <v>0.17993079584775085</v>
+        <f t="shared" si="24"/>
+        <v>0.1853832442067736</v>
       </c>
       <c r="CD38" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CE38" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>7.4999999999999983E-2</v>
       </c>
       <c r="CF38" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="CG38" s="13">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>4.1666666666666685E-2</v>
       </c>
     </row>
@@ -14319,19 +14330,19 @@
         <v>5</v>
       </c>
       <c r="AM39" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.91318327974276525</v>
       </c>
       <c r="AN39" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.19209039548022599</v>
       </c>
       <c r="AO39" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP39" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP39" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR39" s="42" t="s">
@@ -14368,21 +14379,21 @@
         <v>0</v>
       </c>
       <c r="BC39" s="48"/>
-      <c r="BD39" s="104" t="s">
+      <c r="BD39" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="BE39" s="106" t="s">
+      <c r="BE39" s="102" t="s">
         <v>111</v>
       </c>
-      <c r="BF39" s="106"/>
-      <c r="BG39" s="106"/>
-      <c r="BH39" s="106"/>
-      <c r="BI39" s="106" t="s">
+      <c r="BF39" s="102"/>
+      <c r="BG39" s="102"/>
+      <c r="BH39" s="102"/>
+      <c r="BI39" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="BJ39" s="106"/>
-      <c r="BK39" s="106"/>
-      <c r="BL39" s="107"/>
+      <c r="BJ39" s="102"/>
+      <c r="BK39" s="102"/>
+      <c r="BL39" s="103"/>
       <c r="BM39" s="48"/>
       <c r="BN39" s="48"/>
       <c r="BO39" s="4" t="s">
@@ -14468,15 +14479,15 @@
       <c r="T40" s="18"/>
       <c r="U40" s="13">
         <f>1+(U35+U36)/2-(U37+U38)/2</f>
-        <v>0.84659090909090906</v>
+        <v>0.9</v>
       </c>
       <c r="V40" s="13">
         <f>1+(V35+V36)/2-(V37+V38)/2</f>
-        <v>1.1704545454545454</v>
+        <v>1.1724137931034484</v>
       </c>
       <c r="W40" s="13">
         <f>1+(W35+W36)/2-(W37+W38)/2</f>
-        <v>1.4264705882352942</v>
+        <v>1.4393939393939392</v>
       </c>
       <c r="X40" s="13">
         <f>1+(X35+X36)/2-(X37+X38)/2</f>
@@ -14487,19 +14498,19 @@
         <v>6</v>
       </c>
       <c r="AM40" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.85209003215434087</v>
       </c>
       <c r="AN40" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.62146892655367236</v>
       </c>
       <c r="AO40" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP40" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP40" s="87">
+        <f t="shared" si="29"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR40" s="42" t="s">
@@ -14536,7 +14547,7 @@
         <v>0</v>
       </c>
       <c r="BC40" s="48"/>
-      <c r="BD40" s="105"/>
+      <c r="BD40" s="101"/>
       <c r="BE40" s="50" t="s">
         <v>64</v>
       </c>
@@ -14643,9 +14654,9 @@
       <c r="R41" s="26">
         <v>1</v>
       </c>
-      <c r="T41" s="72">
+      <c r="T41" s="65">
         <f>SUM(U40:X40)/2</f>
-        <v>2.0967580213903743</v>
+        <v>2.1309038662486937</v>
       </c>
       <c r="U41" s="21"/>
       <c r="V41" s="21"/>
@@ -14661,19 +14672,19 @@
         <v>8</v>
       </c>
       <c r="AM41" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.887459807073955</v>
       </c>
       <c r="AN41" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.2655367231638418</v>
       </c>
       <c r="AO41" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP41" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP41" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR41" s="42" t="s">
@@ -14714,35 +14725,35 @@
         <v>1</v>
       </c>
       <c r="BE41" s="13">
-        <f t="shared" ref="BE41:BH56" si="24">(1-BI5)/(BI5+1-BE5)</f>
+        <f t="shared" ref="BE41:BH56" si="30">(1-BI5)/(BI5+1-BE5)</f>
         <v>8.8691796008869041E-3</v>
       </c>
       <c r="BF41" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.27777777777777785</v>
       </c>
       <c r="BG41" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.64516129032258063</v>
       </c>
       <c r="BH41" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI41" s="13">
-        <f t="shared" ref="BI41:BL56" si="25">(1-BE5)/(BI5+1-BE5)</f>
+        <f t="shared" ref="BI41:BL56" si="31">(1-BE5)/(BI5+1-BE5)</f>
         <v>0.31929046563192903</v>
       </c>
       <c r="BJ41" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.57539682539682546</v>
       </c>
       <c r="BK41" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.80645161290322587</v>
       </c>
-      <c r="BL41" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL41" s="56">
+        <f t="shared" si="31"/>
         <v>0.25</v>
       </c>
       <c r="BM41" s="48"/>
@@ -14831,19 +14842,19 @@
         <v>9</v>
       </c>
       <c r="AM42" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.91639871382636651</v>
       </c>
       <c r="AN42" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.14124293785310735</v>
       </c>
       <c r="AO42" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP42" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP42" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR42" s="42" t="s">
@@ -14884,35 +14895,35 @@
         <v>2</v>
       </c>
       <c r="BE42" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BF42" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.1103678929765886</v>
       </c>
       <c r="BG42" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BH42" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI42" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>6.3897763578275226E-3</v>
       </c>
       <c r="BJ42" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.51839464882943143</v>
       </c>
       <c r="BK42" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.48000000000000004</v>
       </c>
-      <c r="BL42" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL42" s="56">
+        <f t="shared" si="31"/>
         <v>0.10000000000000003</v>
       </c>
       <c r="BM42" s="48"/>
@@ -15001,19 +15012,19 @@
         <v>10</v>
       </c>
       <c r="AM43" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.65594855305466238</v>
       </c>
       <c r="AN43" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.25988700564971751</v>
       </c>
       <c r="AO43" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP43" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP43" s="87">
+        <f t="shared" si="29"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="AR43" s="42" t="s">
@@ -15054,35 +15065,35 @@
         <v>4</v>
       </c>
       <c r="BE43" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>4.010695187165772E-2</v>
       </c>
       <c r="BF43" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.80208333333333326</v>
       </c>
       <c r="BG43" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.85714285714285721</v>
       </c>
       <c r="BH43" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI43" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.20855614973262038</v>
       </c>
       <c r="BJ43" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.88020833333333326</v>
       </c>
       <c r="BK43" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.9285714285714286</v>
       </c>
-      <c r="BL43" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL43" s="56">
+        <f t="shared" si="31"/>
         <v>0.1818181818181818</v>
       </c>
       <c r="BM43" s="48"/>
@@ -15144,19 +15155,19 @@
         <v>11</v>
       </c>
       <c r="AM44" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.99035369774919613</v>
       </c>
       <c r="AN44" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.48587570621468928</v>
       </c>
       <c r="AO44" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP44" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP44" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR44" s="42" t="s">
@@ -15197,35 +15208,35 @@
         <v>5</v>
       </c>
       <c r="BE44" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.4705882352941131E-2</v>
       </c>
       <c r="BF44" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.375</v>
       </c>
       <c r="BG44" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.85714285714285721</v>
       </c>
       <c r="BH44" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI44" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.10000000000000002</v>
       </c>
       <c r="BJ44" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.63750000000000007</v>
       </c>
       <c r="BK44" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.9285714285714286</v>
       </c>
-      <c r="BL44" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL44" s="56">
+        <f t="shared" si="31"/>
         <v>0.1818181818181818</v>
       </c>
       <c r="BM44" s="48"/>
@@ -15287,19 +15298,19 @@
         <v>12</v>
       </c>
       <c r="AM45" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.92604501607717038</v>
       </c>
       <c r="AN45" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.20903954802259886</v>
       </c>
       <c r="AO45" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP45" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP45" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR45" s="42" t="s">
@@ -15340,35 +15351,35 @@
         <v>6</v>
       </c>
       <c r="BE45" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>5.7471264367816119E-2</v>
       </c>
       <c r="BF45" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.23605150214592274</v>
       </c>
       <c r="BG45" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH45" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI45" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.16379310344827583</v>
       </c>
       <c r="BJ45" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.47639484978540764</v>
       </c>
       <c r="BK45" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.89655172413793105</v>
       </c>
-      <c r="BL45" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL45" s="56">
+        <f t="shared" si="31"/>
         <v>0.1818181818181818</v>
       </c>
       <c r="BM45" s="48"/>
@@ -15430,19 +15441,19 @@
         <v>13</v>
       </c>
       <c r="AM46" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.96463022508038587</v>
       </c>
       <c r="AN46" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.37853107344632769</v>
       </c>
       <c r="AO46" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP46" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP46" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR46" s="42" t="s">
@@ -15483,35 +15494,35 @@
         <v>8</v>
       </c>
       <c r="BE46" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>2.9498525073746323E-2</v>
       </c>
       <c r="BF46" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.55825242718446599</v>
       </c>
       <c r="BG46" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.85714285714285721</v>
       </c>
       <c r="BH46" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI46" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.11209439528023599</v>
       </c>
       <c r="BJ46" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.69902912621359214</v>
       </c>
       <c r="BK46" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.9285714285714286</v>
       </c>
-      <c r="BL46" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL46" s="56">
+        <f t="shared" si="31"/>
         <v>0.25</v>
       </c>
       <c r="BM46" s="48"/>
@@ -15573,19 +15584,19 @@
         <v>14</v>
       </c>
       <c r="AM47" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.89389067524115751</v>
       </c>
       <c r="AN47" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.41807909604519772</v>
       </c>
       <c r="AO47" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP47" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP47" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR47" s="42" t="s">
@@ -15626,35 +15637,35 @@
         <v>9</v>
       </c>
       <c r="BE47" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>4.9140049140049158E-2</v>
       </c>
       <c r="BF47" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BG47" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH47" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI47" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.28501228501228504</v>
       </c>
       <c r="BJ47" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.46200607902735558</v>
       </c>
       <c r="BK47" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.89655172413793105</v>
       </c>
-      <c r="BL47" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL47" s="56">
+        <f t="shared" si="31"/>
         <v>0.5</v>
       </c>
       <c r="BM47" s="48"/>
@@ -15716,19 +15727,19 @@
         <v>15</v>
       </c>
       <c r="AM48" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.96784565916398713</v>
       </c>
       <c r="AN48" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.2711864406779661</v>
       </c>
       <c r="AO48" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP48" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP48" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR48" s="42" t="s">
@@ -15769,35 +15780,35 @@
         <v>10</v>
       </c>
       <c r="BE48" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>9.1346153846153855E-2</v>
       </c>
       <c r="BF48" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.59605911330049266</v>
       </c>
       <c r="BG48" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.5</v>
       </c>
       <c r="BH48" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.15384615384615383</v>
       </c>
       <c r="BI48" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.34375</v>
       </c>
       <c r="BJ48" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.72413793103448276</v>
       </c>
       <c r="BK48" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.73529411764705888</v>
       </c>
-      <c r="BL48" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL48" s="56">
+        <f t="shared" si="31"/>
         <v>0.46153846153846162</v>
       </c>
       <c r="BM48" s="48"/>
@@ -15859,19 +15870,19 @@
         <v>16</v>
       </c>
       <c r="AM49" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.57234726688102899</v>
       </c>
       <c r="AN49" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.32203389830508472</v>
       </c>
       <c r="AO49" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.53846153846153844</v>
       </c>
-      <c r="AP49" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP49" s="87">
+        <f t="shared" si="29"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="AR49" s="42" t="s">
@@ -15912,35 +15923,35 @@
         <v>11</v>
       </c>
       <c r="BE49" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BF49" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.29147982062780264</v>
       </c>
       <c r="BG49" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="BH49" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI49" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>9.5541401273885485E-3</v>
       </c>
       <c r="BJ49" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.49775784753363228</v>
       </c>
       <c r="BK49" s="13">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="BL49" s="57">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="BL49" s="56">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="BM49" s="48"/>
@@ -16002,19 +16013,19 @@
         <v>17</v>
       </c>
       <c r="AM50" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.94212218649517687</v>
       </c>
       <c r="AN50" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>5.0847457627118647E-2</v>
       </c>
       <c r="AO50" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP50" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP50" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR50" s="42" t="s">
@@ -16055,45 +16066,45 @@
         <v>12</v>
       </c>
       <c r="BE50" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.4681892332789581E-2</v>
       </c>
       <c r="BF50" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.44978165938864634</v>
       </c>
       <c r="BG50" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.24390243902439024</v>
       </c>
       <c r="BH50" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI50" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.5073409461663948</v>
       </c>
       <c r="BJ50" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.67685589519650657</v>
       </c>
       <c r="BK50" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.6097560975609756</v>
       </c>
-      <c r="BL50" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL50" s="56">
+        <f t="shared" si="31"/>
         <v>0.43750000000000006</v>
       </c>
       <c r="BM50" s="48"/>
       <c r="BN50" s="48"/>
     </row>
     <row r="51" spans="1:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="64" t="s">
+      <c r="A51" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="B51" s="73" t="s">
+      <c r="B51" s="66" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="27">
@@ -16108,10 +16119,10 @@
       <c r="F51" s="28">
         <v>0</v>
       </c>
-      <c r="H51" s="64" t="s">
+      <c r="H51" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="I51" s="73" t="s">
+      <c r="I51" s="66" t="s">
         <v>119</v>
       </c>
       <c r="J51" s="27">
@@ -16126,7 +16137,7 @@
       <c r="M51" s="27">
         <v>0</v>
       </c>
-      <c r="N51" s="73" t="s">
+      <c r="N51" s="66" t="s">
         <v>120</v>
       </c>
       <c r="O51" s="27">
@@ -16141,56 +16152,56 @@
       <c r="R51" s="28">
         <v>1</v>
       </c>
-      <c r="AL51" s="87" t="s">
+      <c r="AL51" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="AM51" s="98">
-        <f t="shared" si="20"/>
+      <c r="AM51" s="91">
+        <f t="shared" si="26"/>
         <v>0.99678456591639875</v>
       </c>
-      <c r="AN51" s="99">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AO51" s="99">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP51" s="100">
-        <f t="shared" si="23"/>
-        <v>1</v>
-      </c>
-      <c r="AR51" s="64" t="s">
+      <c r="AN51" s="92">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AO51" s="92">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP51" s="93">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="AR51" s="62" t="s">
         <v>21</v>
       </c>
       <c r="AS51" s="21">
         <v>4</v>
       </c>
-      <c r="AT51" s="74">
-        <v>1</v>
-      </c>
-      <c r="AU51" s="74">
+      <c r="AT51" s="67">
+        <v>1</v>
+      </c>
+      <c r="AU51" s="67">
         <v>0.29943502824858759</v>
       </c>
-      <c r="AV51" s="74">
+      <c r="AV51" s="67">
         <v>0.73076923076923073</v>
       </c>
-      <c r="AW51" s="74">
+      <c r="AW51" s="67">
         <v>0</v>
       </c>
       <c r="AX51" s="21">
         <v>5</v>
       </c>
-      <c r="AY51" s="74">
+      <c r="AY51" s="67">
         <v>0.98713826366559487</v>
       </c>
-      <c r="AZ51" s="74">
+      <c r="AZ51" s="67">
         <v>0.5423728813559322</v>
       </c>
-      <c r="BA51" s="74">
+      <c r="BA51" s="67">
         <v>0.69230769230769229</v>
       </c>
-      <c r="BB51" s="75">
+      <c r="BB51" s="68">
         <v>0.1111111111111111</v>
       </c>
       <c r="BC51" s="48"/>
@@ -16198,35 +16209,35 @@
         <v>13</v>
       </c>
       <c r="BE51" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>2.1604938271604934E-2</v>
       </c>
       <c r="BF51" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.25523012552301261</v>
       </c>
       <c r="BG51" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH51" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI51" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>6.1728395061728419E-2</v>
       </c>
       <c r="BJ51" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.5146443514644351</v>
       </c>
       <c r="BK51" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.89655172413793105</v>
       </c>
-      <c r="BL51" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL51" s="56">
+        <f t="shared" si="31"/>
         <v>0.35714285714285715</v>
       </c>
       <c r="BM51" s="48"/>
@@ -16255,20 +16266,20 @@
       <c r="AL52" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AM52" s="91">
-        <f t="shared" si="20"/>
+      <c r="AM52" s="84">
+        <f t="shared" si="26"/>
         <v>0.96784565916398713</v>
       </c>
-      <c r="AN52" s="92">
-        <f t="shared" si="21"/>
+      <c r="AN52" s="85">
+        <f t="shared" si="27"/>
         <v>0.49717514124293788</v>
       </c>
-      <c r="AO52" s="92">
-        <f t="shared" si="22"/>
+      <c r="AO52" s="85">
+        <f t="shared" si="28"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP52" s="93">
-        <f t="shared" si="23"/>
+      <c r="AP52" s="86">
+        <f t="shared" si="29"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR52" s="4"/>
@@ -16276,35 +16287,35 @@
         <v>14</v>
       </c>
       <c r="BE52" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>5.9659090909090898E-2</v>
       </c>
       <c r="BF52" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.40092165898617516</v>
       </c>
       <c r="BG52" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.92592592592592582</v>
       </c>
       <c r="BH52" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI52" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.17613636363636365</v>
       </c>
       <c r="BJ52" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.58525345622119818</v>
       </c>
       <c r="BK52" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.96296296296296291</v>
       </c>
-      <c r="BL52" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL52" s="56">
+        <f t="shared" si="31"/>
         <v>0.4</v>
       </c>
     </row>
@@ -16332,19 +16343,19 @@
         <v>2</v>
       </c>
       <c r="AM53" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.99678456591639875</v>
       </c>
       <c r="AN53" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.16384180790960451</v>
       </c>
       <c r="AO53" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="AP53" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP53" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR53" s="4"/>
@@ -16352,35 +16363,35 @@
         <v>15</v>
       </c>
       <c r="BE53" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>9.4339622641509569E-3</v>
       </c>
       <c r="BF53" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.4358974358974359</v>
       </c>
       <c r="BG53" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.79310344827586199</v>
       </c>
       <c r="BH53" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI53" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>3.1446540880503158E-2</v>
       </c>
       <c r="BJ53" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.67948717948717952</v>
       </c>
       <c r="BK53" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.89655172413793105</v>
       </c>
-      <c r="BL53" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL53" s="56">
+        <f t="shared" si="31"/>
         <v>0.1818181818181818</v>
       </c>
     </row>
@@ -16408,19 +16419,19 @@
         <v>4</v>
       </c>
       <c r="AM54" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="AN54" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>6.7796610169491525E-2</v>
       </c>
       <c r="AO54" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP54" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP54" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR54" s="4"/>
@@ -16428,35 +16439,35 @@
         <v>16</v>
       </c>
       <c r="BE54" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>9.3596059113300503E-2</v>
       </c>
       <c r="BF54" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.40350877192982459</v>
       </c>
       <c r="BG54" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.27500000000000008</v>
       </c>
       <c r="BH54" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.125</v>
       </c>
       <c r="BI54" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.32758620689655171</v>
       </c>
       <c r="BJ54" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.62719298245614041</v>
       </c>
       <c r="BK54" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.62500000000000011</v>
       </c>
-      <c r="BL54" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL54" s="56">
+        <f t="shared" si="31"/>
         <v>0.5625</v>
       </c>
     </row>
@@ -16484,19 +16495,19 @@
         <v>5</v>
       </c>
       <c r="AM55" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.89067524115755625</v>
       </c>
       <c r="AN55" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.30508474576271188</v>
       </c>
       <c r="AO55" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP55" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP55" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR55" s="4"/>
@@ -16504,35 +16515,35 @@
         <v>17</v>
       </c>
       <c r="BE55" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1.2012012012011993E-2</v>
       </c>
       <c r="BF55" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.56108597285067874</v>
       </c>
       <c r="BG55" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.92592592592592582</v>
       </c>
       <c r="BH55" s="13">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="BI55" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>7.8078078078078109E-2</v>
       </c>
       <c r="BJ55" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.7601809954751132</v>
       </c>
       <c r="BK55" s="13">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0.96296296296296291</v>
       </c>
-      <c r="BL55" s="57">
-        <f t="shared" si="25"/>
+      <c r="BL55" s="56">
+        <f t="shared" si="31"/>
         <v>0.1818181818181818</v>
       </c>
     </row>
@@ -16560,55 +16571,55 @@
         <v>6</v>
       </c>
       <c r="AM56" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.89067524115755625</v>
       </c>
       <c r="AN56" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.68926553672316382</v>
       </c>
       <c r="AO56" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP56" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP56" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR56" s="4"/>
-      <c r="BD56" s="64" t="s">
+      <c r="BD56" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="BE56" s="65">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BF56" s="65">
-        <f t="shared" si="24"/>
+      <c r="BE56" s="63">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BF56" s="63">
+        <f t="shared" si="30"/>
         <v>0.2967032967032967</v>
       </c>
-      <c r="BG56" s="65">
-        <f t="shared" si="24"/>
+      <c r="BG56" s="63">
+        <f t="shared" si="30"/>
         <v>0.52941176470588236</v>
       </c>
-      <c r="BH56" s="65">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BI56" s="65">
-        <f t="shared" si="25"/>
+      <c r="BH56" s="63">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BI56" s="63">
+        <f t="shared" si="31"/>
         <v>1.2698412698412683E-2</v>
       </c>
-      <c r="BJ56" s="65">
-        <f t="shared" si="25"/>
+      <c r="BJ56" s="63">
+        <f t="shared" si="31"/>
         <v>0.64835164835164838</v>
       </c>
-      <c r="BK56" s="65">
-        <f t="shared" si="25"/>
+      <c r="BK56" s="63">
+        <f t="shared" si="31"/>
         <v>0.76470588235294112</v>
       </c>
-      <c r="BL56" s="66">
-        <f t="shared" si="25"/>
+      <c r="BL56" s="64">
+        <f t="shared" si="31"/>
         <v>0.10000000000000003</v>
       </c>
     </row>
@@ -16636,19 +16647,19 @@
         <v>8</v>
       </c>
       <c r="AM57" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.92604501607717038</v>
       </c>
       <c r="AN57" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.34463276836158191</v>
       </c>
       <c r="AO57" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP57" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP57" s="87">
+        <f t="shared" si="29"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR57" s="4"/>
@@ -16677,19 +16688,19 @@
         <v>9</v>
       </c>
       <c r="AM58" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.90675241157556274</v>
       </c>
       <c r="AN58" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.22598870056497175</v>
       </c>
       <c r="AO58" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP58" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP58" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR58" s="4"/>
@@ -16718,19 +16729,19 @@
         <v>10</v>
       </c>
       <c r="AM59" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.70096463022508038</v>
       </c>
       <c r="AN59" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.2824858757062147</v>
       </c>
       <c r="AO59" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP59" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP59" s="87">
+        <f t="shared" si="29"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR59" s="4"/>
@@ -16759,19 +16770,19 @@
         <v>11</v>
       </c>
       <c r="AM60" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.99678456591639875</v>
       </c>
       <c r="AN60" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.47457627118644069</v>
       </c>
       <c r="AO60" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP60" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP60" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR60" s="4"/>
@@ -16800,19 +16811,19 @@
         <v>12</v>
       </c>
       <c r="AM61" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.95176848874598075</v>
       </c>
       <c r="AN61" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.12429378531073447</v>
       </c>
       <c r="AO61" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP61" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP61" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR61" s="4"/>
@@ -16841,19 +16852,19 @@
         <v>13</v>
       </c>
       <c r="AM62" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.96141479099678462</v>
       </c>
       <c r="AN62" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.65536723163841804</v>
       </c>
       <c r="AO62" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP62" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP62" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR62" s="4"/>
@@ -16882,19 +16893,19 @@
         <v>14</v>
       </c>
       <c r="AM63" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.92926045016077174</v>
       </c>
       <c r="AN63" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.3615819209039548</v>
       </c>
       <c r="AO63" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP63" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP63" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR63" s="4"/>
@@ -16923,19 +16934,19 @@
         <v>15</v>
       </c>
       <c r="AM64" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.98713826366559487</v>
       </c>
       <c r="AN64" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.15254237288135594</v>
       </c>
       <c r="AO64" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP64" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP64" s="87">
+        <f t="shared" si="29"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR64" s="4"/>
@@ -16964,19 +16975,19 @@
         <v>16</v>
       </c>
       <c r="AM65" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.83279742765273312</v>
       </c>
       <c r="AN65" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0.19209039548022599</v>
       </c>
       <c r="AO65" s="47">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP65" s="94">
-        <f t="shared" si="23"/>
+      <c r="AP65" s="87">
+        <f t="shared" si="29"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="AR65" s="4"/>
@@ -17005,19 +17016,19 @@
         <v>17</v>
       </c>
       <c r="AM66" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.97106109324758838</v>
       </c>
       <c r="AN66" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>6.2146892655367235E-2</v>
       </c>
       <c r="AO66" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP66" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP66" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR66" s="4"/>
@@ -17046,60 +17057,60 @@
         <v>21</v>
       </c>
       <c r="AM67" s="46">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="AN67" s="47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>5.6497175141242938E-3</v>
       </c>
       <c r="AO67" s="47">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AP67" s="94">
-        <f t="shared" si="23"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AP67" s="87">
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="AR67" s="4"/>
     </row>
     <row r="68" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="87" t="s">
+      <c r="A68" s="80" t="s">
         <v>123</v>
       </c>
-      <c r="B68" s="88" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="89">
+      <c r="B68" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="82">
         <v>18</v>
       </c>
-      <c r="D68" s="89">
+      <c r="D68" s="82">
         <v>107</v>
       </c>
-      <c r="E68" s="89">
+      <c r="E68" s="82">
         <v>2</v>
       </c>
-      <c r="F68" s="90">
+      <c r="F68" s="83">
         <v>3</v>
       </c>
       <c r="H68" s="4"/>
-      <c r="AL68" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AM68" s="95">
-        <f t="shared" ref="AM68:AM99" si="26">(AG$4-C68)/(AG$4-AG$5)</f>
+      <c r="AL68" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM68" s="88">
+        <f t="shared" ref="AM68:AM99" si="32">(AG$4-C68)/(AG$4-AG$5)</f>
         <v>0.94212218649517687</v>
       </c>
-      <c r="AN68" s="96">
-        <f t="shared" ref="AN68:AN99" si="27">(D68-AH$5)/(AH$4-AH$5)</f>
+      <c r="AN68" s="89">
+        <f t="shared" ref="AN68:AN99" si="33">(D68-AH$5)/(AH$4-AH$5)</f>
         <v>0.60451977401129942</v>
       </c>
-      <c r="AO68" s="96">
-        <f t="shared" ref="AO68:AO99" si="28">(E68-AI$5)/(AI$4-AI$5)</f>
+      <c r="AO68" s="89">
+        <f t="shared" ref="AO68:AO99" si="34">(E68-AI$5)/(AI$4-AI$5)</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP68" s="97">
-        <f t="shared" ref="AP68:AP99" si="29">(AJ$4-F68)/(AJ$4-AJ$5)</f>
+      <c r="AP68" s="90">
+        <f t="shared" ref="AP68:AP99" si="35">(AJ$4-F68)/(AJ$4-AJ$5)</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="AR68" s="4"/>
@@ -17108,39 +17119,39 @@
       <c r="A69" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="B69" s="84" t="s">
+      <c r="B69" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="85">
-        <v>1</v>
-      </c>
-      <c r="D69" s="85">
+      <c r="C69" s="78">
+        <v>1</v>
+      </c>
+      <c r="D69" s="78">
         <v>144</v>
       </c>
-      <c r="E69" s="85">
+      <c r="E69" s="78">
         <v>3</v>
       </c>
-      <c r="F69" s="86">
+      <c r="F69" s="79">
         <v>1</v>
       </c>
       <c r="H69" s="4"/>
       <c r="AL69" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AM69" s="101">
-        <f t="shared" si="26"/>
+      <c r="AM69" s="94">
+        <f t="shared" si="32"/>
         <v>0.99678456591639875</v>
       </c>
-      <c r="AN69" s="102">
-        <f t="shared" si="27"/>
+      <c r="AN69" s="95">
+        <f t="shared" si="33"/>
         <v>0.81355932203389836</v>
       </c>
-      <c r="AO69" s="102">
-        <f t="shared" si="28"/>
+      <c r="AO69" s="95">
+        <f t="shared" si="34"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP69" s="103">
-        <f t="shared" si="29"/>
+      <c r="AP69" s="96">
+        <f t="shared" si="35"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR69" s="4"/>
@@ -17169,19 +17180,19 @@
         <v>4</v>
       </c>
       <c r="AM70" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.74919614147909963</v>
       </c>
       <c r="AN70" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.12994350282485875</v>
       </c>
       <c r="AO70" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP70" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP70" s="87">
+        <f t="shared" si="35"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR70" s="4"/>
@@ -17210,19 +17221,19 @@
         <v>5</v>
       </c>
       <c r="AM71" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.89389067524115751</v>
       </c>
       <c r="AN71" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.49152542372881358</v>
       </c>
       <c r="AO71" s="47">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AP71" s="94">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AP71" s="87">
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="AR71" s="4"/>
@@ -17251,19 +17262,19 @@
         <v>6</v>
       </c>
       <c r="AM72" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.90353697749196138</v>
       </c>
       <c r="AN72" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.4463276836158192</v>
       </c>
       <c r="AO72" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP72" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP72" s="87">
+        <f t="shared" si="35"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR72" s="4"/>
@@ -17292,19 +17303,19 @@
         <v>8</v>
       </c>
       <c r="AM73" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.87781350482315113</v>
       </c>
       <c r="AN73" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.2824858757062147</v>
       </c>
       <c r="AO73" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP73" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP73" s="87">
+        <f t="shared" si="35"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="AR73" s="4"/>
@@ -17333,19 +17344,19 @@
         <v>9</v>
       </c>
       <c r="AM74" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.6463022508038585</v>
       </c>
       <c r="AN74" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="AO74" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP74" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP74" s="87">
+        <f t="shared" si="35"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="AR74" s="4"/>
@@ -17374,19 +17385,19 @@
         <v>10</v>
       </c>
       <c r="AM75" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.54019292604501612</v>
       </c>
       <c r="AN75" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.31638418079096048</v>
       </c>
       <c r="AO75" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="AP75" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP75" s="87">
+        <f t="shared" si="35"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AR75" s="4"/>
@@ -17415,19 +17426,19 @@
         <v>11</v>
       </c>
       <c r="AM76" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.99678456591639875</v>
       </c>
       <c r="AN76" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.63276836158192096</v>
       </c>
       <c r="AO76" s="47">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AP76" s="94">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AP76" s="87">
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="AR76" s="4"/>
@@ -17456,19 +17467,19 @@
         <v>12</v>
       </c>
       <c r="AM77" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.93890675241157562</v>
       </c>
       <c r="AN77" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.41807909604519772</v>
       </c>
       <c r="AO77" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.23076923076923078</v>
       </c>
-      <c r="AP77" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP77" s="87">
+        <f t="shared" si="35"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR77" s="4"/>
@@ -17497,19 +17508,19 @@
         <v>13</v>
       </c>
       <c r="AM78" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.93890675241157562</v>
       </c>
       <c r="AN78" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.63276836158192096</v>
       </c>
       <c r="AO78" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP78" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP78" s="87">
+        <f t="shared" si="35"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR78" s="4"/>
@@ -17538,19 +17549,19 @@
         <v>14</v>
       </c>
       <c r="AM79" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.80064308681672025</v>
       </c>
       <c r="AN79" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.38983050847457629</v>
       </c>
       <c r="AO79" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP79" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP79" s="87">
+        <f t="shared" si="35"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR79" s="4"/>
@@ -17579,19 +17590,19 @@
         <v>15</v>
       </c>
       <c r="AM80" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.98713826366559487</v>
       </c>
       <c r="AN80" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.42372881355932202</v>
       </c>
       <c r="AO80" s="47">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AP80" s="94">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AP80" s="87">
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="AR80" s="4"/>
@@ -17620,19 +17631,19 @@
         <v>16</v>
       </c>
       <c r="AM81" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.6913183279742765</v>
       </c>
       <c r="AN81" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.48022598870056499</v>
       </c>
       <c r="AO81" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP81" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP81" s="87">
+        <f t="shared" si="35"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="AR81" s="4"/>
@@ -17661,28 +17672,28 @@
         <v>17</v>
       </c>
       <c r="AM82" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.91639871382636651</v>
       </c>
       <c r="AN82" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.29943502824858759</v>
       </c>
       <c r="AO82" s="47">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AP82" s="94">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AP82" s="87">
+        <f t="shared" si="35"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR82" s="4"/>
     </row>
     <row r="83" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="64" t="s">
+      <c r="A83" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="B83" s="73" t="s">
+      <c r="B83" s="66" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="27">
@@ -17698,23 +17709,23 @@
         <v>0</v>
       </c>
       <c r="H83" s="4"/>
-      <c r="AL83" s="87" t="s">
+      <c r="AL83" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="AM83" s="98">
-        <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
-      <c r="AN83" s="99">
-        <f t="shared" si="27"/>
+      <c r="AM83" s="91">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="AN83" s="92">
+        <f t="shared" si="33"/>
         <v>0.29943502824858759</v>
       </c>
-      <c r="AO83" s="99">
-        <f t="shared" si="28"/>
+      <c r="AO83" s="92">
+        <f t="shared" si="34"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP83" s="100">
-        <f t="shared" si="29"/>
+      <c r="AP83" s="93">
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="AR83" s="4"/>
@@ -17742,20 +17753,20 @@
       <c r="AL84" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AM84" s="91">
-        <f t="shared" si="26"/>
+      <c r="AM84" s="84">
+        <f t="shared" si="32"/>
         <v>0.98392282958199362</v>
       </c>
-      <c r="AN84" s="92">
-        <f t="shared" si="27"/>
+      <c r="AN84" s="85">
+        <f t="shared" si="33"/>
         <v>0.39548022598870058</v>
       </c>
-      <c r="AO84" s="92">
-        <f t="shared" si="28"/>
+      <c r="AO84" s="85">
+        <f t="shared" si="34"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP84" s="93">
-        <f t="shared" si="29"/>
+      <c r="AP84" s="86">
+        <f t="shared" si="35"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR84" s="4"/>
@@ -17784,19 +17795,19 @@
         <v>2</v>
       </c>
       <c r="AM85" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.99356913183279738</v>
       </c>
       <c r="AN85" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.3559322033898305</v>
       </c>
       <c r="AO85" s="47">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="AP85" s="94">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="AP85" s="87">
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="AR85" s="4"/>
@@ -17825,19 +17836,19 @@
         <v>4</v>
       </c>
       <c r="AM86" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.909967845659164</v>
       </c>
       <c r="AN86" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>7.909604519774012E-2</v>
       </c>
       <c r="AO86" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP86" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP86" s="87">
+        <f t="shared" si="35"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="AR86" s="4"/>
@@ -17866,19 +17877,19 @@
         <v>5</v>
       </c>
       <c r="AM87" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.909967845659164</v>
       </c>
       <c r="AN87" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.31638418079096048</v>
       </c>
       <c r="AO87" s="47">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AP87" s="94">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AP87" s="87">
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="AR87" s="4"/>
@@ -17907,19 +17918,19 @@
         <v>6</v>
       </c>
       <c r="AM88" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.83601286173633438</v>
       </c>
       <c r="AN88" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.3728813559322034</v>
       </c>
       <c r="AO88" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP88" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP88" s="87">
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="AR88" s="4"/>
@@ -17948,19 +17959,19 @@
         <v>8</v>
       </c>
       <c r="AM89" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="AN89" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.1864406779661017</v>
       </c>
       <c r="AO89" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP89" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP89" s="87">
+        <f t="shared" si="35"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR89" s="4"/>
@@ -17989,19 +18000,19 @@
         <v>9</v>
       </c>
       <c r="AM90" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.62700964630225076</v>
       </c>
       <c r="AN90" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.22598870056497175</v>
       </c>
       <c r="AO90" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP90" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP90" s="87">
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AR90" s="4"/>
@@ -18030,19 +18041,19 @@
         <v>10</v>
       </c>
       <c r="AM91" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.65273311897106112</v>
       </c>
       <c r="AN91" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.30508474576271188</v>
       </c>
       <c r="AO91" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP91" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP91" s="87">
+        <f t="shared" si="35"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AR91" s="4"/>
@@ -18071,19 +18082,19 @@
         <v>11</v>
       </c>
       <c r="AM92" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.99035369774919613</v>
       </c>
       <c r="AN92" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.40677966101694918</v>
       </c>
       <c r="AO92" s="47">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AP92" s="94">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AP92" s="87">
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="AR92" s="4"/>
@@ -18112,19 +18123,19 @@
         <v>12</v>
       </c>
       <c r="AM93" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.97106109324758838</v>
       </c>
       <c r="AN93" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.21468926553672316</v>
       </c>
       <c r="AO93" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP93" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP93" s="87">
+        <f t="shared" si="35"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR93" s="4"/>
@@ -18153,19 +18164,19 @@
         <v>13</v>
       </c>
       <c r="AM94" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.93569131832797425</v>
       </c>
       <c r="AN94" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.33898305084745761</v>
       </c>
       <c r="AO94" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP94" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP94" s="87">
+        <f t="shared" si="35"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="AR94" s="4"/>
@@ -18194,19 +18205,19 @@
         <v>14</v>
       </c>
       <c r="AM95" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.83279742765273312</v>
       </c>
       <c r="AN95" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.50847457627118642</v>
       </c>
       <c r="AO95" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP95" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP95" s="87">
+        <f t="shared" si="35"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AR95" s="4"/>
@@ -18235,19 +18246,19 @@
         <v>15</v>
       </c>
       <c r="AM96" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.96784565916398713</v>
       </c>
       <c r="AN96" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.1751412429378531</v>
       </c>
       <c r="AO96" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP96" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP96" s="87">
+        <f t="shared" si="35"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR96" s="4"/>
@@ -18276,19 +18287,19 @@
         <v>16</v>
       </c>
       <c r="AM97" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.74598070739549838</v>
       </c>
       <c r="AN97" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.29378531073446329</v>
       </c>
       <c r="AO97" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.57692307692307687</v>
       </c>
-      <c r="AP97" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP97" s="87">
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AR97" s="4"/>
@@ -18317,28 +18328,28 @@
         <v>17</v>
       </c>
       <c r="AM98" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0.96141479099678462</v>
       </c>
       <c r="AN98" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.1751412429378531</v>
       </c>
       <c r="AO98" s="47">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP98" s="94">
-        <f t="shared" si="29"/>
+      <c r="AP98" s="87">
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="AR98" s="4"/>
     </row>
     <row r="99" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="64" t="s">
+      <c r="A99" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="B99" s="73" t="s">
+      <c r="B99" s="66" t="s">
         <v>21</v>
       </c>
       <c r="C99" s="27">
@@ -18354,23 +18365,23 @@
         <v>1</v>
       </c>
       <c r="H99" s="4"/>
-      <c r="AL99" s="64" t="s">
+      <c r="AL99" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="AM99" s="95">
-        <f t="shared" si="26"/>
+      <c r="AM99" s="88">
+        <f t="shared" si="32"/>
         <v>0.98713826366559487</v>
       </c>
-      <c r="AN99" s="96">
-        <f t="shared" si="27"/>
+      <c r="AN99" s="89">
+        <f t="shared" si="33"/>
         <v>0.5423728813559322</v>
       </c>
-      <c r="AO99" s="96">
-        <f t="shared" si="28"/>
+      <c r="AO99" s="89">
+        <f t="shared" si="34"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="AP99" s="97">
-        <f t="shared" si="29"/>
+      <c r="AP99" s="90">
+        <f t="shared" si="35"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR99" s="4"/>

--- a/excel/1. Bi-monthly d-set calculations.xlsx
+++ b/excel/1. Bi-monthly d-set calculations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAPTOP 35\Desktop\PhD\2. Fuzzy (1-IJMEMS)\git\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD09A620-A49D-4F78-9206-46BB4A9FA335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDFBBCD-5A6F-488B-BDED-E9A7620311CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{88C08D68-2E9A-4EC7-8AF8-2F1D08621B1E}"/>
   </bookViews>
@@ -456,7 +456,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,8 +512,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -554,6 +561,11 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -1350,10 +1362,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1488,7 +1501,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1618,8 +1630,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1627,6 +1637,54 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1642,56 +1700,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1953,52 +1968,52 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>9.5692001688647374E-2</c:v>
+                  <c:v>9.6369885454017132E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.24785972406491297</c:v>
+                  <c:v>0.24833823368582444</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.7125272970140286E-2</c:v>
+                  <c:v>9.7614204835461044E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1856217383612285</c:v>
+                  <c:v>0.18637685407710242</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.6348326566344313E-2</c:v>
+                  <c:v>7.6703968838989084E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.9329888954713031E-2</c:v>
+                  <c:v>2.0531894246230066E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.4487681982756856E-3</c:v>
+                  <c:v>9.8919201833162686E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.13184769092129592</c:v>
+                  <c:v>0.13221987478717093</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.24360795985716413</c:v>
+                  <c:v>0.24415842848624017</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.1014576639333287E-3</c:v>
+                  <c:v>6.693947502576598E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.12533895113769858</c:v>
+                  <c:v>0.12612626007392394</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.6169443219217416E-2</c:v>
+                  <c:v>6.6889599614389242E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.6364700817106227E-2</c:v>
+                  <c:v>9.6730085783356873E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.5717500435727056E-2</c:v>
+                  <c:v>2.6410661333719249E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.6400004831139305E-2</c:v>
+                  <c:v>4.6645761166413349E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2056,7 +2071,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6EB45485-4FE8-444E-A797-AFA3ACB6C592}" type="CELLRANGE">
+                    <a:fld id="{5E6B3B13-023C-4AE4-9F1A-857EA59F00C9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2088,7 +2103,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{71DFF97F-E37D-4414-AC9B-A8F2B75B184D}" type="CELLRANGE">
+                    <a:fld id="{A6B64476-5217-4CB4-AC36-9271ED4B1550}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2121,7 +2136,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4442DF2C-FF6D-4B28-B879-869358D956F7}" type="CELLRANGE">
+                    <a:fld id="{8F0BE45C-10D3-4DC0-8ABE-5BE694E26E71}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2154,7 +2169,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6B9BFE07-BD0C-421C-A200-FE73964D2D04}" type="CELLRANGE">
+                    <a:fld id="{61B94AC4-EB20-4AF2-A63E-E602063738FD}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2187,7 +2202,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7520B783-3629-49D6-9041-B2CCE8BE0DAE}" type="CELLRANGE">
+                    <a:fld id="{C4A5CE0B-E400-428C-BD06-B85930AF9624}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2220,7 +2235,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F36B9F98-F97F-4C88-B699-D59DFFB29414}" type="CELLRANGE">
+                    <a:fld id="{B3E64F13-557E-418D-B663-E73A3FF2079C}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2253,7 +2268,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DCF4ABC3-B6C6-4049-A739-DCB2882B3FF9}" type="CELLRANGE">
+                    <a:fld id="{A427F1FD-F899-41F9-B1AC-BD1828A4D800}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2286,7 +2301,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{664FA44D-2D6D-4523-A1B1-56AD8A09ED05}" type="CELLRANGE">
+                    <a:fld id="{22B23D7A-93BB-4930-BD31-C4F25385DCC5}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2319,7 +2334,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{929B35B0-0826-4EE8-B297-1246F29FA72F}" type="CELLRANGE">
+                    <a:fld id="{C91E20E2-1FDA-4E50-98FD-F770D790C7EC}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2352,7 +2367,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A800A030-32F0-49B0-B092-F032BC357A97}" type="CELLRANGE">
+                    <a:fld id="{04FF598E-B9A1-4DA2-858A-362DEAD7A113}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2385,7 +2400,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B767B962-A02F-48C2-BEDA-22E1335B649A}" type="CELLRANGE">
+                    <a:fld id="{A6C8E254-C1C5-488F-9FBC-560A38C568E6}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2418,7 +2433,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{851E9BC5-5191-4511-88C8-9BD4F8EF1DE2}" type="CELLRANGE">
+                    <a:fld id="{1E07348B-AE7B-4067-B3D7-D7C5DB0ADC40}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2451,7 +2466,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C571CA8D-71E1-4251-9609-1A10BA262B68}" type="CELLRANGE">
+                    <a:fld id="{B98EF6C6-7D84-4DED-B6EE-5DE353B5AAED}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2484,7 +2499,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{01901D6B-1276-438C-ABFB-C083B5F0263E}" type="CELLRANGE">
+                    <a:fld id="{267FB28B-D776-42A7-AF09-5B7F54F775EA}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2517,7 +2532,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{29E84C6E-3A1A-448B-9DBF-7F57D0EB24FE}" type="CELLRANGE">
+                    <a:fld id="{1D5CAC42-E542-482C-8271-0B4435474CDB}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2550,7 +2565,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F24EBA69-6FC2-4C6F-95FA-7621740B2D0F}" type="CELLRANGE">
+                    <a:fld id="{4A301663-72E2-4F82-A492-F4571B56F839}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2696,52 +2711,52 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.69514697580722284</c:v>
+                  <c:v>0.69558444326789226</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.41837298407203521</c:v>
+                  <c:v>0.41853373684141015</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.58512891391484234</c:v>
+                  <c:v>0.58565764012232724</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.68655732289201454</c:v>
+                  <c:v>0.68709117866230196</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.52735653607068889</c:v>
+                  <c:v>0.52769390374230329</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.70573211816674031</c:v>
+                  <c:v>0.70664665079785571</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.60363880524245672</c:v>
+                  <c:v>0.60372245581113004</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.7201266203540666</c:v>
+                  <c:v>0.72046915796877575</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.61621603296852046</c:v>
+                  <c:v>0.61682042057980135</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.75067520916190289</c:v>
+                  <c:v>0.75066647428127986</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.6652961850344622</c:v>
+                  <c:v>0.66584697024151795</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.55798110091559416</c:v>
+                  <c:v>0.55852885025301613</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.58578531837909842</c:v>
+                  <c:v>0.5862022261994122</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.74860905335020655</c:v>
+                  <c:v>0.74868909075144574</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.4852862351914235</c:v>
+                  <c:v>0.48572066159438559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2754,25 +2769,25 @@
                 <c15:dlblRangeCache>
                   <c:ptCount val="16"/>
                   <c:pt idx="0">
-                    <c:v>0.695</c:v>
+                    <c:v>0.696</c:v>
                   </c:pt>
                   <c:pt idx="1">
                     <c:v>1.000</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>0.418</c:v>
+                    <c:v>0.419</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>0.585</c:v>
+                    <c:v>0.586</c:v>
                   </c:pt>
                   <c:pt idx="4">
                     <c:v>0.687</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>0.527</c:v>
+                    <c:v>0.528</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>0.706</c:v>
+                    <c:v>0.707</c:v>
                   </c:pt>
                   <c:pt idx="7">
                     <c:v>0.604</c:v>
@@ -2781,16 +2796,16 @@
                     <c:v>0.720</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>0.616</c:v>
+                    <c:v>0.617</c:v>
                   </c:pt>
                   <c:pt idx="10">
                     <c:v>0.751</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>0.665</c:v>
+                    <c:v>0.666</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>0.558</c:v>
+                    <c:v>0.559</c:v>
                   </c:pt>
                   <c:pt idx="13">
                     <c:v>0.586</c:v>
@@ -2799,7 +2814,7 @@
                     <c:v>0.749</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>0.485</c:v>
+                    <c:v>0.486</c:v>
                   </c:pt>
                 </c15:dlblRangeCache>
               </c15:datalabelsRange>
@@ -3970,26 +3985,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="73"/>
-      <c r="C1" s="73" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="23"/>
-      <c r="C3" s="69" t="s">
+      <c r="C3" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="69" t="s">
+      <c r="F3" s="68" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4000,10 +4015,10 @@
       <c r="C4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="70">
+      <c r="D4" s="69">
         <v>45170</v>
       </c>
-      <c r="E4" s="70">
+      <c r="E4" s="69">
         <v>45199</v>
       </c>
       <c r="F4" s="8">
@@ -4017,10 +4032,10 @@
       <c r="C5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="70">
+      <c r="D5" s="69">
         <v>45200</v>
       </c>
-      <c r="E5" s="70">
+      <c r="E5" s="69">
         <v>45230</v>
       </c>
       <c r="F5" s="8">
@@ -4034,10 +4049,10 @@
       <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="70">
+      <c r="D6" s="69">
         <v>45231</v>
       </c>
-      <c r="E6" s="70">
+      <c r="E6" s="69">
         <v>45260</v>
       </c>
       <c r="F6" s="8">
@@ -4051,10 +4066,10 @@
       <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="69">
         <v>45261</v>
       </c>
-      <c r="E7" s="70">
+      <c r="E7" s="69">
         <v>45291</v>
       </c>
       <c r="F7" s="8">
@@ -4068,10 +4083,10 @@
       <c r="C8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="70">
+      <c r="D8" s="69">
         <v>45292</v>
       </c>
-      <c r="E8" s="70">
+      <c r="E8" s="69">
         <v>45322</v>
       </c>
       <c r="F8" s="8">
@@ -4085,10 +4100,10 @@
       <c r="C9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="70">
+      <c r="D9" s="69">
         <v>45323</v>
       </c>
-      <c r="E9" s="70">
+      <c r="E9" s="69">
         <v>45351</v>
       </c>
       <c r="F9" s="8">
@@ -4102,10 +4117,10 @@
       <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="70">
+      <c r="D10" s="69">
         <v>45352</v>
       </c>
-      <c r="E10" s="70">
+      <c r="E10" s="69">
         <v>45382</v>
       </c>
       <c r="F10" s="8">
@@ -4119,10 +4134,10 @@
       <c r="C11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="70">
+      <c r="D11" s="69">
         <v>45383</v>
       </c>
-      <c r="E11" s="70">
+      <c r="E11" s="69">
         <v>45412</v>
       </c>
       <c r="F11" s="8">
@@ -4136,10 +4151,10 @@
       <c r="C12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="70">
+      <c r="D12" s="69">
         <v>45413</v>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="69">
         <v>45443</v>
       </c>
       <c r="F12" s="8">
@@ -4153,10 +4168,10 @@
       <c r="C13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="70">
+      <c r="D13" s="69">
         <v>45444</v>
       </c>
-      <c r="E13" s="70">
+      <c r="E13" s="69">
         <v>45473</v>
       </c>
       <c r="F13" s="8">
@@ -4170,10 +4185,10 @@
       <c r="C14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="70">
+      <c r="D14" s="69">
         <v>45474</v>
       </c>
-      <c r="E14" s="70">
+      <c r="E14" s="69">
         <v>45504</v>
       </c>
       <c r="F14" s="8">
@@ -4187,10 +4202,10 @@
       <c r="C15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="70">
+      <c r="D15" s="69">
         <v>45505</v>
       </c>
-      <c r="E15" s="70">
+      <c r="E15" s="69">
         <v>45535</v>
       </c>
       <c r="F15" s="8">
@@ -4201,10 +4216,10 @@
       <c r="B16" s="6"/>
     </row>
     <row r="17" spans="5:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="71" t="s">
+      <c r="E17" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="F17" s="72">
+      <c r="F17" s="71">
         <f>SUM(F4:F15)</f>
         <v>8484</v>
       </c>
@@ -5864,7 +5879,7 @@
     <col min="20" max="20" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="24" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="17.5703125" customWidth="1"/>
     <col min="28" max="28" width="20.140625" customWidth="1"/>
     <col min="29" max="29" width="21" customWidth="1"/>
@@ -5898,110 +5913,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="T1" s="134" t="s">
+      <c r="T1" s="120" t="s">
         <v>129</v>
       </c>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-      <c r="W1" s="134"/>
-      <c r="X1" s="134"/>
-      <c r="Y1" s="134"/>
-      <c r="Z1" s="134"/>
-      <c r="AA1" s="134"/>
-      <c r="AB1" s="134"/>
-      <c r="AC1" s="134"/>
-      <c r="AD1" s="134"/>
-      <c r="AF1" s="134" t="s">
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
+      <c r="AC1" s="120"/>
+      <c r="AD1" s="120"/>
+      <c r="AF1" s="120" t="s">
         <v>130</v>
       </c>
-      <c r="AG1" s="134"/>
-      <c r="AH1" s="134"/>
-      <c r="AI1" s="134"/>
-      <c r="AJ1" s="134"/>
-      <c r="AK1" s="134"/>
-      <c r="AL1" s="134"/>
-      <c r="AM1" s="134"/>
-      <c r="AN1" s="134"/>
-      <c r="AO1" s="134"/>
-      <c r="AP1" s="134"/>
-      <c r="AQ1" s="134"/>
-      <c r="AR1" s="134"/>
-      <c r="AS1" s="134"/>
-      <c r="AT1" s="134"/>
-      <c r="AU1" s="134"/>
-      <c r="AV1" s="134"/>
-      <c r="AW1" s="134"/>
-      <c r="AX1" s="134"/>
-      <c r="AY1" s="134"/>
-      <c r="AZ1" s="134"/>
-      <c r="BA1" s="134"/>
-      <c r="BB1" s="134"/>
-      <c r="BC1" s="134"/>
-      <c r="BD1" s="134"/>
-      <c r="BE1" s="134"/>
-      <c r="BF1" s="134"/>
-      <c r="BG1" s="134"/>
-      <c r="BH1" s="134"/>
-      <c r="BI1" s="134"/>
-      <c r="BJ1" s="134"/>
-      <c r="BK1" s="134"/>
-      <c r="BL1" s="134"/>
-      <c r="BM1" s="134"/>
-      <c r="BN1" s="134"/>
-      <c r="BO1" s="134"/>
-      <c r="BP1" s="134"/>
-      <c r="BQ1" s="134"/>
-      <c r="BR1" s="134"/>
-      <c r="BS1" s="134"/>
-      <c r="BT1" s="134"/>
-      <c r="BU1" s="134"/>
-      <c r="BV1" s="134"/>
-      <c r="BW1" s="134"/>
-      <c r="BX1" s="134"/>
-      <c r="BY1" s="134"/>
-      <c r="BZ1" s="134"/>
-      <c r="CA1" s="134"/>
-      <c r="CB1" s="134"/>
-      <c r="CC1" s="134"/>
-      <c r="CD1" s="134"/>
-      <c r="CE1" s="134"/>
-      <c r="CF1" s="134"/>
-      <c r="CG1" s="134"/>
-      <c r="CH1" s="134"/>
-      <c r="CI1" s="134"/>
-      <c r="CJ1" s="134"/>
-      <c r="CK1" s="134"/>
-      <c r="CL1" s="134"/>
-      <c r="CM1" s="134"/>
-      <c r="CN1" s="134"/>
-      <c r="CO1" s="134"/>
-      <c r="CP1" s="134"/>
-      <c r="CQ1" s="134"/>
-      <c r="CR1" s="134"/>
-      <c r="CS1" s="134"/>
-      <c r="CT1" s="134"/>
-      <c r="CU1" s="134"/>
-      <c r="CV1" s="134"/>
-      <c r="CW1" s="134"/>
-      <c r="CX1" s="134"/>
-      <c r="CY1" s="134"/>
-      <c r="CZ1" s="134"/>
-      <c r="DA1" s="134"/>
-      <c r="DB1" s="134"/>
-      <c r="DC1" s="134"/>
-      <c r="DE1" s="133" t="s">
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="120"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
+      <c r="AK1" s="120"/>
+      <c r="AL1" s="120"/>
+      <c r="AM1" s="120"/>
+      <c r="AN1" s="120"/>
+      <c r="AO1" s="120"/>
+      <c r="AP1" s="120"/>
+      <c r="AQ1" s="120"/>
+      <c r="AR1" s="120"/>
+      <c r="AS1" s="120"/>
+      <c r="AT1" s="120"/>
+      <c r="AU1" s="120"/>
+      <c r="AV1" s="120"/>
+      <c r="AW1" s="120"/>
+      <c r="AX1" s="120"/>
+      <c r="AY1" s="120"/>
+      <c r="AZ1" s="120"/>
+      <c r="BA1" s="120"/>
+      <c r="BB1" s="120"/>
+      <c r="BC1" s="120"/>
+      <c r="BD1" s="120"/>
+      <c r="BE1" s="120"/>
+      <c r="BF1" s="120"/>
+      <c r="BG1" s="120"/>
+      <c r="BH1" s="120"/>
+      <c r="BI1" s="120"/>
+      <c r="BJ1" s="120"/>
+      <c r="BK1" s="120"/>
+      <c r="BL1" s="120"/>
+      <c r="BM1" s="120"/>
+      <c r="BN1" s="120"/>
+      <c r="BO1" s="120"/>
+      <c r="BP1" s="120"/>
+      <c r="BQ1" s="120"/>
+      <c r="BR1" s="120"/>
+      <c r="BS1" s="120"/>
+      <c r="BT1" s="120"/>
+      <c r="BU1" s="120"/>
+      <c r="BV1" s="120"/>
+      <c r="BW1" s="120"/>
+      <c r="BX1" s="120"/>
+      <c r="BY1" s="120"/>
+      <c r="BZ1" s="120"/>
+      <c r="CA1" s="120"/>
+      <c r="CB1" s="120"/>
+      <c r="CC1" s="120"/>
+      <c r="CD1" s="120"/>
+      <c r="CE1" s="120"/>
+      <c r="CF1" s="120"/>
+      <c r="CG1" s="120"/>
+      <c r="CH1" s="120"/>
+      <c r="CI1" s="120"/>
+      <c r="CJ1" s="120"/>
+      <c r="CK1" s="120"/>
+      <c r="CL1" s="120"/>
+      <c r="CM1" s="120"/>
+      <c r="CN1" s="120"/>
+      <c r="CO1" s="120"/>
+      <c r="CP1" s="120"/>
+      <c r="CQ1" s="120"/>
+      <c r="CR1" s="120"/>
+      <c r="CS1" s="120"/>
+      <c r="CT1" s="120"/>
+      <c r="CU1" s="120"/>
+      <c r="CV1" s="120"/>
+      <c r="CW1" s="120"/>
+      <c r="CX1" s="120"/>
+      <c r="CY1" s="120"/>
+      <c r="CZ1" s="120"/>
+      <c r="DA1" s="120"/>
+      <c r="DB1" s="120"/>
+      <c r="DC1" s="120"/>
+      <c r="DE1" s="118" t="s">
         <v>131</v>
       </c>
-      <c r="DF1" s="133"/>
-      <c r="DG1" s="133"/>
-      <c r="DH1" s="133"/>
-      <c r="DI1" s="133"/>
-      <c r="DM1" s="61" t="s">
+      <c r="DF1" s="118"/>
+      <c r="DG1" s="118"/>
+      <c r="DH1" s="118"/>
+      <c r="DI1" s="118"/>
+      <c r="DM1" s="60" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="72" t="s">
         <v>127</v>
       </c>
       <c r="H2" t="s">
@@ -6013,19 +6028,19 @@
       <c r="AF2" t="s">
         <v>54</v>
       </c>
-      <c r="AL2" s="73" t="s">
+      <c r="AL2" s="72" t="s">
         <v>128</v>
       </c>
       <c r="AR2" t="s">
         <v>124</v>
       </c>
-      <c r="BD2" s="100" t="s">
+      <c r="BD2" s="99" t="s">
         <v>133</v>
       </c>
-      <c r="BE2" s="101"/>
-      <c r="BF2" s="101"/>
-      <c r="BG2" s="101"/>
-      <c r="BH2" s="102"/>
+      <c r="BE2" s="100"/>
+      <c r="BF2" s="100"/>
+      <c r="BG2" s="100"/>
+      <c r="BH2" s="101"/>
       <c r="BJ2" t="s">
         <v>55</v>
       </c>
@@ -6052,22 +6067,22 @@
       </c>
     </row>
     <row r="3" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="76" t="s">
+      <c r="F3" s="75" t="s">
         <v>51</v>
       </c>
       <c r="H3" s="29" t="s">
@@ -6138,7 +6153,7 @@
         <v>67</v>
       </c>
       <c r="AK3" s="33"/>
-      <c r="AL3" s="74" t="s">
+      <c r="AL3" s="73" t="s">
         <v>48</v>
       </c>
       <c r="AM3" s="34" t="s">
@@ -6187,7 +6202,7 @@
         <v>67</v>
       </c>
       <c r="BC3" s="12"/>
-      <c r="BD3" s="74" t="s">
+      <c r="BD3" s="73" t="s">
         <v>48</v>
       </c>
       <c r="BE3" s="34" t="s">
@@ -6204,50 +6219,50 @@
       </c>
       <c r="BI3" s="12"/>
       <c r="BJ3" s="15"/>
-      <c r="BK3" s="135" t="s">
+      <c r="BK3" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="BL3" s="135"/>
-      <c r="BM3" s="135"/>
-      <c r="BN3" s="135"/>
-      <c r="BO3" s="135" t="s">
+      <c r="BL3" s="121"/>
+      <c r="BM3" s="121"/>
+      <c r="BN3" s="121"/>
+      <c r="BO3" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="BP3" s="135"/>
-      <c r="BQ3" s="135"/>
-      <c r="BR3" s="136"/>
+      <c r="BP3" s="121"/>
+      <c r="BQ3" s="121"/>
+      <c r="BR3" s="122"/>
       <c r="BS3" s="12"/>
       <c r="BT3" s="12"/>
       <c r="BU3" s="15"/>
-      <c r="BV3" s="135" t="s">
+      <c r="BV3" s="121" t="s">
         <v>134</v>
       </c>
-      <c r="BW3" s="135"/>
-      <c r="BX3" s="135"/>
-      <c r="BY3" s="135"/>
-      <c r="BZ3" s="135" t="s">
+      <c r="BW3" s="121"/>
+      <c r="BX3" s="121"/>
+      <c r="BY3" s="121"/>
+      <c r="BZ3" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="CA3" s="135"/>
-      <c r="CB3" s="135"/>
-      <c r="CC3" s="136"/>
+      <c r="CA3" s="121"/>
+      <c r="CB3" s="121"/>
+      <c r="CC3" s="122"/>
       <c r="CD3" s="9"/>
-      <c r="CF3" s="122" t="s">
+      <c r="CF3" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="CG3" s="122"/>
-      <c r="CH3" s="122" t="s">
+      <c r="CG3" s="119"/>
+      <c r="CH3" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="CI3" s="122"/>
-      <c r="CJ3" s="122" t="s">
+      <c r="CI3" s="119"/>
+      <c r="CJ3" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="CK3" s="122"/>
-      <c r="CL3" s="122" t="s">
+      <c r="CK3" s="119"/>
+      <c r="CL3" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="CM3" s="122"/>
+      <c r="CM3" s="119"/>
       <c r="CO3" s="40" t="s">
         <v>74</v>
       </c>
@@ -6270,10 +6285,10 @@
       <c r="DC3" t="s">
         <v>78</v>
       </c>
-      <c r="DF3" s="132" t="s">
+      <c r="DF3" s="117" t="s">
         <v>79</v>
       </c>
-      <c r="DG3" s="132"/>
+      <c r="DG3" s="117"/>
       <c r="DH3" t="s">
         <v>80</v>
       </c>
@@ -6288,19 +6303,19 @@
       <c r="A4" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="78">
+      <c r="B4" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="77">
         <v>6</v>
       </c>
-      <c r="D4" s="78">
+      <c r="D4" s="77">
         <v>32</v>
       </c>
-      <c r="E4" s="78">
+      <c r="E4" s="77">
         <v>2</v>
       </c>
-      <c r="F4" s="79">
+      <c r="F4" s="78">
         <v>0</v>
       </c>
       <c r="H4" s="42" t="s">
@@ -6385,19 +6400,19 @@
       <c r="AL4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AM4" s="84">
+      <c r="AM4" s="83">
         <f t="shared" ref="AM4:AM35" si="0">(AG$4-C4)/(AG$4-AG$5)</f>
         <v>0.98070739549839225</v>
       </c>
-      <c r="AN4" s="85">
+      <c r="AN4" s="84">
         <f t="shared" ref="AN4:AN35" si="1">(D4-AH$5)/(AH$4-AH$5)</f>
         <v>0.1807909604519774</v>
       </c>
-      <c r="AO4" s="85">
+      <c r="AO4" s="84">
         <f t="shared" ref="AO4:AO35" si="2">(E4-AI$5)/(AI$4-AI$5)</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP4" s="86">
+      <c r="AP4" s="85">
         <f t="shared" ref="AP4:AP35" si="3">(AJ$4-F4)/(AJ$4-AJ$5)</f>
         <v>1</v>
       </c>
@@ -6438,19 +6453,19 @@
       <c r="BD4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="BE4" s="84">
+      <c r="BE4" s="83">
         <f>1-AM4</f>
         <v>1.9292604501607746E-2</v>
       </c>
-      <c r="BF4" s="85">
+      <c r="BF4" s="84">
         <f t="shared" ref="BF4:BH4" si="4">1-AN4</f>
         <v>0.8192090395480226</v>
       </c>
-      <c r="BG4" s="85">
+      <c r="BG4" s="84">
         <f t="shared" si="4"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH4" s="86">
+      <c r="BH4" s="85">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6534,10 +6549,12 @@
         <v>0.55172413793103448</v>
       </c>
       <c r="CL4" s="54">
-        <v>0.22727272727272727</v>
+        <f>V37</f>
+        <v>0.22988505747126436</v>
       </c>
       <c r="CM4" s="54">
-        <v>0.375</v>
+        <f>V38</f>
+        <v>0.37931034482758619</v>
       </c>
       <c r="CO4" s="40" t="s">
         <v>91</v>
@@ -6559,33 +6576,33 @@
       </c>
       <c r="DB4" s="14">
         <f t="shared" si="5"/>
-        <v>6.6633535266871269E-2</v>
+        <v>6.6974070233682736E-2</v>
       </c>
       <c r="DC4" s="14">
         <f t="shared" si="5"/>
-        <v>0.27296731419937559</v>
+        <v>0.27413121406808477</v>
       </c>
       <c r="DE4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="DF4" s="14">
         <f t="shared" ref="DF4:DF19" si="6">CZ4-DC4</f>
-        <v>-0.23953827130322378</v>
+        <v>-0.24070217117193296</v>
       </c>
       <c r="DG4" s="14">
         <f t="shared" ref="DG4:DG19" si="7">DA4-DB4</f>
-        <v>0.16549196441028208</v>
-      </c>
-      <c r="DH4" s="97">
+        <v>0.16515142944347061</v>
+      </c>
+      <c r="DH4" s="96">
         <f t="shared" ref="DH4:DH19" si="8">(DF4+$DF$21)/($DF$21+$DG$21)</f>
-        <v>9.5692001688647374E-2</v>
-      </c>
-      <c r="DI4" s="55">
+        <v>9.6369885454017132E-2</v>
+      </c>
+      <c r="DI4" s="54">
         <f t="shared" ref="DI4:DI19" si="9">(DG4+$DF$21)/($DF$21+$DG$21)</f>
-        <v>0.69514697580722284</v>
+        <v>0.69558444326789226</v>
       </c>
       <c r="DK4" s="14"/>
-      <c r="DM4" s="137">
+      <c r="DM4" s="114">
         <f>RANK(DH4,$DH$4:$DH$19,0)</f>
         <v>8</v>
       </c>
@@ -6643,7 +6660,7 @@
       <c r="R5" s="26">
         <v>0</v>
       </c>
-      <c r="T5" s="57" t="s">
+      <c r="T5" s="56" t="s">
         <v>92</v>
       </c>
       <c r="U5" s="52">
@@ -6664,7 +6681,7 @@
       <c r="AB5" t="s">
         <v>94</v>
       </c>
-      <c r="AC5" s="58" t="s">
+      <c r="AC5" s="57" t="s">
         <v>95</v>
       </c>
       <c r="AD5" s="19" t="s">
@@ -6704,7 +6721,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP5" s="87">
+      <c r="AP5" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6757,7 +6774,7 @@
         <f t="shared" ref="BG5:BG68" si="12">1-AO5</f>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH5" s="87">
+      <c r="BH5" s="86">
         <f t="shared" ref="BH5:BH68" si="13">1-AP5</f>
         <v>0</v>
       </c>
@@ -6793,7 +6810,7 @@
         <f t="shared" ref="BQ5:BQ20" si="20">MAX(AO4,AO20,AO36,AO52,AO68,AO84)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="BR5" s="56">
+      <c r="BR5" s="55">
         <f t="shared" ref="BR5:BR20" si="21">MAX(AP4,AP20,AP36,AP52,AP68,AP84)</f>
         <v>1</v>
       </c>
@@ -6830,51 +6847,51 @@
         <f t="shared" si="23"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="CC5" s="56">
+      <c r="CC5" s="55">
         <f t="shared" si="23"/>
         <v>0.33333333333333337</v>
       </c>
       <c r="CD5" s="13"/>
       <c r="CE5" s="33"/>
-      <c r="CF5" s="126" t="s">
+      <c r="CF5" s="123" t="s">
         <v>40</v>
       </c>
-      <c r="CG5" s="125"/>
-      <c r="CH5" s="126" t="s">
+      <c r="CG5" s="124"/>
+      <c r="CH5" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="CI5" s="125"/>
-      <c r="CJ5" s="126" t="s">
+      <c r="CI5" s="124"/>
+      <c r="CJ5" s="123" t="s">
         <v>40</v>
       </c>
-      <c r="CK5" s="125"/>
-      <c r="CL5" s="126" t="s">
+      <c r="CK5" s="124"/>
+      <c r="CL5" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="CM5" s="125"/>
+      <c r="CM5" s="124"/>
       <c r="CO5" s="41"/>
-      <c r="CP5" s="59" t="s">
+      <c r="CP5" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="CQ5" s="59" t="s">
+      <c r="CQ5" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="CR5" s="59" t="s">
+      <c r="CR5" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="CS5" s="59" t="s">
+      <c r="CS5" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="CT5" s="59" t="s">
+      <c r="CT5" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="CU5" s="59" t="s">
+      <c r="CU5" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="CV5" s="59" t="s">
+      <c r="CV5" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="CW5" s="59" t="s">
+      <c r="CW5" s="58" t="s">
         <v>100</v>
       </c>
       <c r="CY5" s="4" t="s">
@@ -6890,33 +6907,33 @@
       </c>
       <c r="DB5" s="14">
         <f t="shared" si="5"/>
-        <v>1.1771348504938285E-2</v>
+        <v>1.1906651361316887E-2</v>
       </c>
       <c r="DC5" s="14">
         <f t="shared" si="5"/>
-        <v>0.16601104765574823</v>
+        <v>0.16705964479268237</v>
       </c>
       <c r="DE5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="DF5" s="14">
         <f t="shared" si="6"/>
-        <v>-0.13672399646520245</v>
+        <v>-0.13777259360213659</v>
       </c>
       <c r="DG5" s="14">
         <f t="shared" si="7"/>
-        <v>0.37147022395901624</v>
-      </c>
-      <c r="DH5" s="97">
+        <v>0.37133492110263761</v>
+      </c>
+      <c r="DH5" s="96">
         <f t="shared" si="8"/>
-        <v>0.24785972406491297</v>
-      </c>
-      <c r="DI5" s="55">
+        <v>0.24833823368582444</v>
+      </c>
+      <c r="DI5" s="54">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="DK5" s="14"/>
-      <c r="DM5" s="138">
+      <c r="DM5" s="115">
         <f t="shared" ref="DM5:DM19" si="24">RANK(DH5,$DH$4:$DH$19,0)</f>
         <v>1</v>
       </c>
@@ -6974,7 +6991,7 @@
       <c r="R6" s="26">
         <v>1</v>
       </c>
-      <c r="T6" s="60" t="s">
+      <c r="T6" s="59" t="s">
         <v>37</v>
       </c>
       <c r="U6" s="52">
@@ -7029,7 +7046,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP6" s="87">
+      <c r="AP6" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -7082,7 +7099,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH6" s="87">
+      <c r="BH6" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -7118,7 +7135,7 @@
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
-      <c r="BR6" s="56">
+      <c r="BR6" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -7155,34 +7172,34 @@
         <f t="shared" ref="CB6:CB20" si="31">MAX(BG5,BG21,BG37,BG53,BG69,BG85)</f>
         <v>0.92307692307692313</v>
       </c>
-      <c r="CC6" s="56">
+      <c r="CC6" s="55">
         <f t="shared" ref="CC6:CC20" si="32">MAX(BH5,BH21,BH37,BH53,BH69,BH85)</f>
         <v>0.11111111111111116</v>
       </c>
       <c r="CD6" s="13"/>
       <c r="CE6" s="41"/>
-      <c r="CF6" s="107" t="s">
+      <c r="CF6" s="106" t="s">
         <v>97</v>
       </c>
-      <c r="CG6" s="107" t="s">
+      <c r="CG6" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="CH6" s="107" t="s">
+      <c r="CH6" s="106" t="s">
         <v>97</v>
       </c>
-      <c r="CI6" s="107" t="s">
+      <c r="CI6" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="CJ6" s="107" t="s">
+      <c r="CJ6" s="106" t="s">
         <v>99</v>
       </c>
-      <c r="CK6" s="107" t="s">
+      <c r="CK6" s="106" t="s">
         <v>100</v>
       </c>
-      <c r="CL6" s="107" t="s">
+      <c r="CL6" s="106" t="s">
         <v>99</v>
       </c>
-      <c r="CM6" s="107" t="s">
+      <c r="CM6" s="106" t="s">
         <v>100</v>
       </c>
       <c r="CO6" s="4" t="s">
@@ -7214,11 +7231,11 @@
       </c>
       <c r="CV6" s="13">
         <f t="shared" si="33"/>
-        <v>6.3131313131313135E-2</v>
+        <v>6.3856960408684549E-2</v>
       </c>
       <c r="CW6" s="13">
-        <f t="shared" si="33"/>
-        <v>0.21577380952380951</v>
+        <f>CM7*CM$4</f>
+        <v>0.21825396825396823</v>
       </c>
       <c r="CY6" s="4" t="s">
         <v>4</v>
@@ -7233,33 +7250,33 @@
       </c>
       <c r="DB6" s="14">
         <f t="shared" si="5"/>
-        <v>0.13569765415820495</v>
+        <v>0.13668094887487303</v>
       </c>
       <c r="DC6" s="14">
         <f t="shared" si="5"/>
-        <v>0.31639156831959592</v>
+        <v>0.31817203411013428</v>
       </c>
       <c r="DE6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="DF6" s="14">
         <f t="shared" si="6"/>
-        <v>-0.3041939263119075</v>
+        <v>-0.30597439210244587</v>
       </c>
       <c r="DG6" s="14">
         <f t="shared" si="7"/>
-        <v>-2.1514299532565118E-2</v>
-      </c>
-      <c r="DH6" s="97">
+        <v>-2.2497594249233199E-2</v>
+      </c>
+      <c r="DH6" s="96">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="DI6" s="55">
+      <c r="DI6" s="54">
         <f t="shared" si="9"/>
-        <v>0.41837298407203521</v>
+        <v>0.41853373684141015</v>
       </c>
       <c r="DK6" s="14"/>
-      <c r="DM6" s="138">
+      <c r="DM6" s="115">
         <f t="shared" si="24"/>
         <v>16</v>
       </c>
@@ -7348,7 +7365,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP7" s="87">
+      <c r="AP7" s="86">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -7401,7 +7418,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH7" s="87">
+      <c r="BH7" s="86">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
@@ -7437,7 +7454,7 @@
         <f t="shared" si="20"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="BR7" s="56">
+      <c r="BR7" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -7474,43 +7491,43 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC7" s="56">
+      <c r="CC7" s="55">
         <f t="shared" si="32"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="CD7" s="13"/>
-      <c r="CE7" s="106" t="s">
-        <v>1</v>
-      </c>
-      <c r="CF7" s="108">
+      <c r="CE7" s="105" t="s">
+        <v>1</v>
+      </c>
+      <c r="CF7" s="107">
         <f>BK23</f>
         <v>0.37028824833702884</v>
       </c>
-      <c r="CG7" s="109">
+      <c r="CG7" s="108">
         <f>BO23</f>
         <v>0.68070953436807102</v>
       </c>
-      <c r="CH7" s="109">
+      <c r="CH7" s="108">
         <f>BK41</f>
         <v>8.8691796008869058E-3</v>
       </c>
-      <c r="CI7" s="109">
+      <c r="CI7" s="108">
         <f>BO41</f>
         <v>0.31929046563192909</v>
       </c>
-      <c r="CJ7" s="109">
+      <c r="CJ7" s="108">
         <f>BL23</f>
         <v>0.12698412698412698</v>
       </c>
-      <c r="CK7" s="109">
+      <c r="CK7" s="108">
         <f>BP23</f>
         <v>0.42460317460317459</v>
       </c>
-      <c r="CL7" s="109">
+      <c r="CL7" s="108">
         <f>BL41</f>
         <v>0.27777777777777779</v>
       </c>
-      <c r="CM7" s="110">
+      <c r="CM7" s="109">
         <f>BP41</f>
         <v>0.57539682539682535</v>
       </c>
@@ -7543,11 +7560,11 @@
       </c>
       <c r="CV7" s="13">
         <f t="shared" si="33"/>
-        <v>2.5083612040133769E-2</v>
+        <v>2.5371929419905424E-2</v>
       </c>
       <c r="CW7" s="13">
         <f t="shared" si="33"/>
-        <v>0.1943979933110368</v>
+        <v>0.19663245300426707</v>
       </c>
       <c r="CY7" s="4" t="s">
         <v>5</v>
@@ -7562,33 +7579,33 @@
       </c>
       <c r="DB7" s="14">
         <f t="shared" si="5"/>
-        <v>8.926385852261326E-2</v>
+        <v>8.9723580727808741E-2</v>
       </c>
       <c r="DC7" s="14">
         <f t="shared" si="5"/>
-        <v>0.26311324996258983</v>
+        <v>0.2644027707481631</v>
       </c>
       <c r="DE7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="DF7" s="14">
         <f t="shared" si="6"/>
-        <v>-0.23856986128070615</v>
+        <v>-0.23985938206627941</v>
       </c>
       <c r="DG7" s="14">
         <f t="shared" si="7"/>
-        <v>9.1156704107312997E-2</v>
-      </c>
-      <c r="DH7" s="97">
+        <v>9.0696981902117516E-2</v>
+      </c>
+      <c r="DH7" s="96">
         <f t="shared" si="8"/>
-        <v>9.7125272970140286E-2</v>
-      </c>
-      <c r="DI7" s="55">
+        <v>9.7614204835461044E-2</v>
+      </c>
+      <c r="DI7" s="54">
         <f t="shared" si="9"/>
-        <v>0.58512891391484234</v>
+        <v>0.58565764012232724</v>
       </c>
       <c r="DK7" s="14"/>
-      <c r="DM7" s="138">
+      <c r="DM7" s="115">
         <f t="shared" si="24"/>
         <v>6</v>
       </c>
@@ -7675,7 +7692,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP8" s="87">
+      <c r="AP8" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -7728,7 +7745,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH8" s="87">
+      <c r="BH8" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -7764,7 +7781,7 @@
         <f t="shared" si="20"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="BR8" s="56">
+      <c r="BR8" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -7801,15 +7818,15 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC8" s="56">
+      <c r="CC8" s="55">
         <f t="shared" si="32"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="CD8" s="13"/>
-      <c r="CE8" s="106" t="s">
+      <c r="CE8" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="CF8" s="111">
+      <c r="CF8" s="110">
         <f t="shared" ref="CF8:CF22" si="35">BK24</f>
         <v>0.9872204472843451</v>
       </c>
@@ -7837,7 +7854,7 @@
         <f t="shared" ref="CL8:CL21" si="41">BL42</f>
         <v>0.1103678929765886</v>
       </c>
-      <c r="CM8" s="103">
+      <c r="CM8" s="102">
         <f t="shared" ref="CM8:CM21" si="42">BP42</f>
         <v>0.51839464882943143</v>
       </c>
@@ -7870,11 +7887,11 @@
       </c>
       <c r="CV8" s="13">
         <f t="shared" si="33"/>
-        <v>0.18229166666666666</v>
+        <v>0.1843869731800766</v>
       </c>
       <c r="CW8" s="13">
         <f t="shared" si="33"/>
-        <v>0.330078125</v>
+        <v>0.33387212643678155</v>
       </c>
       <c r="CY8" s="4" t="s">
         <v>6</v>
@@ -7889,33 +7906,33 @@
       </c>
       <c r="DB8" s="14">
         <f t="shared" si="5"/>
-        <v>7.2288080710454589E-2</v>
+        <v>7.2577462356071196E-2</v>
       </c>
       <c r="DC8" s="14">
         <f t="shared" si="5"/>
-        <v>0.23732812535231856</v>
+        <v>0.23829176623222181</v>
       </c>
       <c r="DE8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="DF8" s="14">
         <f t="shared" si="6"/>
-        <v>-0.17877597219025632</v>
+        <v>-0.17973961307015957</v>
       </c>
       <c r="DG8" s="14">
         <f t="shared" si="7"/>
-        <v>0.15968824387220579</v>
-      </c>
-      <c r="DH8" s="97">
+        <v>0.15939886222658917</v>
+      </c>
+      <c r="DH8" s="96">
         <f t="shared" si="8"/>
-        <v>0.1856217383612285</v>
-      </c>
-      <c r="DI8" s="55">
+        <v>0.18637685407710242</v>
+      </c>
+      <c r="DI8" s="54">
         <f t="shared" si="9"/>
-        <v>0.68655732289201454</v>
+        <v>0.68709117866230196</v>
       </c>
       <c r="DK8" s="14"/>
-      <c r="DM8" s="138">
+      <c r="DM8" s="115">
         <f t="shared" si="24"/>
         <v>3</v>
       </c>
@@ -8002,7 +8019,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP9" s="87">
+      <c r="AP9" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -8055,7 +8072,7 @@
         <f t="shared" si="12"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH9" s="87">
+      <c r="BH9" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -8091,7 +8108,7 @@
         <f t="shared" si="20"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="BR9" s="56">
+      <c r="BR9" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -8128,15 +8145,15 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC9" s="56">
+      <c r="CC9" s="55">
         <f t="shared" si="32"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="CD9" s="13"/>
-      <c r="CE9" s="106" t="s">
+      <c r="CE9" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="CF9" s="111">
+      <c r="CF9" s="110">
         <f t="shared" si="35"/>
         <v>0.62299465240641705</v>
       </c>
@@ -8164,7 +8181,7 @@
         <f t="shared" si="41"/>
         <v>0.80208333333333326</v>
       </c>
-      <c r="CM9" s="103">
+      <c r="CM9" s="102">
         <f t="shared" si="42"/>
         <v>0.88020833333333326</v>
       </c>
@@ -8197,11 +8214,11 @@
       </c>
       <c r="CV9" s="13">
         <f t="shared" si="33"/>
-        <v>8.5227272727272721E-2</v>
+        <v>8.6206896551724144E-2</v>
       </c>
       <c r="CW9" s="13">
         <f t="shared" si="33"/>
-        <v>0.23906250000000001</v>
+        <v>0.24181034482758623</v>
       </c>
       <c r="CY9" s="4" t="s">
         <v>8</v>
@@ -8216,33 +8233,33 @@
       </c>
       <c r="DB9" s="14">
         <f t="shared" si="5"/>
-        <v>0.10932296625395384</v>
+        <v>0.11000734235230308</v>
       </c>
       <c r="DC9" s="14">
         <f t="shared" si="5"/>
-        <v>0.28845037627015502</v>
+        <v>0.28986435680030959</v>
       </c>
       <c r="DE9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="DF9" s="14">
         <f t="shared" si="6"/>
-        <v>-0.25260809911785148</v>
+        <v>-0.25402207964800605</v>
       </c>
       <c r="DG9" s="14">
         <f t="shared" si="7"/>
-        <v>5.2121979522112213E-2</v>
-      </c>
-      <c r="DH9" s="97">
+        <v>5.1437603423762968E-2</v>
+      </c>
+      <c r="DH9" s="96">
         <f t="shared" si="8"/>
-        <v>7.6348326566344313E-2</v>
-      </c>
-      <c r="DI9" s="55">
+        <v>7.6703968838989084E-2</v>
+      </c>
+      <c r="DI9" s="54">
         <f t="shared" si="9"/>
-        <v>0.52735653607068889</v>
+        <v>0.52769390374230329</v>
       </c>
       <c r="DK9" s="14"/>
-      <c r="DM9" s="138">
+      <c r="DM9" s="115">
         <f t="shared" si="24"/>
         <v>9</v>
       </c>
@@ -8329,7 +8346,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP10" s="87">
+      <c r="AP10" s="86">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -8382,7 +8399,7 @@
         <f t="shared" si="12"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH10" s="87">
+      <c r="BH10" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -8418,7 +8435,7 @@
         <f t="shared" si="20"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="BR10" s="56">
+      <c r="BR10" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -8455,15 +8472,15 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC10" s="56">
+      <c r="CC10" s="55">
         <f t="shared" si="32"/>
         <v>0.33333333333333337</v>
       </c>
       <c r="CD10" s="13"/>
-      <c r="CE10" s="106" t="s">
+      <c r="CE10" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="CF10" s="111">
+      <c r="CF10" s="110">
         <f t="shared" si="35"/>
         <v>0.81470588235294106</v>
       </c>
@@ -8491,7 +8508,7 @@
         <f t="shared" si="41"/>
         <v>0.375</v>
       </c>
-      <c r="CM10" s="103">
+      <c r="CM10" s="102">
         <f t="shared" si="42"/>
         <v>0.63750000000000007</v>
       </c>
@@ -8524,11 +8541,11 @@
       </c>
       <c r="CV10" s="13">
         <f t="shared" si="33"/>
-        <v>5.3648068669527899E-2</v>
+        <v>5.4264713136993742E-2</v>
       </c>
       <c r="CW10" s="13">
         <f t="shared" si="33"/>
-        <v>0.1786480686695279</v>
+        <v>0.18070149474618913</v>
       </c>
       <c r="CY10" s="4" t="s">
         <v>9</v>
@@ -8547,29 +8564,29 @@
       </c>
       <c r="DC10" s="14">
         <f t="shared" si="5"/>
-        <v>0.30881033866580726</v>
+        <v>0.30974487426104963</v>
       </c>
       <c r="DE10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="DF10" s="14">
         <f t="shared" si="6"/>
-        <v>-0.29113341331649001</v>
+        <v>-0.29206794891173238</v>
       </c>
       <c r="DG10" s="14">
         <f t="shared" si="7"/>
         <v>0.17264396562812223</v>
       </c>
-      <c r="DH10" s="97">
+      <c r="DH10" s="96">
         <f t="shared" si="8"/>
-        <v>1.9329888954713031E-2</v>
-      </c>
-      <c r="DI10" s="55">
+        <v>2.0531894246230066E-2</v>
+      </c>
+      <c r="DI10" s="54">
         <f t="shared" si="9"/>
-        <v>0.70573211816674031</v>
+        <v>0.70664665079785571</v>
       </c>
       <c r="DK10" s="14"/>
-      <c r="DM10" s="138">
+      <c r="DM10" s="115">
         <f t="shared" si="24"/>
         <v>13</v>
       </c>
@@ -8656,7 +8673,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP11" s="87">
+      <c r="AP11" s="86">
         <f t="shared" si="3"/>
         <v>0.66666666666666663</v>
       </c>
@@ -8709,7 +8726,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH11" s="87">
+      <c r="BH11" s="86">
         <f t="shared" si="13"/>
         <v>0.33333333333333337</v>
       </c>
@@ -8745,7 +8762,7 @@
         <f t="shared" si="20"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="BR11" s="56">
+      <c r="BR11" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -8782,15 +8799,15 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC11" s="56">
+      <c r="CC11" s="55">
         <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="CD11" s="13"/>
-      <c r="CE11" s="106" t="s">
+      <c r="CE11" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="CF11" s="111">
+      <c r="CF11" s="110">
         <f t="shared" si="35"/>
         <v>0.72988505747126442</v>
       </c>
@@ -8818,7 +8835,7 @@
         <f t="shared" si="41"/>
         <v>0.23605150214592277</v>
       </c>
-      <c r="CM11" s="103">
+      <c r="CM11" s="102">
         <f t="shared" si="42"/>
         <v>0.47639484978540775</v>
       </c>
@@ -8851,11 +8868,11 @@
       </c>
       <c r="CV11" s="13">
         <f t="shared" si="33"/>
-        <v>0.12687555163283318</v>
+        <v>0.12833389130677378</v>
       </c>
       <c r="CW11" s="13">
         <f t="shared" si="33"/>
-        <v>0.26213592233009708</v>
+        <v>0.26514897890860389</v>
       </c>
       <c r="CY11" s="4" t="s">
         <v>10</v>
@@ -8870,33 +8887,33 @@
       </c>
       <c r="DB11" s="14">
         <f t="shared" si="5"/>
-        <v>0.10722278556435305</v>
+        <v>0.10795350985766868</v>
       </c>
       <c r="DC11" s="14">
         <f t="shared" si="5"/>
-        <v>0.33479165506767594</v>
+        <v>0.33625642512836773</v>
       </c>
       <c r="DE11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="DF11" s="14">
         <f t="shared" si="6"/>
-        <v>-0.29780973237611263</v>
+        <v>-0.29927450243680442</v>
       </c>
       <c r="DG11" s="14">
         <f t="shared" si="7"/>
-        <v>0.1036631741027926</v>
-      </c>
-      <c r="DH11" s="97">
+        <v>0.10293244980947698</v>
+      </c>
+      <c r="DH11" s="96">
         <f t="shared" si="8"/>
-        <v>9.4487681982756856E-3</v>
-      </c>
-      <c r="DI11" s="55">
+        <v>9.8919201833162686E-3</v>
+      </c>
+      <c r="DI11" s="54">
         <f t="shared" si="9"/>
-        <v>0.60363880524245672</v>
+        <v>0.60372245581113004</v>
       </c>
       <c r="DK11" s="14"/>
-      <c r="DM11" s="138">
+      <c r="DM11" s="115">
         <f t="shared" si="24"/>
         <v>14</v>
       </c>
@@ -8983,7 +9000,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP12" s="87">
+      <c r="AP12" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -9036,7 +9053,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH12" s="87">
+      <c r="BH12" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -9072,7 +9089,7 @@
         <f t="shared" si="20"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="BR12" s="56">
+      <c r="BR12" s="55">
         <f t="shared" si="21"/>
         <v>0.77777777777777779</v>
       </c>
@@ -9109,15 +9126,15 @@
         <f t="shared" si="31"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="CC12" s="56">
+      <c r="CC12" s="55">
         <f t="shared" si="32"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="CD12" s="13"/>
-      <c r="CE12" s="106" t="s">
+      <c r="CE12" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="CF12" s="111">
+      <c r="CF12" s="110">
         <f t="shared" si="35"/>
         <v>0.80530973451327437</v>
       </c>
@@ -9145,7 +9162,7 @@
         <f t="shared" si="41"/>
         <v>0.55825242718446599</v>
       </c>
-      <c r="CM12" s="103">
+      <c r="CM12" s="102">
         <f t="shared" si="42"/>
         <v>0.69902912621359214</v>
       </c>
@@ -9182,7 +9199,7 @@
       </c>
       <c r="CW12" s="13">
         <f t="shared" si="33"/>
-        <v>0.17325227963525835</v>
+        <v>0.17524368514830727</v>
       </c>
       <c r="CY12" s="4" t="s">
         <v>21</v>
@@ -9197,33 +9214,33 @@
       </c>
       <c r="DB12" s="14">
         <f t="shared" si="43"/>
-        <v>6.1759562461585316E-2</v>
+        <v>6.2123298711849878E-2</v>
       </c>
       <c r="DC12" s="14">
         <f t="shared" si="43"/>
-        <v>0.22188496222198609</v>
+        <v>0.22319643347988438</v>
       </c>
       <c r="DE12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="DF12" s="14">
         <f t="shared" si="6"/>
-        <v>-0.2151091682603867</v>
+        <v>-0.216420639518285</v>
       </c>
       <c r="DG12" s="14">
         <f t="shared" si="7"/>
-        <v>0.18236981471709501</v>
-      </c>
-      <c r="DH12" s="97">
+        <v>0.18200607846683045</v>
+      </c>
+      <c r="DH12" s="96">
         <f t="shared" si="8"/>
-        <v>0.13184769092129592</v>
-      </c>
-      <c r="DI12" s="55">
+        <v>0.13221987478717093</v>
+      </c>
+      <c r="DI12" s="54">
         <f t="shared" si="9"/>
-        <v>0.7201266203540666</v>
+        <v>0.72046915796877575</v>
       </c>
       <c r="DK12" s="14"/>
-      <c r="DM12" s="138">
+      <c r="DM12" s="115">
         <f t="shared" si="24"/>
         <v>4</v>
       </c>
@@ -9310,7 +9327,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP13" s="87">
+      <c r="AP13" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -9363,7 +9380,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH13" s="87">
+      <c r="BH13" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -9399,7 +9416,7 @@
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="BR13" s="56">
+      <c r="BR13" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -9436,15 +9453,15 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC13" s="56">
+      <c r="CC13" s="55">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="CD13" s="13"/>
-      <c r="CE13" s="106" t="s">
+      <c r="CE13" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="CF13" s="111">
+      <c r="CF13" s="110">
         <f t="shared" si="35"/>
         <v>0.47911547911547908</v>
       </c>
@@ -9472,7 +9489,7 @@
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="CM13" s="103">
+      <c r="CM13" s="102">
         <f t="shared" si="42"/>
         <v>0.46200607902735558</v>
       </c>
@@ -9505,11 +9522,11 @@
       </c>
       <c r="CV13" s="13">
         <f t="shared" si="33"/>
-        <v>0.1354679802955665</v>
+        <v>0.13702508351735462</v>
       </c>
       <c r="CW13" s="13">
         <f t="shared" si="33"/>
-        <v>0.27155172413793105</v>
+        <v>0.27467300832342451</v>
       </c>
       <c r="CY13" s="4" t="s">
         <v>11</v>
@@ -9524,33 +9541,33 @@
       </c>
       <c r="DB13" s="14">
         <f t="shared" si="44"/>
-        <v>8.7970901907073393E-2</v>
+        <v>8.8328234562830704E-2</v>
       </c>
       <c r="DC13" s="14">
         <f t="shared" si="44"/>
-        <v>0.20229210782842255</v>
+        <v>0.20329896130383721</v>
       </c>
       <c r="DE13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="DF13" s="14">
         <f t="shared" si="6"/>
-        <v>-0.1395967611157834</v>
+        <v>-0.14060361459119805</v>
       </c>
       <c r="DG13" s="14">
         <f t="shared" si="7"/>
-        <v>0.11216115598708741</v>
-      </c>
-      <c r="DH13" s="97">
+        <v>0.1118038233313301</v>
+      </c>
+      <c r="DH13" s="96">
         <f t="shared" si="8"/>
-        <v>0.24360795985716413</v>
-      </c>
-      <c r="DI13" s="55">
+        <v>0.24415842848624017</v>
+      </c>
+      <c r="DI13" s="54">
         <f t="shared" si="9"/>
-        <v>0.61621603296852046</v>
+        <v>0.61682042057980135</v>
       </c>
       <c r="DK13" s="14"/>
-      <c r="DM13" s="138">
+      <c r="DM13" s="115">
         <f t="shared" si="24"/>
         <v>2</v>
       </c>
@@ -9637,7 +9654,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP14" s="87">
+      <c r="AP14" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -9690,7 +9707,7 @@
         <f t="shared" si="12"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH14" s="87">
+      <c r="BH14" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -9726,7 +9743,7 @@
         <f t="shared" si="20"/>
         <v>0.61538461538461542</v>
       </c>
-      <c r="BR14" s="56">
+      <c r="BR14" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -9763,15 +9780,15 @@
         <f t="shared" si="31"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="CC14" s="56">
+      <c r="CC14" s="55">
         <f t="shared" si="32"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="CD14" s="13"/>
-      <c r="CE14" s="106" t="s">
+      <c r="CE14" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="CF14" s="111">
+      <c r="CF14" s="110">
         <f t="shared" si="35"/>
         <v>0.40384615384615391</v>
       </c>
@@ -9799,7 +9816,7 @@
         <f t="shared" si="41"/>
         <v>0.59605911330049266</v>
       </c>
-      <c r="CM14" s="103">
+      <c r="CM14" s="102">
         <f t="shared" si="42"/>
         <v>0.72413793103448276</v>
       </c>
@@ -9832,11 +9849,11 @@
       </c>
       <c r="CV14" s="13">
         <f t="shared" si="33"/>
-        <v>6.6245413779046053E-2</v>
+        <v>6.7006855316736239E-2</v>
       </c>
       <c r="CW14" s="13">
         <f t="shared" si="33"/>
-        <v>0.18665919282511212</v>
+        <v>0.18880470078861913</v>
       </c>
       <c r="CY14" s="4" t="s">
         <v>12</v>
@@ -9851,33 +9868,33 @@
       </c>
       <c r="DB14" s="14">
         <f t="shared" ref="DB14:DB19" si="47">(CR15+CV15+CR32+CV32)/$T$41</f>
-        <v>6.2355973018900147E-2</v>
+        <v>6.2907371995728489E-2</v>
       </c>
       <c r="DC14" s="14">
         <f t="shared" ref="DC14:DC19" si="48">(CS15+CW15+CS32+CW32)/$T$41</f>
-        <v>0.32341137890436455</v>
+        <v>0.32478050791721741</v>
       </c>
       <c r="DE14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="DF14" s="14">
         <f t="shared" si="6"/>
-        <v>-0.30007139010399198</v>
+        <v>-0.30144051911684483</v>
       </c>
       <c r="DG14" s="14">
         <f t="shared" si="7"/>
-        <v>0.20301040101591758</v>
-      </c>
-      <c r="DH14" s="97">
+        <v>0.20245900203908923</v>
+      </c>
+      <c r="DH14" s="96">
         <f t="shared" si="8"/>
-        <v>6.1014576639333287E-3</v>
-      </c>
-      <c r="DI14" s="55">
+        <v>6.693947502576598E-3</v>
+      </c>
+      <c r="DI14" s="54">
         <f t="shared" si="9"/>
-        <v>0.75067520916190289</v>
+        <v>0.75066647428127986</v>
       </c>
       <c r="DK14" s="14"/>
-      <c r="DM14" s="138">
+      <c r="DM14" s="115">
         <f t="shared" si="24"/>
         <v>15</v>
       </c>
@@ -9964,7 +9981,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="87">
+      <c r="AP15" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10017,7 +10034,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH15" s="87">
+      <c r="BH15" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -10053,7 +10070,7 @@
         <f t="shared" si="20"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="BR15" s="56">
+      <c r="BR15" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -10090,15 +10107,15 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC15" s="56">
+      <c r="CC15" s="55">
         <f t="shared" si="32"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="CD15" s="13"/>
-      <c r="CE15" s="106" t="s">
+      <c r="CE15" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="CF15" s="111">
+      <c r="CF15" s="110">
         <f t="shared" si="35"/>
         <v>0.98089171974522282</v>
       </c>
@@ -10126,7 +10143,7 @@
         <f t="shared" si="41"/>
         <v>0.29147982062780264</v>
       </c>
-      <c r="CM15" s="103">
+      <c r="CM15" s="102">
         <f t="shared" si="42"/>
         <v>0.49775784753363228</v>
       </c>
@@ -10159,11 +10176,11 @@
       </c>
       <c r="CV15" s="13">
         <f t="shared" si="33"/>
-        <v>0.10222310440651053</v>
+        <v>0.10339808261807962</v>
       </c>
       <c r="CW15" s="13">
         <f t="shared" si="33"/>
-        <v>0.25382096069868998</v>
+        <v>0.25673844300557147</v>
       </c>
       <c r="CY15" s="4" t="s">
         <v>13</v>
@@ -10178,33 +10195,33 @@
       </c>
       <c r="DB15" s="14">
         <f t="shared" si="47"/>
-        <v>7.3086808973700138E-2</v>
+        <v>7.3399702190067501E-2</v>
       </c>
       <c r="DC15" s="14">
         <f t="shared" si="48"/>
-        <v>0.2684072067113118</v>
+        <v>0.26944821783035694</v>
       </c>
       <c r="DE15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="DF15" s="14">
         <f t="shared" si="6"/>
-        <v>-0.21950689039560556</v>
+        <v>-0.2205479015146507</v>
       </c>
       <c r="DG15" s="14">
         <f t="shared" si="7"/>
-        <v>0.14532285522788968</v>
-      </c>
-      <c r="DH15" s="97">
+        <v>0.14500996201152233</v>
+      </c>
+      <c r="DH15" s="96">
         <f t="shared" si="8"/>
-        <v>0.12533895113769858</v>
-      </c>
-      <c r="DI15" s="55">
+        <v>0.12612626007392394</v>
+      </c>
+      <c r="DI15" s="54">
         <f t="shared" si="9"/>
-        <v>0.6652961850344622</v>
+        <v>0.66584697024151795</v>
       </c>
       <c r="DK15" s="14"/>
-      <c r="DM15" s="138">
+      <c r="DM15" s="115">
         <f t="shared" si="24"/>
         <v>5</v>
       </c>
@@ -10291,7 +10308,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP16" s="87">
+      <c r="AP16" s="86">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -10344,7 +10361,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH16" s="87">
+      <c r="BH16" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -10380,7 +10397,7 @@
         <f t="shared" si="20"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="BR16" s="56">
+      <c r="BR16" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -10417,15 +10434,15 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC16" s="56">
+      <c r="CC16" s="55">
         <f t="shared" si="32"/>
         <v>0.66666666666666674</v>
       </c>
       <c r="CD16" s="13"/>
-      <c r="CE16" s="106" t="s">
+      <c r="CE16" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="CF16" s="111">
+      <c r="CF16" s="110">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
@@ -10453,7 +10470,7 @@
         <f t="shared" si="41"/>
         <v>0.44978165938864634</v>
       </c>
-      <c r="CM16" s="103">
+      <c r="CM16" s="102">
         <f t="shared" si="42"/>
         <v>0.67685589519650657</v>
       </c>
@@ -10486,11 +10503,11 @@
       </c>
       <c r="CV16" s="13">
         <f t="shared" si="33"/>
-        <v>5.8006846709775593E-2</v>
+        <v>5.8673592074255772E-2</v>
       </c>
       <c r="CW16" s="13">
         <f t="shared" si="33"/>
-        <v>0.19299163179916318</v>
+        <v>0.19520992641754434</v>
       </c>
       <c r="CY16" s="4" t="s">
         <v>14</v>
@@ -10505,33 +10522,33 @@
       </c>
       <c r="DB16" s="14">
         <f t="shared" si="47"/>
-        <v>9.7503786837757123E-2</v>
+        <v>9.7995287075569801E-2</v>
       </c>
       <c r="DC16" s="14">
         <f t="shared" si="48"/>
-        <v>0.30790420743641789</v>
+        <v>0.30908804507818394</v>
       </c>
       <c r="DE16" s="4" t="s">
         <v>14</v>
       </c>
       <c r="DF16" s="14">
         <f t="shared" si="6"/>
-        <v>-0.25948560568529483</v>
+        <v>-0.26066944332706088</v>
       </c>
       <c r="DG16" s="14">
         <f t="shared" si="7"/>
-        <v>7.2813900105462043E-2</v>
-      </c>
-      <c r="DH16" s="97">
+        <v>7.2322399867649365E-2</v>
+      </c>
+      <c r="DH16" s="96">
         <f t="shared" si="8"/>
-        <v>6.6169443219217416E-2</v>
-      </c>
-      <c r="DI16" s="55">
+        <v>6.6889599614389242E-2</v>
+      </c>
+      <c r="DI16" s="54">
         <f t="shared" si="9"/>
-        <v>0.55798110091559416</v>
+        <v>0.55852885025301613</v>
       </c>
       <c r="DK16" s="14"/>
-      <c r="DM16" s="138">
+      <c r="DM16" s="115">
         <f t="shared" si="24"/>
         <v>10</v>
       </c>
@@ -10618,7 +10635,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP17" s="87">
+      <c r="AP17" s="86">
         <f t="shared" si="3"/>
         <v>0.66666666666666663</v>
       </c>
@@ -10671,7 +10688,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH17" s="87">
+      <c r="BH17" s="86">
         <f t="shared" si="13"/>
         <v>0.33333333333333337</v>
       </c>
@@ -10707,7 +10724,7 @@
         <f t="shared" si="20"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="BR17" s="56">
+      <c r="BR17" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -10744,15 +10761,15 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC17" s="56">
+      <c r="CC17" s="55">
         <f t="shared" si="32"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="CD17" s="13"/>
-      <c r="CE17" s="106" t="s">
+      <c r="CE17" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="CF17" s="111">
+      <c r="CF17" s="110">
         <f t="shared" si="35"/>
         <v>0.89814814814814814</v>
       </c>
@@ -10780,7 +10797,7 @@
         <f t="shared" si="41"/>
         <v>0.25523012552301261</v>
       </c>
-      <c r="CM17" s="103">
+      <c r="CM17" s="102">
         <f t="shared" si="42"/>
         <v>0.5146443514644351</v>
       </c>
@@ -10813,11 +10830,11 @@
       </c>
       <c r="CV17" s="13">
         <f t="shared" si="33"/>
-        <v>9.1118558860494345E-2</v>
+        <v>9.2165898617511524E-2</v>
       </c>
       <c r="CW17" s="13">
         <f t="shared" si="33"/>
-        <v>0.21947004608294932</v>
+        <v>0.22199269029079929</v>
       </c>
       <c r="CY17" s="4" t="s">
         <v>15</v>
@@ -10832,33 +10849,33 @@
       </c>
       <c r="DB17" s="14">
         <f t="shared" si="47"/>
-        <v>9.1932895470408699E-2</v>
+        <v>9.2467273418328222E-2</v>
       </c>
       <c r="DC17" s="14">
         <f t="shared" si="48"/>
-        <v>0.26018695394060715</v>
+        <v>0.26156140545665313</v>
       </c>
       <c r="DE17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="DF17" s="14">
         <f t="shared" si="6"/>
-        <v>-0.23908375261820564</v>
+        <v>-0.24045820413425162</v>
       </c>
       <c r="DG17" s="14">
         <f t="shared" si="7"/>
-        <v>9.1600213071888509E-2</v>
-      </c>
-      <c r="DH17" s="97">
+        <v>9.1065835123968986E-2</v>
+      </c>
+      <c r="DH17" s="96">
         <f t="shared" si="8"/>
-        <v>9.6364700817106227E-2</v>
-      </c>
-      <c r="DI17" s="55">
+        <v>9.6730085783356873E-2</v>
+      </c>
+      <c r="DI17" s="54">
         <f t="shared" si="9"/>
-        <v>0.58578531837909842</v>
+        <v>0.5862022261994122</v>
       </c>
       <c r="DK17" s="14"/>
-      <c r="DM17" s="138">
+      <c r="DM17" s="115">
         <f t="shared" si="24"/>
         <v>7</v>
       </c>
@@ -10945,7 +10962,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP18" s="87">
+      <c r="AP18" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -10998,7 +11015,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH18" s="87">
+      <c r="BH18" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -11034,7 +11051,7 @@
         <f t="shared" si="20"/>
         <v>0.57692307692307687</v>
       </c>
-      <c r="BR18" s="56">
+      <c r="BR18" s="55">
         <f t="shared" si="21"/>
         <v>0.77777777777777779</v>
       </c>
@@ -11071,15 +11088,15 @@
         <f t="shared" si="31"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="CC18" s="56">
+      <c r="CC18" s="55">
         <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="CD18" s="13"/>
-      <c r="CE18" s="106" t="s">
+      <c r="CE18" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="CF18" s="111">
+      <c r="CF18" s="110">
         <f t="shared" si="35"/>
         <v>0.70738636363636365</v>
       </c>
@@ -11107,7 +11124,7 @@
         <f t="shared" si="41"/>
         <v>0.40092165898617516</v>
       </c>
-      <c r="CM18" s="103">
+      <c r="CM18" s="102">
         <f t="shared" si="42"/>
         <v>0.58525345622119818</v>
       </c>
@@ -11140,11 +11157,11 @@
       </c>
       <c r="CV18" s="13">
         <f t="shared" si="33"/>
-        <v>9.9067599067599071E-2</v>
+        <v>0.10020630710285883</v>
       </c>
       <c r="CW18" s="13">
         <f t="shared" si="33"/>
-        <v>0.25480769230769229</v>
+        <v>0.25773651635720601</v>
       </c>
       <c r="CY18" s="4" t="s">
         <v>16</v>
@@ -11159,43 +11176,43 @@
       </c>
       <c r="DB18" s="14">
         <f t="shared" si="47"/>
-        <v>7.1709592149002715E-2</v>
+        <v>7.2204263995528845E-2</v>
       </c>
       <c r="DC18" s="14">
         <f t="shared" si="48"/>
-        <v>0.32335167096206724</v>
+        <v>0.3246203429423698</v>
       </c>
       <c r="DE18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="DF18" s="14">
         <f t="shared" si="6"/>
-        <v>-0.28681753323290987</v>
+        <v>-0.28808620521321243</v>
       </c>
       <c r="DG18" s="14">
         <f t="shared" si="7"/>
-        <v>0.20161437360508042</v>
-      </c>
-      <c r="DH18" s="97">
+        <v>0.20111970175855429</v>
+      </c>
+      <c r="DH18" s="96">
         <f t="shared" si="8"/>
-        <v>2.5717500435727056E-2</v>
-      </c>
-      <c r="DI18" s="55">
+        <v>2.6410661333719249E-2</v>
+      </c>
+      <c r="DI18" s="54">
         <f t="shared" si="9"/>
-        <v>0.74860905335020655</v>
+        <v>0.74868909075144574</v>
       </c>
       <c r="DK18" s="14"/>
-      <c r="DM18" s="138">
+      <c r="DM18" s="115">
         <f t="shared" si="24"/>
         <v>12</v>
       </c>
       <c r="DO18" s="14"/>
     </row>
     <row r="19" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="66" t="s">
+      <c r="B19" s="65" t="s">
         <v>21</v>
       </c>
       <c r="C19" s="27">
@@ -11257,22 +11274,22 @@
         <v>9</v>
       </c>
       <c r="AD19" s="19"/>
-      <c r="AL19" s="80" t="s">
+      <c r="AL19" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="AM19" s="91">
+      <c r="AM19" s="90">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AN19" s="92">
+      <c r="AN19" s="91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO19" s="92">
+      <c r="AO19" s="91">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP19" s="93">
+      <c r="AP19" s="92">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -11310,22 +11327,22 @@
         <v>0</v>
       </c>
       <c r="BC19" s="48"/>
-      <c r="BD19" s="80" t="s">
+      <c r="BD19" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="BE19" s="91">
+      <c r="BE19" s="90">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BF19" s="92">
+      <c r="BF19" s="91">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="BG19" s="92">
+      <c r="BG19" s="91">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH19" s="93">
+      <c r="BH19" s="92">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -11361,7 +11378,7 @@
         <f t="shared" si="20"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="BR19" s="56">
+      <c r="BR19" s="55">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
@@ -11398,15 +11415,15 @@
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC19" s="56">
+      <c r="CC19" s="55">
         <f t="shared" si="32"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="CD19" s="13"/>
-      <c r="CE19" s="106" t="s">
+      <c r="CE19" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="CF19" s="111">
+      <c r="CF19" s="110">
         <f t="shared" si="35"/>
         <v>0.94654088050314467</v>
       </c>
@@ -11434,7 +11451,7 @@
         <f t="shared" si="41"/>
         <v>0.4358974358974359</v>
       </c>
-      <c r="CM19" s="103">
+      <c r="CM19" s="102">
         <f t="shared" si="42"/>
         <v>0.67948717948717952</v>
       </c>
@@ -11467,11 +11484,11 @@
       </c>
       <c r="CV19" s="13">
         <f t="shared" si="33"/>
-        <v>9.1706539074960125E-2</v>
+        <v>9.2760637225247022E-2</v>
       </c>
       <c r="CW19" s="13">
         <f t="shared" si="33"/>
-        <v>0.2351973684210526</v>
+        <v>0.2379007864488808</v>
       </c>
       <c r="CY19" s="4" t="s">
         <v>17</v>
@@ -11486,33 +11503,33 @@
       </c>
       <c r="DB19" s="14">
         <f t="shared" si="47"/>
-        <v>0.11292990140480394</v>
+        <v>0.11361775122011904</v>
       </c>
       <c r="DC19" s="14">
         <f t="shared" si="48"/>
-        <v>0.28648171194313482</v>
+        <v>0.2880193891109199</v>
       </c>
       <c r="DE19" s="4" t="s">
         <v>17</v>
       </c>
       <c r="DF19" s="14">
         <f t="shared" si="6"/>
-        <v>-0.27284310647510901</v>
+        <v>-0.27438078364289409</v>
       </c>
       <c r="DG19" s="14">
         <f t="shared" si="7"/>
-        <v>2.3696585426881273E-2</v>
-      </c>
-      <c r="DH19" s="97">
+        <v>2.3008735611566175E-2</v>
+      </c>
+      <c r="DH19" s="96">
         <f t="shared" si="8"/>
-        <v>4.6400004831139305E-2</v>
-      </c>
-      <c r="DI19" s="55">
+        <v>4.6645761166413349E-2</v>
+      </c>
+      <c r="DI19" s="54">
         <f t="shared" si="9"/>
-        <v>0.4852862351914235</v>
+        <v>0.48572066159438559</v>
       </c>
       <c r="DK19" s="14"/>
-      <c r="DM19" s="139">
+      <c r="DM19" s="116">
         <f t="shared" si="24"/>
         <v>11</v>
       </c>
@@ -11575,19 +11592,19 @@
       <c r="AL20" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AM20" s="84">
+      <c r="AM20" s="83">
         <f t="shared" si="0"/>
         <v>0.98713826366559487</v>
       </c>
-      <c r="AN20" s="85">
+      <c r="AN20" s="84">
         <f t="shared" si="1"/>
         <v>0.24293785310734464</v>
       </c>
-      <c r="AO20" s="85">
+      <c r="AO20" s="84">
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP20" s="86">
+      <c r="AP20" s="85">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -11628,100 +11645,100 @@
       <c r="BD20" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="BE20" s="84">
+      <c r="BE20" s="83">
         <f t="shared" si="10"/>
         <v>1.2861736334405127E-2</v>
       </c>
-      <c r="BF20" s="85">
+      <c r="BF20" s="84">
         <f t="shared" si="11"/>
         <v>0.75706214689265539</v>
       </c>
-      <c r="BG20" s="85">
+      <c r="BG20" s="84">
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH20" s="86">
+      <c r="BH20" s="85">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BI20" s="48"/>
-      <c r="BJ20" s="62" t="s">
+      <c r="BJ20" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="BK20" s="63">
+      <c r="BK20" s="62">
         <f t="shared" si="14"/>
         <v>0.98713826366559487</v>
       </c>
-      <c r="BL20" s="63">
+      <c r="BL20" s="62">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="BM20" s="63">
+      <c r="BM20" s="62">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="BN20" s="63">
+      <c r="BN20" s="62">
         <f t="shared" si="17"/>
         <v>0.88888888888888884</v>
       </c>
-      <c r="BO20" s="63">
+      <c r="BO20" s="62">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="BP20" s="63">
+      <c r="BP20" s="62">
         <f t="shared" si="19"/>
         <v>0.5423728813559322</v>
       </c>
-      <c r="BQ20" s="63">
+      <c r="BQ20" s="62">
         <f t="shared" si="20"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="BR20" s="64">
+      <c r="BR20" s="63">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="BS20" s="48"/>
       <c r="BT20" s="48"/>
-      <c r="BU20" s="62" t="s">
+      <c r="BU20" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="BV20" s="63">
+      <c r="BV20" s="62">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="BW20" s="63">
+      <c r="BW20" s="62">
         <f t="shared" si="26"/>
         <v>0.4576271186440678</v>
       </c>
-      <c r="BX20" s="63">
+      <c r="BX20" s="62">
         <f t="shared" si="27"/>
         <v>0.69230769230769229</v>
       </c>
-      <c r="BY20" s="63">
+      <c r="BY20" s="62">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="BZ20" s="63">
+      <c r="BZ20" s="62">
         <f t="shared" si="29"/>
         <v>1.2861736334405127E-2</v>
       </c>
-      <c r="CA20" s="63">
+      <c r="CA20" s="62">
         <f t="shared" si="30"/>
         <v>1</v>
       </c>
-      <c r="CB20" s="63">
+      <c r="CB20" s="62">
         <f t="shared" si="31"/>
         <v>1</v>
       </c>
-      <c r="CC20" s="64">
+      <c r="CC20" s="63">
         <f t="shared" si="32"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="CD20" s="13"/>
-      <c r="CE20" s="106" t="s">
+      <c r="CE20" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="CF20" s="111">
+      <c r="CF20" s="110">
         <f t="shared" si="35"/>
         <v>0.43842364532019712</v>
       </c>
@@ -11749,7 +11766,7 @@
         <f t="shared" si="41"/>
         <v>0.40350877192982454</v>
       </c>
-      <c r="CM20" s="103">
+      <c r="CM20" s="102">
         <f t="shared" si="42"/>
         <v>0.6271929824561403</v>
       </c>
@@ -11782,11 +11799,11 @@
       </c>
       <c r="CV20" s="13">
         <f t="shared" si="33"/>
-        <v>0.12751953928424517</v>
+        <v>0.12898528111509855</v>
       </c>
       <c r="CW20" s="13">
         <f t="shared" si="33"/>
-        <v>0.28506787330316746</v>
+        <v>0.28834451552504292</v>
       </c>
       <c r="DH20" s="13"/>
       <c r="DI20" s="13"/>
@@ -11862,7 +11879,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP21" s="87">
+      <c r="AP21" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -11915,26 +11932,26 @@
         <f t="shared" si="12"/>
         <v>0.88461538461538458</v>
       </c>
-      <c r="BH21" s="87">
+      <c r="BH21" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BI21" s="48"/>
-      <c r="BJ21" s="128" t="s">
+      <c r="BJ21" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="BK21" s="130" t="s">
+      <c r="BK21" s="127" t="s">
         <v>111</v>
       </c>
-      <c r="BL21" s="130"/>
-      <c r="BM21" s="130"/>
-      <c r="BN21" s="130"/>
-      <c r="BO21" s="130" t="s">
+      <c r="BL21" s="127"/>
+      <c r="BM21" s="127"/>
+      <c r="BN21" s="127"/>
+      <c r="BO21" s="127" t="s">
         <v>112</v>
       </c>
-      <c r="BP21" s="130"/>
-      <c r="BQ21" s="130"/>
-      <c r="BR21" s="131"/>
+      <c r="BP21" s="127"/>
+      <c r="BQ21" s="127"/>
+      <c r="BR21" s="128"/>
       <c r="BS21" s="48"/>
       <c r="BT21" s="48"/>
       <c r="BU21" s="48"/>
@@ -11947,10 +11964,10 @@
       <c r="CB21" s="48"/>
       <c r="CC21" s="48"/>
       <c r="CD21" s="48"/>
-      <c r="CE21" s="106" t="s">
+      <c r="CE21" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="CF21" s="111">
+      <c r="CF21" s="110">
         <f t="shared" si="35"/>
         <v>0.85585585585585566</v>
       </c>
@@ -11978,7 +11995,7 @@
         <f t="shared" si="41"/>
         <v>0.56108597285067874</v>
       </c>
-      <c r="CM21" s="103">
+      <c r="CM21" s="102">
         <f t="shared" si="42"/>
         <v>0.7601809954751132</v>
       </c>
@@ -12011,19 +12028,19 @@
       </c>
       <c r="CV21" s="13">
         <f t="shared" si="33"/>
-        <v>6.7432567432567425E-2</v>
+        <v>6.8207654414550969E-2</v>
       </c>
       <c r="CW21" s="13">
-        <f t="shared" si="33"/>
-        <v>0.24313186813186816</v>
+        <f>CM22*CM$4</f>
+        <v>0.24592648730579764</v>
       </c>
       <c r="DF21" s="13">
         <f>ABS(MIN(DF4:DF19))</f>
-        <v>0.3041939263119075</v>
+        <v>0.30597439210244587</v>
       </c>
       <c r="DG21" s="13">
         <f>MAX(DG4:DG19)</f>
-        <v>0.37147022395901624</v>
+        <v>0.37133492110263761</v>
       </c>
     </row>
     <row r="22" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12113,7 +12130,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP22" s="87">
+      <c r="AP22" s="86">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -12166,12 +12183,12 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH22" s="87">
+      <c r="BH22" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="BI22" s="48"/>
-      <c r="BJ22" s="129"/>
+      <c r="BJ22" s="126"/>
       <c r="BK22" s="50" t="s">
         <v>64</v>
       </c>
@@ -12208,10 +12225,10 @@
       <c r="CB22" s="48"/>
       <c r="CC22" s="48"/>
       <c r="CD22" s="48"/>
-      <c r="CE22" s="106" t="s">
+      <c r="CE22" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="CF22" s="111">
+      <c r="CF22" s="110">
         <f t="shared" si="35"/>
         <v>0.97460317460317469</v>
       </c>
@@ -12239,33 +12256,33 @@
         <f t="shared" ref="CL22" si="50">BL56</f>
         <v>0.2967032967032967</v>
       </c>
-      <c r="CM22" s="103">
+      <c r="CM22" s="102">
         <f t="shared" ref="CM22" si="51">BP56</f>
         <v>0.64835164835164838</v>
       </c>
       <c r="CO22" s="41"/>
-      <c r="CP22" s="59" t="s">
+      <c r="CP22" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="CQ22" s="59" t="s">
+      <c r="CQ22" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="CR22" s="59" t="s">
+      <c r="CR22" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="CS22" s="59" t="s">
+      <c r="CS22" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="CT22" s="59" t="s">
+      <c r="CT22" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="CU22" s="59" t="s">
+      <c r="CU22" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="CV22" s="59" t="s">
+      <c r="CV22" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="CW22" s="59" t="s">
+      <c r="CW22" s="58" t="s">
         <v>116</v>
       </c>
     </row>
@@ -12356,7 +12373,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP23" s="87">
+      <c r="AP23" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -12409,7 +12426,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH23" s="87">
+      <c r="BH23" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -12462,22 +12479,22 @@
       <c r="CC23" s="48"/>
       <c r="CD23" s="48"/>
       <c r="CE23" s="41"/>
-      <c r="CF23" s="121" t="s">
+      <c r="CF23" s="136" t="s">
         <v>72</v>
       </c>
-      <c r="CG23" s="122"/>
-      <c r="CH23" s="122" t="s">
+      <c r="CG23" s="119"/>
+      <c r="CH23" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="CI23" s="122"/>
-      <c r="CJ23" s="122" t="s">
+      <c r="CI23" s="119"/>
+      <c r="CJ23" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="CK23" s="122"/>
-      <c r="CL23" s="122" t="s">
+      <c r="CK23" s="119"/>
+      <c r="CL23" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="CM23" s="123"/>
+      <c r="CM23" s="129"/>
       <c r="CO23" s="4" t="s">
         <v>1</v>
       </c>
@@ -12601,7 +12618,7 @@
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP24" s="87">
+      <c r="AP24" s="86">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -12654,7 +12671,7 @@
         <f t="shared" si="12"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH24" s="87">
+      <c r="BH24" s="86">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
@@ -12707,7 +12724,7 @@
       <c r="CC24" s="48"/>
       <c r="CD24" s="48"/>
       <c r="CE24" s="33"/>
-      <c r="CF24" s="112">
+      <c r="CF24" s="137">
         <f>W35</f>
         <v>0.45454545454545453</v>
       </c>
@@ -12735,7 +12752,7 @@
         <f>X37</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="CM24" s="113">
+      <c r="CM24" s="138">
         <f>X38</f>
         <v>0.41666666666666669</v>
       </c>
@@ -12844,7 +12861,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP25" s="87">
+      <c r="AP25" s="86">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -12897,7 +12914,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH25" s="87">
+      <c r="BH25" s="86">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
@@ -12950,22 +12967,22 @@
       <c r="CC25" s="48"/>
       <c r="CD25" s="48"/>
       <c r="CE25" s="33"/>
-      <c r="CF25" s="124" t="s">
+      <c r="CF25" s="130" t="s">
         <v>40</v>
       </c>
-      <c r="CG25" s="125"/>
-      <c r="CH25" s="126" t="s">
+      <c r="CG25" s="124"/>
+      <c r="CH25" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="CI25" s="125"/>
-      <c r="CJ25" s="126" t="s">
+      <c r="CI25" s="124"/>
+      <c r="CJ25" s="123" t="s">
         <v>40</v>
       </c>
-      <c r="CK25" s="125"/>
-      <c r="CL25" s="126" t="s">
+      <c r="CK25" s="124"/>
+      <c r="CL25" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="CM25" s="127"/>
+      <c r="CM25" s="131"/>
       <c r="CO25" s="4" t="s">
         <v>4</v>
       </c>
@@ -13073,7 +13090,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP26" s="87">
+      <c r="AP26" s="86">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -13126,7 +13143,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH26" s="87">
+      <c r="BH26" s="86">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
@@ -13179,28 +13196,28 @@
       <c r="CC26" s="48"/>
       <c r="CD26" s="48"/>
       <c r="CE26" s="41"/>
-      <c r="CF26" s="114" t="s">
+      <c r="CF26" s="111" t="s">
         <v>113</v>
       </c>
-      <c r="CG26" s="59" t="s">
+      <c r="CG26" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="CH26" s="59" t="s">
+      <c r="CH26" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="CI26" s="59" t="s">
+      <c r="CI26" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="CJ26" s="59" t="s">
+      <c r="CJ26" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="CK26" s="59" t="s">
+      <c r="CK26" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="CL26" s="59" t="s">
+      <c r="CL26" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="CM26" s="115" t="s">
+      <c r="CM26" s="112" t="s">
         <v>116</v>
       </c>
       <c r="CO26" s="4" t="s">
@@ -13326,7 +13343,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP27" s="87">
+      <c r="AP27" s="86">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -13379,7 +13396,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH27" s="87">
+      <c r="BH27" s="86">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
@@ -13431,10 +13448,10 @@
       <c r="CB27" s="48"/>
       <c r="CC27" s="48"/>
       <c r="CD27" s="48"/>
-      <c r="CE27" s="106" t="s">
-        <v>1</v>
-      </c>
-      <c r="CF27" s="111">
+      <c r="CE27" s="105" t="s">
+        <v>1</v>
+      </c>
+      <c r="CF27" s="110">
         <f>BM23</f>
         <v>3.2258064516129031E-2</v>
       </c>
@@ -13462,7 +13479,7 @@
         <f>BN41</f>
         <v>0</v>
       </c>
-      <c r="CM27" s="103">
+      <c r="CM27" s="102">
         <f>BR41</f>
         <v>0.25</v>
       </c>
@@ -13589,7 +13606,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP28" s="87">
+      <c r="AP28" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -13642,7 +13659,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH28" s="87">
+      <c r="BH28" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -13694,10 +13711,10 @@
       <c r="CB28" s="48"/>
       <c r="CC28" s="48"/>
       <c r="CD28" s="48"/>
-      <c r="CE28" s="106" t="s">
+      <c r="CE28" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="CF28" s="111">
+      <c r="CF28" s="110">
         <f t="shared" ref="CF28:CF41" si="63">BM24</f>
         <v>0.04</v>
       </c>
@@ -13725,7 +13742,7 @@
         <f t="shared" ref="CL28:CL41" si="69">BN42</f>
         <v>0</v>
       </c>
-      <c r="CM28" s="103">
+      <c r="CM28" s="102">
         <f t="shared" ref="CM28:CM41" si="70">BR42</f>
         <v>0.10000000000000003</v>
       </c>
@@ -13852,7 +13869,7 @@
         <f t="shared" si="2"/>
         <v>0.61538461538461542</v>
       </c>
-      <c r="AP29" s="87">
+      <c r="AP29" s="86">
         <f t="shared" si="3"/>
         <v>0.22222222222222221</v>
       </c>
@@ -13905,7 +13922,7 @@
         <f t="shared" si="12"/>
         <v>0.38461538461538458</v>
       </c>
-      <c r="BH29" s="87">
+      <c r="BH29" s="86">
         <f t="shared" si="13"/>
         <v>0.77777777777777779</v>
       </c>
@@ -13957,10 +13974,10 @@
       <c r="CB29" s="48"/>
       <c r="CC29" s="48"/>
       <c r="CD29" s="48"/>
-      <c r="CE29" s="106" t="s">
+      <c r="CE29" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="CF29" s="111">
+      <c r="CF29" s="110">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
@@ -13988,7 +14005,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM29" s="103">
+      <c r="CM29" s="102">
         <f t="shared" si="70"/>
         <v>0.1818181818181818</v>
       </c>
@@ -14097,7 +14114,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP30" s="87">
+      <c r="AP30" s="86">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -14150,7 +14167,7 @@
         <f t="shared" si="12"/>
         <v>0.88461538461538458</v>
       </c>
-      <c r="BH30" s="87">
+      <c r="BH30" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -14202,10 +14219,10 @@
       <c r="CB30" s="48"/>
       <c r="CC30" s="48"/>
       <c r="CD30" s="48"/>
-      <c r="CE30" s="106" t="s">
+      <c r="CE30" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="CF30" s="111">
+      <c r="CF30" s="110">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
@@ -14233,7 +14250,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM30" s="103">
+      <c r="CM30" s="102">
         <f t="shared" si="70"/>
         <v>0.1818181818181818</v>
       </c>
@@ -14344,7 +14361,7 @@
         <f t="shared" si="2"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP31" s="87">
+      <c r="AP31" s="86">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -14397,7 +14414,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH31" s="87">
+      <c r="BH31" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -14449,10 +14466,10 @@
       <c r="CB31" s="48"/>
       <c r="CC31" s="48"/>
       <c r="CD31" s="48"/>
-      <c r="CE31" s="106" t="s">
+      <c r="CE31" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="CF31" s="111">
+      <c r="CF31" s="110">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
@@ -14480,7 +14497,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM31" s="103">
+      <c r="CM31" s="102">
         <f t="shared" si="70"/>
         <v>0.1818181818181818</v>
       </c>
@@ -14605,7 +14622,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP32" s="87">
+      <c r="AP32" s="86">
         <f t="shared" si="3"/>
         <v>0.88888888888888884</v>
       </c>
@@ -14658,7 +14675,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH32" s="87">
+      <c r="BH32" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -14710,10 +14727,10 @@
       <c r="CB32" s="48"/>
       <c r="CC32" s="48"/>
       <c r="CD32" s="48"/>
-      <c r="CE32" s="106" t="s">
+      <c r="CE32" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="CF32" s="111">
+      <c r="CF32" s="110">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
@@ -14741,7 +14758,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM32" s="103">
+      <c r="CM32" s="102">
         <f t="shared" si="70"/>
         <v>0.25</v>
       </c>
@@ -14850,7 +14867,7 @@
         <f t="shared" si="2"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP33" s="87">
+      <c r="AP33" s="86">
         <f t="shared" si="3"/>
         <v>0.77777777777777779</v>
       </c>
@@ -14903,7 +14920,7 @@
         <f t="shared" si="12"/>
         <v>0.88461538461538458</v>
       </c>
-      <c r="BH33" s="87">
+      <c r="BH33" s="86">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
@@ -14955,10 +14972,10 @@
       <c r="CB33" s="48"/>
       <c r="CC33" s="48"/>
       <c r="CD33" s="48"/>
-      <c r="CE33" s="106" t="s">
+      <c r="CE33" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="CF33" s="111">
+      <c r="CF33" s="110">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
@@ -14986,7 +15003,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM33" s="103">
+      <c r="CM33" s="102">
         <f t="shared" si="70"/>
         <v>0.5</v>
       </c>
@@ -15107,7 +15124,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP34" s="87">
+      <c r="AP34" s="86">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -15160,7 +15177,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH34" s="87">
+      <c r="BH34" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -15212,10 +15229,10 @@
       <c r="CB34" s="48"/>
       <c r="CC34" s="48"/>
       <c r="CD34" s="48"/>
-      <c r="CE34" s="106" t="s">
+      <c r="CE34" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="CF34" s="111">
+      <c r="CF34" s="110">
         <f t="shared" si="63"/>
         <v>2.9411764705882353E-2</v>
       </c>
@@ -15243,7 +15260,7 @@
         <f t="shared" si="69"/>
         <v>0.15384615384615383</v>
       </c>
-      <c r="CM34" s="103">
+      <c r="CM34" s="102">
         <f t="shared" si="70"/>
         <v>0.46153846153846151</v>
       </c>
@@ -15284,22 +15301,22 @@
       </c>
     </row>
     <row r="35" spans="1:101" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="80" t="s">
+      <c r="A35" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="81" t="s">
+      <c r="B35" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="82">
-        <v>0</v>
-      </c>
-      <c r="D35" s="82">
-        <v>0</v>
-      </c>
-      <c r="E35" s="82">
-        <v>0</v>
-      </c>
-      <c r="F35" s="83">
+      <c r="C35" s="81">
+        <v>0</v>
+      </c>
+      <c r="D35" s="81">
+        <v>0</v>
+      </c>
+      <c r="E35" s="81">
+        <v>0</v>
+      </c>
+      <c r="F35" s="82">
         <v>0</v>
       </c>
       <c r="H35" s="42" t="s">
@@ -15338,39 +15355,39 @@
       <c r="T35" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="U35" s="98">
+      <c r="U35" s="97">
         <f>U22/U$32</f>
         <v>1.4814814814814815E-2</v>
       </c>
-      <c r="V35" s="98">
+      <c r="V35" s="97">
         <f>V22/V$32</f>
         <v>0.40229885057471265</v>
       </c>
-      <c r="W35" s="98">
+      <c r="W35" s="97">
         <f>W22/W$32</f>
         <v>0.45454545454545453</v>
       </c>
-      <c r="X35" s="99">
+      <c r="X35" s="98">
         <f>X22/X$32</f>
         <v>0</v>
       </c>
       <c r="AD35" s="19"/>
-      <c r="AL35" s="62" t="s">
+      <c r="AL35" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="AM35" s="88">
+      <c r="AM35" s="87">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AN35" s="89">
+      <c r="AN35" s="88">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AO35" s="89">
+      <c r="AO35" s="88">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AP35" s="90">
+      <c r="AP35" s="89">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -15408,22 +15425,22 @@
         <v>0</v>
       </c>
       <c r="BC35" s="48"/>
-      <c r="BD35" s="62" t="s">
+      <c r="BD35" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="BE35" s="88">
+      <c r="BE35" s="87">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BF35" s="89">
+      <c r="BF35" s="88">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="BG35" s="89">
+      <c r="BG35" s="88">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH35" s="90">
+      <c r="BH35" s="89">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -15475,10 +15492,10 @@
       <c r="CB35" s="48"/>
       <c r="CC35" s="48"/>
       <c r="CD35" s="48"/>
-      <c r="CE35" s="106" t="s">
+      <c r="CE35" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="CF35" s="111">
+      <c r="CF35" s="110">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
@@ -15506,7 +15523,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM35" s="103">
+      <c r="CM35" s="102">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
@@ -15550,19 +15567,19 @@
       <c r="A36" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" s="78">
+      <c r="B36" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="77">
         <v>144</v>
       </c>
-      <c r="D36" s="78">
+      <c r="D36" s="77">
         <v>51</v>
       </c>
-      <c r="E36" s="78">
+      <c r="E36" s="77">
         <v>6</v>
       </c>
-      <c r="F36" s="79">
+      <c r="F36" s="78">
         <v>2</v>
       </c>
       <c r="H36" s="42" t="s">
@@ -15611,7 +15628,7 @@
         <f>W27/W$32</f>
         <v>0.78787878787878785</v>
       </c>
-      <c r="X36" s="56">
+      <c r="X36" s="55">
         <f>X27/X$32</f>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -15619,19 +15636,19 @@
       <c r="AL36" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="AM36" s="94">
+      <c r="AM36" s="93">
         <f t="shared" ref="AM36:AM67" si="72">(AG$4-C36)/(AG$4-AG$5)</f>
         <v>0.53697749196141475</v>
       </c>
-      <c r="AN36" s="95">
+      <c r="AN36" s="94">
         <f t="shared" ref="AN36:AN67" si="73">(D36-AH$5)/(AH$4-AH$5)</f>
         <v>0.28813559322033899</v>
       </c>
-      <c r="AO36" s="95">
+      <c r="AO36" s="94">
         <f t="shared" ref="AO36:AO67" si="74">(E36-AI$5)/(AI$4-AI$5)</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="AP36" s="96">
+      <c r="AP36" s="95">
         <f t="shared" ref="AP36:AP67" si="75">(AJ$4-F36)/(AJ$4-AJ$5)</f>
         <v>0.77777777777777779</v>
       </c>
@@ -15672,19 +15689,19 @@
       <c r="BD36" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="BE36" s="94">
+      <c r="BE36" s="93">
         <f t="shared" si="10"/>
         <v>0.46302250803858525</v>
       </c>
-      <c r="BF36" s="95">
+      <c r="BF36" s="94">
         <f t="shared" si="11"/>
         <v>0.71186440677966101</v>
       </c>
-      <c r="BG36" s="95">
+      <c r="BG36" s="94">
         <f t="shared" si="12"/>
         <v>0.76923076923076916</v>
       </c>
-      <c r="BH36" s="96">
+      <c r="BH36" s="95">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
@@ -15736,10 +15753,10 @@
       <c r="CB36" s="48"/>
       <c r="CC36" s="48"/>
       <c r="CD36" s="48"/>
-      <c r="CE36" s="106" t="s">
+      <c r="CE36" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="CF36" s="111">
+      <c r="CF36" s="110">
         <f t="shared" si="63"/>
         <v>2.4390243902439022E-2</v>
       </c>
@@ -15767,7 +15784,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM36" s="103">
+      <c r="CM36" s="102">
         <f t="shared" si="70"/>
         <v>0.43750000000000006</v>
       </c>
@@ -15866,7 +15883,7 @@
         <f>U23/U$32</f>
         <v>7.407407407407407E-2</v>
       </c>
-      <c r="V37" s="13">
+      <c r="V37" s="139">
         <f>V23/V$32</f>
         <v>0.22988505747126436</v>
       </c>
@@ -15874,7 +15891,7 @@
         <f>W23/W$32</f>
         <v>0.12121212121212122</v>
       </c>
-      <c r="X37" s="56">
+      <c r="X37" s="55">
         <f>X23/X$32</f>
         <v>0.16666666666666666</v>
       </c>
@@ -15894,7 +15911,7 @@
         <f t="shared" si="74"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP37" s="87">
+      <c r="AP37" s="86">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
@@ -15947,7 +15964,7 @@
         <f t="shared" si="12"/>
         <v>0.73076923076923084</v>
       </c>
-      <c r="BH37" s="87">
+      <c r="BH37" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -15999,10 +16016,10 @@
       <c r="CB37" s="48"/>
       <c r="CC37" s="48"/>
       <c r="CD37" s="48"/>
-      <c r="CE37" s="106" t="s">
+      <c r="CE37" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="CF37" s="111">
+      <c r="CF37" s="110">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
@@ -16030,7 +16047,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM37" s="103">
+      <c r="CM37" s="102">
         <f t="shared" si="70"/>
         <v>0.35714285714285715</v>
       </c>
@@ -16123,19 +16140,19 @@
         <v>2</v>
       </c>
       <c r="T38" s="20"/>
-      <c r="U38" s="63">
+      <c r="U38" s="62">
         <f>U28/U$32</f>
         <v>0.2074074074074074</v>
       </c>
-      <c r="V38" s="63">
+      <c r="V38" s="140">
         <f>V28/V$32</f>
         <v>0.37931034482758619</v>
       </c>
-      <c r="W38" s="63">
+      <c r="W38" s="62">
         <f>W28/W$32</f>
         <v>0.24242424242424243</v>
       </c>
-      <c r="X38" s="64">
+      <c r="X38" s="63">
         <f>X28/X$32</f>
         <v>0.41666666666666669</v>
       </c>
@@ -16155,7 +16172,7 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP38" s="87">
+      <c r="AP38" s="86">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
@@ -16208,7 +16225,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH38" s="87">
+      <c r="BH38" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -16260,10 +16277,10 @@
       <c r="CB38" s="48"/>
       <c r="CC38" s="48"/>
       <c r="CD38" s="48"/>
-      <c r="CE38" s="106" t="s">
+      <c r="CE38" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="CF38" s="111">
+      <c r="CF38" s="110">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
@@ -16291,7 +16308,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM38" s="103">
+      <c r="CM38" s="102">
         <f t="shared" si="70"/>
         <v>0.4</v>
       </c>
@@ -16402,7 +16419,7 @@
         <f t="shared" si="74"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP39" s="87">
+      <c r="AP39" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -16455,26 +16472,26 @@
         <f t="shared" si="12"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH39" s="87">
+      <c r="BH39" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="BI39" s="48"/>
-      <c r="BJ39" s="117" t="s">
+      <c r="BJ39" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="BK39" s="119" t="s">
+      <c r="BK39" s="134" t="s">
         <v>111</v>
       </c>
-      <c r="BL39" s="119"/>
-      <c r="BM39" s="119"/>
-      <c r="BN39" s="119"/>
-      <c r="BO39" s="119" t="s">
+      <c r="BL39" s="134"/>
+      <c r="BM39" s="134"/>
+      <c r="BN39" s="134"/>
+      <c r="BO39" s="134" t="s">
         <v>112</v>
       </c>
-      <c r="BP39" s="119"/>
-      <c r="BQ39" s="119"/>
-      <c r="BR39" s="120"/>
+      <c r="BP39" s="134"/>
+      <c r="BQ39" s="134"/>
+      <c r="BR39" s="135"/>
       <c r="BS39" s="48"/>
       <c r="BT39" s="48"/>
       <c r="BU39" s="48"/>
@@ -16487,10 +16504,10 @@
       <c r="CB39" s="48"/>
       <c r="CC39" s="48"/>
       <c r="CD39" s="48"/>
-      <c r="CE39" s="106" t="s">
+      <c r="CE39" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="CF39" s="111">
+      <c r="CF39" s="110">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
@@ -16518,7 +16535,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM39" s="103">
+      <c r="CM39" s="102">
         <f t="shared" si="70"/>
         <v>0.1818181818181818</v>
       </c>
@@ -16608,7 +16625,7 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP40" s="87">
+      <c r="AP40" s="86">
         <f t="shared" si="75"/>
         <v>0.77777777777777779</v>
       </c>
@@ -16661,12 +16678,12 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH40" s="87">
+      <c r="BH40" s="86">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="BI40" s="48"/>
-      <c r="BJ40" s="118"/>
+      <c r="BJ40" s="133"/>
       <c r="BK40" s="50" t="s">
         <v>64</v>
       </c>
@@ -16703,10 +16720,10 @@
       <c r="CB40" s="48"/>
       <c r="CC40" s="48"/>
       <c r="CD40" s="48"/>
-      <c r="CE40" s="106" t="s">
+      <c r="CE40" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="CF40" s="111">
+      <c r="CF40" s="110">
         <f t="shared" si="63"/>
         <v>2.5000000000000005E-2</v>
       </c>
@@ -16734,7 +16751,7 @@
         <f t="shared" si="69"/>
         <v>0.125</v>
       </c>
-      <c r="CM40" s="103">
+      <c r="CM40" s="102">
         <f t="shared" si="70"/>
         <v>0.5625</v>
       </c>
@@ -16791,7 +16808,7 @@
       <c r="R41" s="26">
         <v>1</v>
       </c>
-      <c r="T41" s="65">
+      <c r="T41" s="64">
         <f>SUM(U40:X40)/2</f>
         <v>2.1309038662486937</v>
       </c>
@@ -16820,7 +16837,7 @@
         <f t="shared" si="74"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP41" s="87">
+      <c r="AP41" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -16873,7 +16890,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH41" s="87">
+      <c r="BH41" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -16925,10 +16942,10 @@
       <c r="CB41" s="48"/>
       <c r="CC41" s="48"/>
       <c r="CD41" s="48"/>
-      <c r="CE41" s="106" t="s">
+      <c r="CE41" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="CF41" s="111">
+      <c r="CF41" s="110">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
@@ -16956,7 +16973,7 @@
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="CM41" s="103">
+      <c r="CM41" s="102">
         <f t="shared" si="70"/>
         <v>0.1818181818181818</v>
       </c>
@@ -17028,7 +17045,7 @@
         <f t="shared" si="74"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP42" s="87">
+      <c r="AP42" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17081,7 +17098,7 @@
         <f t="shared" si="12"/>
         <v>0.88461538461538458</v>
       </c>
-      <c r="BH42" s="87">
+      <c r="BH42" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -17133,38 +17150,38 @@
       <c r="CB42" s="48"/>
       <c r="CC42" s="48"/>
       <c r="CD42" s="48"/>
-      <c r="CE42" s="106" t="s">
+      <c r="CE42" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="CF42" s="116">
+      <c r="CF42" s="113">
         <f>BM38</f>
         <v>0</v>
       </c>
-      <c r="CG42" s="104">
+      <c r="CG42" s="103">
         <f>BQ38</f>
         <v>0.23529411764705882</v>
       </c>
-      <c r="CH42" s="104">
+      <c r="CH42" s="103">
         <f>BM56</f>
         <v>0.52941176470588236</v>
       </c>
-      <c r="CI42" s="104">
+      <c r="CI42" s="103">
         <f t="shared" si="66"/>
         <v>0.76470588235294112</v>
       </c>
-      <c r="CJ42" s="104">
+      <c r="CJ42" s="103">
         <f>BN38</f>
         <v>0.79999999999999993</v>
       </c>
-      <c r="CK42" s="104">
+      <c r="CK42" s="103">
         <f t="shared" si="68"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="CL42" s="104">
+      <c r="CL42" s="103">
         <f>BN56</f>
         <v>0</v>
       </c>
-      <c r="CM42" s="105">
+      <c r="CM42" s="104">
         <f>BR56</f>
         <v>0.10000000000000003</v>
       </c>
@@ -17236,7 +17253,7 @@
         <f t="shared" si="74"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP43" s="87">
+      <c r="AP43" s="86">
         <f t="shared" si="75"/>
         <v>0.66666666666666663</v>
       </c>
@@ -17289,7 +17306,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH43" s="87">
+      <c r="BH43" s="86">
         <f t="shared" si="13"/>
         <v>0.33333333333333337</v>
       </c>
@@ -17409,7 +17426,7 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP44" s="87">
+      <c r="AP44" s="86">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
@@ -17462,7 +17479,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH44" s="87">
+      <c r="BH44" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -17567,6 +17584,14 @@
       <c r="R45" s="26">
         <v>1</v>
       </c>
+      <c r="V45" s="13">
+        <f>40/174</f>
+        <v>0.22988505747126436</v>
+      </c>
+      <c r="Z45" s="13">
+        <f>V45</f>
+        <v>0.22988505747126436</v>
+      </c>
       <c r="AL45" s="42" t="s">
         <v>12</v>
       </c>
@@ -17582,7 +17607,7 @@
         <f t="shared" si="74"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP45" s="87">
+      <c r="AP45" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17635,7 +17660,7 @@
         <f t="shared" si="12"/>
         <v>0.84615384615384615</v>
       </c>
-      <c r="BH45" s="87">
+      <c r="BH45" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -17740,6 +17765,10 @@
       <c r="R46" s="26">
         <v>5</v>
       </c>
+      <c r="Z46" s="13">
+        <f>66/174</f>
+        <v>0.37931034482758619</v>
+      </c>
       <c r="AL46" s="42" t="s">
         <v>13</v>
       </c>
@@ -17755,7 +17784,7 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP46" s="87">
+      <c r="AP46" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17808,7 +17837,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH46" s="87">
+      <c r="BH46" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -17928,7 +17957,7 @@
         <f t="shared" si="74"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP47" s="87">
+      <c r="AP47" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -17981,7 +18010,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH47" s="87">
+      <c r="BH47" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -18101,7 +18130,7 @@
         <f t="shared" si="74"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP48" s="87">
+      <c r="AP48" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -18154,7 +18183,7 @@
         <f t="shared" si="12"/>
         <v>0.88461538461538458</v>
       </c>
-      <c r="BH48" s="87">
+      <c r="BH48" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -18274,7 +18303,7 @@
         <f t="shared" si="74"/>
         <v>0.53846153846153844</v>
       </c>
-      <c r="AP49" s="87">
+      <c r="AP49" s="86">
         <f t="shared" si="75"/>
         <v>0.66666666666666663</v>
       </c>
@@ -18327,7 +18356,7 @@
         <f t="shared" si="12"/>
         <v>0.46153846153846156</v>
       </c>
-      <c r="BH49" s="87">
+      <c r="BH49" s="86">
         <f t="shared" si="13"/>
         <v>0.33333333333333337</v>
       </c>
@@ -18447,7 +18476,7 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP50" s="87">
+      <c r="AP50" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -18500,7 +18529,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH50" s="87">
+      <c r="BH50" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -18554,10 +18583,10 @@
       <c r="CD50" s="48"/>
     </row>
     <row r="51" spans="1:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="62" t="s">
+      <c r="A51" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="B51" s="66" t="s">
+      <c r="B51" s="65" t="s">
         <v>21</v>
       </c>
       <c r="C51" s="27">
@@ -18572,10 +18601,10 @@
       <c r="F51" s="28">
         <v>0</v>
       </c>
-      <c r="H51" s="62" t="s">
+      <c r="H51" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="I51" s="66" t="s">
+      <c r="I51" s="65" t="s">
         <v>119</v>
       </c>
       <c r="J51" s="27">
@@ -18590,7 +18619,7 @@
       <c r="M51" s="27">
         <v>0</v>
       </c>
-      <c r="N51" s="66" t="s">
+      <c r="N51" s="65" t="s">
         <v>120</v>
       </c>
       <c r="O51" s="27">
@@ -18605,75 +18634,75 @@
       <c r="R51" s="28">
         <v>1</v>
       </c>
-      <c r="AL51" s="80" t="s">
+      <c r="AL51" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="AM51" s="91">
+      <c r="AM51" s="90">
         <f t="shared" si="72"/>
         <v>0.99678456591639875</v>
       </c>
-      <c r="AN51" s="92">
+      <c r="AN51" s="91">
         <f t="shared" si="73"/>
         <v>0</v>
       </c>
-      <c r="AO51" s="92">
+      <c r="AO51" s="91">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP51" s="93">
+      <c r="AP51" s="92">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
-      <c r="AR51" s="62" t="s">
+      <c r="AR51" s="61" t="s">
         <v>21</v>
       </c>
       <c r="AS51" s="21">
         <v>4</v>
       </c>
-      <c r="AT51" s="67">
-        <v>1</v>
-      </c>
-      <c r="AU51" s="67">
+      <c r="AT51" s="66">
+        <v>1</v>
+      </c>
+      <c r="AU51" s="66">
         <v>0.29943502824858759</v>
       </c>
-      <c r="AV51" s="67">
+      <c r="AV51" s="66">
         <v>0.73076923076923073</v>
       </c>
-      <c r="AW51" s="67">
+      <c r="AW51" s="66">
         <v>0</v>
       </c>
       <c r="AX51" s="21">
         <v>5</v>
       </c>
-      <c r="AY51" s="67">
+      <c r="AY51" s="66">
         <v>0.98713826366559487</v>
       </c>
-      <c r="AZ51" s="67">
+      <c r="AZ51" s="66">
         <v>0.5423728813559322</v>
       </c>
-      <c r="BA51" s="67">
+      <c r="BA51" s="66">
         <v>0.69230769230769229</v>
       </c>
-      <c r="BB51" s="68">
+      <c r="BB51" s="67">
         <v>0.1111111111111111</v>
       </c>
       <c r="BC51" s="48"/>
-      <c r="BD51" s="80" t="s">
+      <c r="BD51" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="BE51" s="91">
+      <c r="BE51" s="90">
         <f t="shared" si="10"/>
         <v>3.215434083601254E-3</v>
       </c>
-      <c r="BF51" s="92">
+      <c r="BF51" s="91">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="BG51" s="92">
+      <c r="BG51" s="91">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH51" s="93">
+      <c r="BH51" s="92">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -18749,19 +18778,19 @@
       <c r="AL52" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AM52" s="84">
+      <c r="AM52" s="83">
         <f t="shared" si="72"/>
         <v>0.96784565916398713</v>
       </c>
-      <c r="AN52" s="85">
+      <c r="AN52" s="84">
         <f t="shared" si="73"/>
         <v>0.49717514124293788</v>
       </c>
-      <c r="AO52" s="85">
+      <c r="AO52" s="84">
         <f t="shared" si="74"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP52" s="86">
+      <c r="AP52" s="85">
         <f t="shared" si="75"/>
         <v>0.77777777777777779</v>
       </c>
@@ -18769,19 +18798,19 @@
       <c r="BD52" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="BE52" s="84">
+      <c r="BE52" s="83">
         <f t="shared" si="10"/>
         <v>3.2154340836012874E-2</v>
       </c>
-      <c r="BF52" s="85">
+      <c r="BF52" s="84">
         <f t="shared" si="11"/>
         <v>0.50282485875706207</v>
       </c>
-      <c r="BG52" s="85">
+      <c r="BG52" s="84">
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH52" s="86">
+      <c r="BH52" s="85">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
@@ -18856,7 +18885,7 @@
         <f t="shared" si="74"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="AP53" s="87">
+      <c r="AP53" s="86">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
@@ -18876,7 +18905,7 @@
         <f t="shared" si="12"/>
         <v>0.65384615384615385</v>
       </c>
-      <c r="BH53" s="87">
+      <c r="BH53" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -18951,7 +18980,7 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP54" s="87">
+      <c r="AP54" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -18971,7 +19000,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH54" s="87">
+      <c r="BH54" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -19046,7 +19075,7 @@
         <f t="shared" si="74"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP55" s="87">
+      <c r="AP55" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -19066,7 +19095,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH55" s="87">
+      <c r="BH55" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -19141,7 +19170,7 @@
         <f t="shared" si="74"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP56" s="87">
+      <c r="AP56" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -19161,11 +19190,11 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH56" s="87">
+      <c r="BH56" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
-      <c r="BJ56" s="62" t="s">
+      <c r="BJ56" s="61" t="s">
         <v>21</v>
       </c>
       <c r="BK56" s="13">
@@ -19236,7 +19265,7 @@
         <f t="shared" si="74"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP57" s="87">
+      <c r="AP57" s="86">
         <f t="shared" si="75"/>
         <v>0.88888888888888884</v>
       </c>
@@ -19256,7 +19285,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH57" s="87">
+      <c r="BH57" s="86">
         <f t="shared" si="13"/>
         <v>0.11111111111111116</v>
       </c>
@@ -19296,7 +19325,7 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP58" s="87">
+      <c r="AP58" s="86">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
@@ -19316,7 +19345,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH58" s="87">
+      <c r="BH58" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -19356,7 +19385,7 @@
         <f t="shared" si="74"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP59" s="87">
+      <c r="AP59" s="86">
         <f t="shared" si="75"/>
         <v>0.77777777777777779</v>
       </c>
@@ -19376,7 +19405,7 @@
         <f t="shared" si="12"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH59" s="87">
+      <c r="BH59" s="86">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
@@ -19416,7 +19445,7 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP60" s="87">
+      <c r="AP60" s="86">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
@@ -19436,7 +19465,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH60" s="87">
+      <c r="BH60" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -19476,7 +19505,7 @@
         <f t="shared" si="74"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP61" s="87">
+      <c r="AP61" s="86">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
@@ -19496,7 +19525,7 @@
         <f t="shared" si="12"/>
         <v>0.73076923076923084</v>
       </c>
-      <c r="BH61" s="87">
+      <c r="BH61" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -19536,7 +19565,7 @@
         <f t="shared" si="74"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP62" s="87">
+      <c r="AP62" s="86">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
@@ -19556,7 +19585,7 @@
         <f t="shared" si="12"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH62" s="87">
+      <c r="BH62" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -19596,7 +19625,7 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP63" s="87">
+      <c r="AP63" s="86">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
@@ -19616,7 +19645,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH63" s="87">
+      <c r="BH63" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -19656,7 +19685,7 @@
         <f t="shared" si="74"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP64" s="87">
+      <c r="AP64" s="86">
         <f t="shared" si="75"/>
         <v>0.77777777777777779</v>
       </c>
@@ -19676,7 +19705,7 @@
         <f t="shared" si="12"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH64" s="87">
+      <c r="BH64" s="86">
         <f t="shared" si="13"/>
         <v>0.22222222222222221</v>
       </c>
@@ -19716,7 +19745,7 @@
         <f t="shared" si="74"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP65" s="87">
+      <c r="AP65" s="86">
         <f t="shared" si="75"/>
         <v>0.55555555555555558</v>
       </c>
@@ -19736,7 +19765,7 @@
         <f t="shared" si="12"/>
         <v>0.84615384615384615</v>
       </c>
-      <c r="BH65" s="87">
+      <c r="BH65" s="86">
         <f t="shared" si="13"/>
         <v>0.44444444444444442</v>
       </c>
@@ -19776,7 +19805,7 @@
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP66" s="87">
+      <c r="AP66" s="86">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
@@ -19796,7 +19825,7 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH66" s="87">
+      <c r="BH66" s="86">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -19821,82 +19850,82 @@
         <v>0</v>
       </c>
       <c r="H67" s="4"/>
-      <c r="AL67" s="80" t="s">
+      <c r="AL67" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="AM67" s="91">
+      <c r="AM67" s="90">
         <f t="shared" si="72"/>
         <v>1</v>
       </c>
-      <c r="AN67" s="92">
+      <c r="AN67" s="91">
         <f t="shared" si="73"/>
         <v>5.6497175141242938E-3</v>
       </c>
-      <c r="AO67" s="92">
+      <c r="AO67" s="91">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="AP67" s="93">
+      <c r="AP67" s="92">
         <f t="shared" si="75"/>
         <v>1</v>
       </c>
       <c r="AR67" s="4"/>
-      <c r="BD67" s="80" t="s">
+      <c r="BD67" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="BE67" s="91">
+      <c r="BE67" s="90">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BF67" s="92">
+      <c r="BF67" s="91">
         <f t="shared" si="11"/>
         <v>0.99435028248587576</v>
       </c>
-      <c r="BG67" s="92">
+      <c r="BG67" s="91">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="BH67" s="93">
+      <c r="BH67" s="92">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="80" t="s">
+      <c r="A68" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="B68" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="82">
+      <c r="B68" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="81">
         <v>18</v>
       </c>
-      <c r="D68" s="82">
+      <c r="D68" s="81">
         <v>107</v>
       </c>
-      <c r="E68" s="82">
+      <c r="E68" s="81">
         <v>2</v>
       </c>
-      <c r="F68" s="83">
+      <c r="F68" s="82">
         <v>3</v>
       </c>
       <c r="H68" s="4"/>
       <c r="AL68" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AM68" s="84">
+      <c r="AM68" s="83">
         <f t="shared" ref="AM68:AM99" si="86">(AG$4-C68)/(AG$4-AG$5)</f>
         <v>0.94212218649517687</v>
       </c>
-      <c r="AN68" s="85">
+      <c r="AN68" s="84">
         <f t="shared" ref="AN68:AN99" si="87">(D68-AH$5)/(AH$4-AH$5)</f>
         <v>0.60451977401129942</v>
       </c>
-      <c r="AO68" s="85">
+      <c r="AO68" s="84">
         <f t="shared" ref="AO68:AO99" si="88">(E68-AI$5)/(AI$4-AI$5)</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP68" s="86">
+      <c r="AP68" s="85">
         <f t="shared" ref="AP68:AP99" si="89">(AJ$4-F68)/(AJ$4-AJ$5)</f>
         <v>0.66666666666666663</v>
       </c>
@@ -19904,19 +19933,19 @@
       <c r="BD68" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="BE68" s="84">
+      <c r="BE68" s="83">
         <f t="shared" si="10"/>
         <v>5.7877813504823128E-2</v>
       </c>
-      <c r="BF68" s="85">
+      <c r="BF68" s="84">
         <f t="shared" si="11"/>
         <v>0.39548022598870058</v>
       </c>
-      <c r="BG68" s="85">
+      <c r="BG68" s="84">
         <f t="shared" si="12"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH68" s="86">
+      <c r="BH68" s="85">
         <f t="shared" si="13"/>
         <v>0.33333333333333337</v>
       </c>
@@ -19925,19 +19954,19 @@
       <c r="A69" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="B69" s="77" t="s">
+      <c r="B69" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="78">
-        <v>1</v>
-      </c>
-      <c r="D69" s="78">
+      <c r="C69" s="77">
+        <v>1</v>
+      </c>
+      <c r="D69" s="77">
         <v>144</v>
       </c>
-      <c r="E69" s="78">
+      <c r="E69" s="77">
         <v>3</v>
       </c>
-      <c r="F69" s="79">
+      <c r="F69" s="78">
         <v>1</v>
       </c>
       <c r="H69" s="4"/>
@@ -19956,7 +19985,7 @@
         <f t="shared" si="88"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP69" s="87">
+      <c r="AP69" s="86">
         <f t="shared" si="89"/>
         <v>0.88888888888888884</v>
       </c>
@@ -19976,7 +20005,7 @@
         <f t="shared" ref="BG69:BG99" si="92">1-AO69</f>
         <v>0.88461538461538458</v>
       </c>
-      <c r="BH69" s="87">
+      <c r="BH69" s="86">
         <f t="shared" ref="BH69:BH99" si="93">1-AP69</f>
         <v>0.11111111111111116</v>
       </c>
@@ -20016,7 +20045,7 @@
         <f t="shared" si="88"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP70" s="87">
+      <c r="AP70" s="86">
         <f t="shared" si="89"/>
         <v>0.88888888888888884</v>
       </c>
@@ -20036,7 +20065,7 @@
         <f t="shared" si="92"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH70" s="87">
+      <c r="BH70" s="86">
         <f t="shared" si="93"/>
         <v>0.11111111111111116</v>
       </c>
@@ -20076,7 +20105,7 @@
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="AP71" s="87">
+      <c r="AP71" s="86">
         <f t="shared" si="89"/>
         <v>1</v>
       </c>
@@ -20096,7 +20125,7 @@
         <f t="shared" si="92"/>
         <v>1</v>
       </c>
-      <c r="BH71" s="87">
+      <c r="BH71" s="86">
         <f t="shared" si="93"/>
         <v>0</v>
       </c>
@@ -20136,7 +20165,7 @@
         <f t="shared" si="88"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP72" s="87">
+      <c r="AP72" s="86">
         <f t="shared" si="89"/>
         <v>0.88888888888888884</v>
       </c>
@@ -20156,7 +20185,7 @@
         <f t="shared" si="92"/>
         <v>0.88461538461538458</v>
       </c>
-      <c r="BH72" s="87">
+      <c r="BH72" s="86">
         <f t="shared" si="93"/>
         <v>0.11111111111111116</v>
       </c>
@@ -20196,7 +20225,7 @@
         <f t="shared" si="88"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP73" s="87">
+      <c r="AP73" s="86">
         <f t="shared" si="89"/>
         <v>0.66666666666666663</v>
       </c>
@@ -20216,7 +20245,7 @@
         <f t="shared" si="92"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH73" s="87">
+      <c r="BH73" s="86">
         <f t="shared" si="93"/>
         <v>0.33333333333333337</v>
       </c>
@@ -20256,7 +20285,7 @@
         <f t="shared" si="88"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP74" s="87">
+      <c r="AP74" s="86">
         <f t="shared" si="89"/>
         <v>0.44444444444444442</v>
       </c>
@@ -20276,7 +20305,7 @@
         <f t="shared" si="92"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH74" s="87">
+      <c r="BH74" s="86">
         <f t="shared" si="93"/>
         <v>0.55555555555555558</v>
       </c>
@@ -20316,7 +20345,7 @@
         <f t="shared" si="88"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="AP75" s="87">
+      <c r="AP75" s="86">
         <f t="shared" si="89"/>
         <v>0.33333333333333331</v>
       </c>
@@ -20336,7 +20365,7 @@
         <f t="shared" si="92"/>
         <v>0.65384615384615385</v>
       </c>
-      <c r="BH75" s="87">
+      <c r="BH75" s="86">
         <f t="shared" si="93"/>
         <v>0.66666666666666674</v>
       </c>
@@ -20376,7 +20405,7 @@
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="AP76" s="87">
+      <c r="AP76" s="86">
         <f t="shared" si="89"/>
         <v>1</v>
       </c>
@@ -20396,7 +20425,7 @@
         <f t="shared" si="92"/>
         <v>1</v>
       </c>
-      <c r="BH76" s="87">
+      <c r="BH76" s="86">
         <f t="shared" si="93"/>
         <v>0</v>
       </c>
@@ -20436,7 +20465,7 @@
         <f t="shared" si="88"/>
         <v>0.23076923076923078</v>
       </c>
-      <c r="AP77" s="87">
+      <c r="AP77" s="86">
         <f t="shared" si="89"/>
         <v>0.77777777777777779</v>
       </c>
@@ -20456,7 +20485,7 @@
         <f t="shared" si="92"/>
         <v>0.76923076923076916</v>
       </c>
-      <c r="BH77" s="87">
+      <c r="BH77" s="86">
         <f t="shared" si="93"/>
         <v>0.22222222222222221</v>
       </c>
@@ -20496,7 +20525,7 @@
         <f t="shared" si="88"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP78" s="87">
+      <c r="AP78" s="86">
         <f t="shared" si="89"/>
         <v>0.88888888888888884</v>
       </c>
@@ -20516,7 +20545,7 @@
         <f t="shared" si="92"/>
         <v>0.88461538461538458</v>
       </c>
-      <c r="BH78" s="87">
+      <c r="BH78" s="86">
         <f t="shared" si="93"/>
         <v>0.11111111111111116</v>
       </c>
@@ -20556,7 +20585,7 @@
         <f t="shared" si="88"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP79" s="87">
+      <c r="AP79" s="86">
         <f t="shared" si="89"/>
         <v>0.77777777777777779</v>
       </c>
@@ -20576,7 +20605,7 @@
         <f t="shared" si="92"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH79" s="87">
+      <c r="BH79" s="86">
         <f t="shared" si="93"/>
         <v>0.22222222222222221</v>
       </c>
@@ -20616,7 +20645,7 @@
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="AP80" s="87">
+      <c r="AP80" s="86">
         <f t="shared" si="89"/>
         <v>1</v>
       </c>
@@ -20636,7 +20665,7 @@
         <f t="shared" si="92"/>
         <v>1</v>
       </c>
-      <c r="BH80" s="87">
+      <c r="BH80" s="86">
         <f t="shared" si="93"/>
         <v>0</v>
       </c>
@@ -20676,7 +20705,7 @@
         <f t="shared" si="88"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP81" s="87">
+      <c r="AP81" s="86">
         <f t="shared" si="89"/>
         <v>0.55555555555555558</v>
       </c>
@@ -20696,7 +20725,7 @@
         <f t="shared" si="92"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH81" s="87">
+      <c r="BH81" s="86">
         <f t="shared" si="93"/>
         <v>0.44444444444444442</v>
       </c>
@@ -20736,7 +20765,7 @@
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="AP82" s="87">
+      <c r="AP82" s="86">
         <f t="shared" si="89"/>
         <v>0.77777777777777779</v>
       </c>
@@ -20756,16 +20785,16 @@
         <f t="shared" si="92"/>
         <v>1</v>
       </c>
-      <c r="BH82" s="87">
+      <c r="BH82" s="86">
         <f t="shared" si="93"/>
         <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="83" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="62" t="s">
+      <c r="A83" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="B83" s="66" t="s">
+      <c r="B83" s="65" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="27">
@@ -20781,42 +20810,42 @@
         <v>0</v>
       </c>
       <c r="H83" s="4"/>
-      <c r="AL83" s="80" t="s">
+      <c r="AL83" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="AM83" s="91">
+      <c r="AM83" s="90">
         <f t="shared" si="86"/>
         <v>1</v>
       </c>
-      <c r="AN83" s="92">
+      <c r="AN83" s="91">
         <f t="shared" si="87"/>
         <v>0.29943502824858759</v>
       </c>
-      <c r="AO83" s="92">
+      <c r="AO83" s="91">
         <f t="shared" si="88"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="AP83" s="93">
+      <c r="AP83" s="92">
         <f t="shared" si="89"/>
         <v>1</v>
       </c>
       <c r="AR83" s="4"/>
-      <c r="BD83" s="80" t="s">
+      <c r="BD83" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="BE83" s="91">
+      <c r="BE83" s="90">
         <f t="shared" si="90"/>
         <v>0</v>
       </c>
-      <c r="BF83" s="92">
+      <c r="BF83" s="91">
         <f t="shared" si="91"/>
         <v>0.70056497175141241</v>
       </c>
-      <c r="BG83" s="92">
+      <c r="BG83" s="91">
         <f t="shared" si="92"/>
         <v>0.73076923076923084</v>
       </c>
-      <c r="BH83" s="93">
+      <c r="BH83" s="92">
         <f t="shared" si="93"/>
         <v>0</v>
       </c>
@@ -20844,19 +20873,19 @@
       <c r="AL84" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="AM84" s="94">
+      <c r="AM84" s="93">
         <f t="shared" si="86"/>
         <v>0.98392282958199362</v>
       </c>
-      <c r="AN84" s="95">
+      <c r="AN84" s="94">
         <f t="shared" si="87"/>
         <v>0.39548022598870058</v>
       </c>
-      <c r="AO84" s="95">
+      <c r="AO84" s="94">
         <f t="shared" si="88"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP84" s="96">
+      <c r="AP84" s="95">
         <f t="shared" si="89"/>
         <v>0.88888888888888884</v>
       </c>
@@ -20864,19 +20893,19 @@
       <c r="BD84" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="BE84" s="94">
+      <c r="BE84" s="93">
         <f t="shared" si="90"/>
         <v>1.6077170418006381E-2</v>
       </c>
-      <c r="BF84" s="95">
+      <c r="BF84" s="94">
         <f t="shared" si="91"/>
         <v>0.60451977401129942</v>
       </c>
-      <c r="BG84" s="95">
+      <c r="BG84" s="94">
         <f t="shared" si="92"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH84" s="96">
+      <c r="BH84" s="95">
         <f t="shared" si="93"/>
         <v>0.11111111111111116</v>
       </c>
@@ -20916,7 +20945,7 @@
         <f t="shared" si="88"/>
         <v>1</v>
       </c>
-      <c r="AP85" s="87">
+      <c r="AP85" s="86">
         <f t="shared" si="89"/>
         <v>1</v>
       </c>
@@ -20936,7 +20965,7 @@
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="BH85" s="87">
+      <c r="BH85" s="86">
         <f t="shared" si="93"/>
         <v>0</v>
       </c>
@@ -20976,7 +21005,7 @@
         <f t="shared" si="88"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP86" s="87">
+      <c r="AP86" s="86">
         <f t="shared" si="89"/>
         <v>0.77777777777777779</v>
       </c>
@@ -20996,7 +21025,7 @@
         <f t="shared" si="92"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH86" s="87">
+      <c r="BH86" s="86">
         <f t="shared" si="93"/>
         <v>0.22222222222222221</v>
       </c>
@@ -21036,7 +21065,7 @@
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="AP87" s="87">
+      <c r="AP87" s="86">
         <f t="shared" si="89"/>
         <v>1</v>
       </c>
@@ -21056,7 +21085,7 @@
         <f t="shared" si="92"/>
         <v>1</v>
       </c>
-      <c r="BH87" s="87">
+      <c r="BH87" s="86">
         <f t="shared" si="93"/>
         <v>0</v>
       </c>
@@ -21096,7 +21125,7 @@
         <f t="shared" si="88"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="AP88" s="87">
+      <c r="AP88" s="86">
         <f t="shared" si="89"/>
         <v>1</v>
       </c>
@@ -21116,7 +21145,7 @@
         <f t="shared" si="92"/>
         <v>0.88461538461538458</v>
       </c>
-      <c r="BH88" s="87">
+      <c r="BH88" s="86">
         <f t="shared" si="93"/>
         <v>0</v>
       </c>
@@ -21156,7 +21185,7 @@
         <f t="shared" si="88"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP89" s="87">
+      <c r="AP89" s="86">
         <f t="shared" si="89"/>
         <v>0.88888888888888884</v>
       </c>
@@ -21176,7 +21205,7 @@
         <f t="shared" si="92"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH89" s="87">
+      <c r="BH89" s="86">
         <f t="shared" si="93"/>
         <v>0.11111111111111116</v>
       </c>
@@ -21216,7 +21245,7 @@
         <f t="shared" si="88"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP90" s="87">
+      <c r="AP90" s="86">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
@@ -21236,7 +21265,7 @@
         <f t="shared" si="92"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH90" s="87">
+      <c r="BH90" s="86">
         <f t="shared" si="93"/>
         <v>1</v>
       </c>
@@ -21276,7 +21305,7 @@
         <f t="shared" si="88"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="AP91" s="87">
+      <c r="AP91" s="86">
         <f t="shared" si="89"/>
         <v>0.33333333333333331</v>
       </c>
@@ -21296,7 +21325,7 @@
         <f t="shared" si="92"/>
         <v>0.84615384615384615</v>
       </c>
-      <c r="BH91" s="87">
+      <c r="BH91" s="86">
         <f t="shared" si="93"/>
         <v>0.66666666666666674</v>
       </c>
@@ -21336,7 +21365,7 @@
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="AP92" s="87">
+      <c r="AP92" s="86">
         <f t="shared" si="89"/>
         <v>1</v>
       </c>
@@ -21356,7 +21385,7 @@
         <f t="shared" si="92"/>
         <v>1</v>
       </c>
-      <c r="BH92" s="87">
+      <c r="BH92" s="86">
         <f t="shared" si="93"/>
         <v>0</v>
       </c>
@@ -21396,7 +21425,7 @@
         <f t="shared" si="88"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP93" s="87">
+      <c r="AP93" s="86">
         <f t="shared" si="89"/>
         <v>0.88888888888888884</v>
       </c>
@@ -21416,7 +21445,7 @@
         <f t="shared" si="92"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH93" s="87">
+      <c r="BH93" s="86">
         <f t="shared" si="93"/>
         <v>0.11111111111111116</v>
       </c>
@@ -21456,7 +21485,7 @@
         <f t="shared" si="88"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP94" s="87">
+      <c r="AP94" s="86">
         <f t="shared" si="89"/>
         <v>0.44444444444444442</v>
       </c>
@@ -21476,7 +21505,7 @@
         <f t="shared" si="92"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH94" s="87">
+      <c r="BH94" s="86">
         <f t="shared" si="93"/>
         <v>0.55555555555555558</v>
       </c>
@@ -21516,7 +21545,7 @@
         <f t="shared" si="88"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP95" s="87">
+      <c r="AP95" s="86">
         <f t="shared" si="89"/>
         <v>0.33333333333333331</v>
       </c>
@@ -21536,7 +21565,7 @@
         <f t="shared" si="92"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH95" s="87">
+      <c r="BH95" s="86">
         <f t="shared" si="93"/>
         <v>0.66666666666666674</v>
       </c>
@@ -21576,7 +21605,7 @@
         <f t="shared" si="88"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="AP96" s="87">
+      <c r="AP96" s="86">
         <f t="shared" si="89"/>
         <v>0.88888888888888884</v>
       </c>
@@ -21596,7 +21625,7 @@
         <f t="shared" si="92"/>
         <v>0.92307692307692313</v>
       </c>
-      <c r="BH96" s="87">
+      <c r="BH96" s="86">
         <f t="shared" si="93"/>
         <v>0.11111111111111116</v>
       </c>
@@ -21636,7 +21665,7 @@
         <f t="shared" si="88"/>
         <v>0.57692307692307687</v>
       </c>
-      <c r="AP97" s="87">
+      <c r="AP97" s="86">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
@@ -21656,7 +21685,7 @@
         <f t="shared" si="92"/>
         <v>0.42307692307692313</v>
       </c>
-      <c r="BH97" s="87">
+      <c r="BH97" s="86">
         <f t="shared" si="93"/>
         <v>1</v>
       </c>
@@ -21696,7 +21725,7 @@
         <f t="shared" si="88"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="AP98" s="87">
+      <c r="AP98" s="86">
         <f t="shared" si="89"/>
         <v>1</v>
       </c>
@@ -21716,16 +21745,16 @@
         <f t="shared" si="92"/>
         <v>0.96153846153846156</v>
       </c>
-      <c r="BH98" s="87">
+      <c r="BH98" s="86">
         <f t="shared" si="93"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="62" t="s">
+      <c r="A99" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="B99" s="66" t="s">
+      <c r="B99" s="65" t="s">
         <v>21</v>
       </c>
       <c r="C99" s="27">
@@ -21741,42 +21770,42 @@
         <v>1</v>
       </c>
       <c r="H99" s="4"/>
-      <c r="AL99" s="62" t="s">
+      <c r="AL99" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="AM99" s="88">
+      <c r="AM99" s="87">
         <f t="shared" si="86"/>
         <v>0.98713826366559487</v>
       </c>
-      <c r="AN99" s="89">
+      <c r="AN99" s="88">
         <f t="shared" si="87"/>
         <v>0.5423728813559322</v>
       </c>
-      <c r="AO99" s="89">
+      <c r="AO99" s="88">
         <f t="shared" si="88"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="AP99" s="90">
+      <c r="AP99" s="89">
         <f t="shared" si="89"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AR99" s="4"/>
-      <c r="BD99" s="62" t="s">
+      <c r="BD99" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="BE99" s="88">
+      <c r="BE99" s="87">
         <f t="shared" si="90"/>
         <v>1.2861736334405127E-2</v>
       </c>
-      <c r="BF99" s="89">
+      <c r="BF99" s="88">
         <f t="shared" si="91"/>
         <v>0.4576271186440678</v>
       </c>
-      <c r="BG99" s="89">
+      <c r="BG99" s="88">
         <f t="shared" si="92"/>
         <v>0.69230769230769229</v>
       </c>
-      <c r="BH99" s="90">
+      <c r="BH99" s="89">
         <f t="shared" si="93"/>
         <v>0.11111111111111116</v>
       </c>
@@ -21786,6 +21815,24 @@
     <sortCondition ref="CY4:CY19"/>
   </sortState>
   <mergeCells count="30">
+    <mergeCell ref="BJ39:BJ40"/>
+    <mergeCell ref="BK39:BN39"/>
+    <mergeCell ref="BO39:BR39"/>
+    <mergeCell ref="CF23:CG23"/>
+    <mergeCell ref="CH23:CI23"/>
+    <mergeCell ref="CJ23:CK23"/>
+    <mergeCell ref="CL23:CM23"/>
+    <mergeCell ref="CF25:CG25"/>
+    <mergeCell ref="CH25:CI25"/>
+    <mergeCell ref="CJ25:CK25"/>
+    <mergeCell ref="CL25:CM25"/>
+    <mergeCell ref="CF5:CG5"/>
+    <mergeCell ref="CH5:CI5"/>
+    <mergeCell ref="CJ5:CK5"/>
+    <mergeCell ref="CL5:CM5"/>
+    <mergeCell ref="BJ21:BJ22"/>
+    <mergeCell ref="BK21:BN21"/>
+    <mergeCell ref="BO21:BR21"/>
     <mergeCell ref="DF3:DG3"/>
     <mergeCell ref="DE1:DI1"/>
     <mergeCell ref="CL3:CM3"/>
@@ -21798,24 +21845,6 @@
     <mergeCell ref="CJ3:CK3"/>
     <mergeCell ref="BV3:BY3"/>
     <mergeCell ref="BZ3:CC3"/>
-    <mergeCell ref="CF5:CG5"/>
-    <mergeCell ref="CH5:CI5"/>
-    <mergeCell ref="CJ5:CK5"/>
-    <mergeCell ref="CL5:CM5"/>
-    <mergeCell ref="BJ21:BJ22"/>
-    <mergeCell ref="BK21:BN21"/>
-    <mergeCell ref="BO21:BR21"/>
-    <mergeCell ref="CJ23:CK23"/>
-    <mergeCell ref="CL23:CM23"/>
-    <mergeCell ref="CF25:CG25"/>
-    <mergeCell ref="CH25:CI25"/>
-    <mergeCell ref="CJ25:CK25"/>
-    <mergeCell ref="CL25:CM25"/>
-    <mergeCell ref="BJ39:BJ40"/>
-    <mergeCell ref="BK39:BN39"/>
-    <mergeCell ref="BO39:BR39"/>
-    <mergeCell ref="CF23:CG23"/>
-    <mergeCell ref="CH23:CI23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
